--- a/Design-Files/FMM-v1.0/BOM/Client-BOM-FMM-v1.0.xlsx
+++ b/Design-Files/FMM-v1.0/BOM/Client-BOM-FMM-v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="402">
   <si>
     <t>#</t>
   </si>
@@ -216,9 +216,6 @@
     <t>R1</t>
   </si>
   <si>
-    <t>R2</t>
-  </si>
-  <si>
     <t>R3</t>
   </si>
   <si>
@@ -261,9 +258,6 @@
     <t>R18</t>
   </si>
   <si>
-    <t>R19, R23, R24, R27</t>
-  </si>
-  <si>
     <t>R20, R22</t>
   </si>
   <si>
@@ -276,9 +270,6 @@
     <t>R29, R31</t>
   </si>
   <si>
-    <t>R30</t>
-  </si>
-  <si>
     <t>R32</t>
   </si>
   <si>
@@ -1197,7 +1188,43 @@
     <t>MDD</t>
   </si>
   <si>
-    <t>SB2</t>
+    <t>FB1, FB2, FB3, FB4, FB5</t>
+  </si>
+  <si>
+    <t>R2, R16</t>
+  </si>
+  <si>
+    <t>R17, R30, R41</t>
+  </si>
+  <si>
+    <t>R19, R23, R24, R27, R42, R43</t>
+  </si>
+  <si>
+    <t>R44, R45</t>
+  </si>
+  <si>
+    <t>SB1, SB2</t>
+  </si>
+  <si>
+    <t>MMZ2012R102ATD25</t>
+  </si>
+  <si>
+    <t>RC0402FR-070RL</t>
+  </si>
+  <si>
+    <t>Ferrite Bead</t>
+  </si>
+  <si>
+    <t>FERRITE BEAD 1K OHM 0805 1LN</t>
+  </si>
+  <si>
+    <t>Ind-0805</t>
+  </si>
+  <si>
+    <t>RES 0 OHM JUMPER 1/16W 0402</t>
+  </si>
+  <si>
+    <t>0R</t>
   </si>
 </sst>
 </file>
@@ -1205,7 +1232,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -1521,13 +1548,10 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1542,7 +1566,7 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1551,34 +1575,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="13" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="13" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1593,8 +1593,35 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1884,7 +1911,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S89"/>
+  <dimension ref="A1:T92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="4" customWidth="1"/>
@@ -1902,7 +1929,7 @@
     <col min="14" max="14" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="29.42578125" customWidth="1"/>
     <col min="16" max="16" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="25.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1914,13 +1941,13 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
     </row>
     <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1934,37 +1961,37 @@
         <v>22</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J2" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="K2" s="5" t="s">
-        <v>362</v>
-      </c>
-      <c r="L2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="M2" s="5" t="s">
-        <v>360</v>
-      </c>
       <c r="N2" s="5" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1980,19 +2007,19 @@
         <v>23</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="J3" s="7">
         <v>5</v>
@@ -2001,13 +2028,13 @@
         <f>J3*5</f>
         <v>25</v>
       </c>
-      <c r="L3" s="15" t="s">
-        <v>359</v>
-      </c>
-      <c r="M3" s="16">
+      <c r="L3" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="M3" s="15">
         <v>0.124</v>
       </c>
-      <c r="N3" s="16">
+      <c r="N3" s="15">
         <f>M3*K3</f>
         <v>3.1</v>
       </c>
@@ -2016,7 +2043,7 @@
     <row r="4" spans="1:15" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="11">
-        <f t="shared" ref="B4:B85" si="0">ROW(B4) - ROW($B$2)</f>
+        <f t="shared" ref="B4:B87" si="0">ROW(B4) - ROW($B$2)</f>
         <v>2</v>
       </c>
       <c r="C4" s="12" t="s">
@@ -2026,35 +2053,35 @@
         <v>24</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="J4" s="9">
         <v>23</v>
       </c>
       <c r="K4" s="7">
-        <f t="shared" ref="K4:K67" si="1">J4*5</f>
+        <f t="shared" ref="K4:K69" si="1">J4*5</f>
         <v>115</v>
       </c>
-      <c r="L4" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M4" s="16">
+      <c r="L4" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M4" s="15">
         <v>1.9400000000000001E-2</v>
       </c>
-      <c r="N4" s="16">
-        <f t="shared" ref="N4:N68" si="2">M4*K4</f>
+      <c r="N4" s="15">
+        <f t="shared" ref="N4:N70" si="2">M4*K4</f>
         <v>2.2309999999999999</v>
       </c>
       <c r="O4" s="9"/>
@@ -2072,19 +2099,19 @@
         <v>25</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="J5" s="7">
         <v>2</v>
@@ -2093,13 +2120,13 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L5" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M5" s="16">
+      <c r="L5" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M5" s="15">
         <v>0.92100000000000004</v>
       </c>
-      <c r="N5" s="16">
+      <c r="N5" s="15">
         <f t="shared" si="2"/>
         <v>9.2100000000000009</v>
       </c>
@@ -2118,19 +2145,19 @@
         <v>26</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J6" s="9">
         <v>2</v>
@@ -2139,13 +2166,13 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L6" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M6" s="16">
+      <c r="L6" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M6" s="15">
         <v>1.0389999999999999</v>
       </c>
-      <c r="N6" s="16">
+      <c r="N6" s="15">
         <f t="shared" si="2"/>
         <v>10.389999999999999</v>
       </c>
@@ -2164,19 +2191,19 @@
         <v>27</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="J7" s="7">
         <v>2</v>
@@ -2185,13 +2212,13 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L7" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M7" s="16">
+      <c r="L7" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M7" s="15">
         <v>0.22</v>
       </c>
-      <c r="N7" s="16">
+      <c r="N7" s="15">
         <f t="shared" si="2"/>
         <v>2.2000000000000002</v>
       </c>
@@ -2210,19 +2237,19 @@
         <v>28</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="J8" s="9">
         <v>1</v>
@@ -2231,13 +2258,13 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L8" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M8" s="16">
+      <c r="L8" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M8" s="15">
         <v>0.1</v>
       </c>
-      <c r="N8" s="16">
+      <c r="N8" s="15">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
@@ -2256,19 +2283,19 @@
         <v>29</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="J9" s="7">
         <v>1</v>
@@ -2277,13 +2304,13 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L9" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M9" s="16">
+      <c r="L9" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M9" s="15">
         <v>0.1</v>
       </c>
-      <c r="N9" s="16">
+      <c r="N9" s="15">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
@@ -2302,19 +2329,19 @@
         <v>30</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="J10" s="9">
         <v>1</v>
@@ -2323,13 +2350,13 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L10" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M10" s="16">
+      <c r="L10" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M10" s="15">
         <v>0.1</v>
       </c>
-      <c r="N10" s="16">
+      <c r="N10" s="15">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
@@ -2348,19 +2375,19 @@
         <v>31</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="J11" s="7">
         <v>1</v>
@@ -2369,13 +2396,13 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L11" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M11" s="16">
+      <c r="L11" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M11" s="15">
         <v>0.1</v>
       </c>
-      <c r="N11" s="16">
+      <c r="N11" s="15">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
@@ -2394,19 +2421,19 @@
         <v>32</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="J12" s="9">
         <v>3</v>
@@ -2415,13 +2442,13 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="L12" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M12" s="16">
+      <c r="L12" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M12" s="15">
         <v>0.22600000000000001</v>
       </c>
-      <c r="N12" s="16">
+      <c r="N12" s="15">
         <f t="shared" si="2"/>
         <v>3.39</v>
       </c>
@@ -2440,19 +2467,19 @@
         <v>33</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="J13" s="7">
         <v>2</v>
@@ -2461,13 +2488,13 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L13" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M13" s="16">
+      <c r="L13" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M13" s="15">
         <v>0.73699999999999999</v>
       </c>
-      <c r="N13" s="16">
+      <c r="N13" s="15">
         <f t="shared" si="2"/>
         <v>7.37</v>
       </c>
@@ -2486,19 +2513,19 @@
         <v>34</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="J14" s="9">
         <v>1</v>
@@ -2507,13 +2534,13 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L14" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M14" s="16">
+      <c r="L14" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M14" s="15">
         <v>0.22</v>
       </c>
-      <c r="N14" s="16">
+      <c r="N14" s="15">
         <f t="shared" si="2"/>
         <v>1.1000000000000001</v>
       </c>
@@ -2532,19 +2559,19 @@
         <v>35</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="J15" s="7">
         <v>7</v>
@@ -2553,13 +2580,13 @@
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="L15" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M15" s="16">
+      <c r="L15" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M15" s="15">
         <v>0.26</v>
       </c>
-      <c r="N15" s="16">
+      <c r="N15" s="15">
         <f t="shared" si="2"/>
         <v>9.1</v>
       </c>
@@ -2578,19 +2605,19 @@
         <v>36</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="J16" s="9">
         <v>1</v>
@@ -2599,13 +2626,13 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L16" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M16" s="16">
+      <c r="L16" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M16" s="15">
         <v>0.45</v>
       </c>
-      <c r="N16" s="16">
+      <c r="N16" s="15">
         <f t="shared" si="2"/>
         <v>2.25</v>
       </c>
@@ -2624,19 +2651,19 @@
         <v>37</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="J17" s="7">
         <v>2</v>
@@ -2645,13 +2672,13 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L17" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M17" s="16">
+      <c r="L17" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M17" s="15">
         <v>0.11899999999999999</v>
       </c>
-      <c r="N17" s="16">
+      <c r="N17" s="15">
         <f t="shared" si="2"/>
         <v>1.19</v>
       </c>
@@ -2670,19 +2697,19 @@
         <v>38</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="J18" s="9">
         <v>1</v>
@@ -2691,13 +2718,13 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L18" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M18" s="16">
+      <c r="L18" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M18" s="15">
         <v>0.48</v>
       </c>
-      <c r="N18" s="16">
+      <c r="N18" s="15">
         <f t="shared" si="2"/>
         <v>2.4</v>
       </c>
@@ -2713,22 +2740,22 @@
         <v>2</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="J19" s="7">
         <v>1</v>
@@ -2737,13 +2764,13 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L19" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M19" s="16">
+      <c r="L19" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M19" s="15">
         <v>0.37</v>
       </c>
-      <c r="N19" s="16">
+      <c r="N19" s="15">
         <f t="shared" si="2"/>
         <v>1.85</v>
       </c>
@@ -2762,19 +2789,19 @@
         <v>39</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="J20" s="7">
         <v>1</v>
@@ -2783,13 +2810,13 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L20" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M20" s="16">
+      <c r="L20" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M20" s="15">
         <v>2.96</v>
       </c>
-      <c r="N20" s="16">
+      <c r="N20" s="15">
         <f t="shared" si="2"/>
         <v>14.8</v>
       </c>
@@ -2808,19 +2835,19 @@
         <v>40</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="J21" s="9">
         <v>1</v>
@@ -2829,13 +2856,13 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L21" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M21" s="16">
+      <c r="L21" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M21" s="15">
         <v>0.91</v>
       </c>
-      <c r="N21" s="16">
+      <c r="N21" s="15">
         <f t="shared" si="2"/>
         <v>4.55</v>
       </c>
@@ -2854,19 +2881,19 @@
         <v>41</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="J22" s="7">
         <v>1</v>
@@ -2875,13 +2902,13 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L22" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M22" s="16">
+      <c r="L22" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M22" s="15">
         <v>0.21</v>
       </c>
-      <c r="N22" s="16">
+      <c r="N22" s="15">
         <f t="shared" si="2"/>
         <v>1.05</v>
       </c>
@@ -2900,19 +2927,19 @@
         <v>42</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="J23" s="9">
         <v>1</v>
@@ -2921,13 +2948,13 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L23" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M23" s="16">
+      <c r="L23" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M23" s="15">
         <v>0.38</v>
       </c>
-      <c r="N23" s="16">
+      <c r="N23" s="15">
         <f t="shared" si="2"/>
         <v>1.9</v>
       </c>
@@ -2946,19 +2973,19 @@
         <v>43</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="J24" s="7">
         <v>2</v>
@@ -2967,13 +2994,13 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L24" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M24" s="16">
+      <c r="L24" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M24" s="15">
         <v>0.255</v>
       </c>
-      <c r="N24" s="16">
+      <c r="N24" s="15">
         <f t="shared" si="2"/>
         <v>2.5499999999999998</v>
       </c>
@@ -2992,19 +3019,19 @@
         <v>44</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="J25" s="9">
         <v>1</v>
@@ -3013,13 +3040,13 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L25" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M25" s="16">
+      <c r="L25" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M25" s="15">
         <v>0.41</v>
       </c>
-      <c r="N25" s="16">
+      <c r="N25" s="15">
         <f t="shared" si="2"/>
         <v>2.0499999999999998</v>
       </c>
@@ -3035,22 +3062,22 @@
         <v>4</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="J26" s="7">
         <v>3</v>
@@ -3058,13 +3085,13 @@
       <c r="K26" s="7">
         <v>50</v>
       </c>
-      <c r="L26" s="17" t="s">
-        <v>371</v>
-      </c>
-      <c r="M26" s="16">
+      <c r="L26" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="M26" s="15">
         <v>1.54E-2</v>
       </c>
-      <c r="N26" s="16">
+      <c r="N26" s="15">
         <f t="shared" si="2"/>
         <v>0.77</v>
       </c>
@@ -3083,19 +3110,19 @@
         <v>45</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="J27" s="9">
         <v>1</v>
@@ -3104,13 +3131,13 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L27" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M27" s="16">
+      <c r="L27" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M27" s="15">
         <v>1.5</v>
       </c>
-      <c r="N27" s="16">
+      <c r="N27" s="15">
         <f t="shared" si="2"/>
         <v>7.5</v>
       </c>
@@ -3129,19 +3156,19 @@
         <v>46</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="J28" s="7">
         <v>4</v>
@@ -3150,13 +3177,13 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L28" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M28" s="16">
+      <c r="L28" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M28" s="15">
         <v>0.26900000000000002</v>
       </c>
-      <c r="N28" s="16">
+      <c r="N28" s="15">
         <f t="shared" si="2"/>
         <v>5.3800000000000008</v>
       </c>
@@ -3172,22 +3199,22 @@
         <v>3</v>
       </c>
       <c r="D29" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="E29" s="8" t="s">
         <v>387</v>
       </c>
-      <c r="E29" s="8" t="s">
-        <v>390</v>
-      </c>
       <c r="F29" s="7" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>384</v>
+        <v>355</v>
       </c>
       <c r="J29" s="7">
         <v>1</v>
@@ -3195,13 +3222,13 @@
       <c r="K29" s="7">
         <v>20</v>
       </c>
-      <c r="L29" s="17" t="s">
-        <v>371</v>
-      </c>
-      <c r="M29" s="16">
+      <c r="L29" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="M29" s="15">
         <v>2.3300000000000001E-2</v>
       </c>
-      <c r="N29" s="16">
+      <c r="N29" s="15">
         <f t="shared" si="2"/>
         <v>0.46600000000000003</v>
       </c>
@@ -3210,1515 +3237,1514 @@
     <row r="30" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B30) - ROW($B$2)</f>
         <v>28</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>7</v>
+        <v>397</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>127</v>
+        <v>398</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>363</v>
+        <v>399</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>197</v>
+        <v>395</v>
       </c>
       <c r="H30" s="9" t="s">
         <v>301</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="J30" s="9">
+        <v>355</v>
+      </c>
+      <c r="J30" s="7">
+        <v>5</v>
+      </c>
+      <c r="K30" s="7">
+        <v>20</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M30" s="15">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="N30" s="15">
+        <f t="shared" si="2"/>
+        <v>1.8599999999999999</v>
+      </c>
+      <c r="O30" s="7"/>
+    </row>
+    <row r="31" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="1"/>
+      <c r="B31" s="11">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="J31" s="9">
         <v>2</v>
       </c>
-      <c r="K30" s="7">
+      <c r="K31" s="7">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L30" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M30" s="16">
+      <c r="L31" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M31" s="15">
         <v>4.3280000000000003</v>
       </c>
-      <c r="N30" s="16">
+      <c r="N31" s="15">
         <f t="shared" si="2"/>
         <v>43.28</v>
       </c>
-      <c r="O30" s="9"/>
-    </row>
-    <row r="31" spans="1:15" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="1"/>
-      <c r="B31" s="11">
-        <f>ROW(B31) - ROW($B$2)</f>
-        <v>29</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="I31" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="J31" s="7">
-        <v>1</v>
-      </c>
-      <c r="K31" s="7">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L31" s="17" t="s">
-        <v>371</v>
-      </c>
-      <c r="M31" s="16">
-        <v>0.16750000000000001</v>
-      </c>
-      <c r="N31" s="16">
-        <f t="shared" si="2"/>
-        <v>0.83750000000000002</v>
-      </c>
-      <c r="O31" s="7"/>
-    </row>
-    <row r="32" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O31" s="9"/>
+    </row>
+    <row r="32" spans="1:15" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B32) - ROW($B$2)</f>
         <v>30</v>
       </c>
-      <c r="C32" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>375</v>
+      <c r="C32" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>125</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="G32" s="10" t="s">
-        <v>373</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>374</v>
+        <v>360</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>299</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="J32" s="9">
+        <v>355</v>
+      </c>
+      <c r="J32" s="7">
         <v>1</v>
       </c>
       <c r="K32" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L32" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M32" s="16">
-        <v>11.43</v>
-      </c>
-      <c r="N32" s="16">
-        <f t="shared" si="2"/>
-        <v>57.15</v>
-      </c>
-      <c r="O32" s="9"/>
-    </row>
-    <row r="33" spans="1:15" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L32" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="M32" s="15">
+        <v>0.16750000000000001</v>
+      </c>
+      <c r="N32" s="15">
+        <f t="shared" si="2"/>
+        <v>0.83750000000000002</v>
+      </c>
+      <c r="O32" s="7"/>
+    </row>
+    <row r="33" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="11">
-        <f>ROW(B33) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C33" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>129</v>
+      <c r="C33" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>372</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>303</v>
+        <v>360</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>371</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="J33" s="7">
+        <v>355</v>
+      </c>
+      <c r="J33" s="9">
         <v>1</v>
       </c>
       <c r="K33" s="7">
-        <v>12</v>
-      </c>
-      <c r="L33" s="17" t="s">
-        <v>371</v>
-      </c>
-      <c r="M33" s="16">
-        <v>6.8000000000000005E-2</v>
-      </c>
-      <c r="N33" s="16">
-        <f t="shared" si="2"/>
-        <v>0.81600000000000006</v>
-      </c>
-      <c r="O33" s="7"/>
-    </row>
-    <row r="34" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M33" s="15">
+        <v>11.43</v>
+      </c>
+      <c r="N33" s="15">
+        <f t="shared" si="2"/>
+        <v>57.15</v>
+      </c>
+      <c r="O33" s="9"/>
+    </row>
+    <row r="34" spans="1:15" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="11">
+        <f>ROW(B34) - ROW($B$2)</f>
+        <v>32</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="J34" s="7">
+        <v>1</v>
+      </c>
+      <c r="K34" s="7">
+        <v>12</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="M34" s="15">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="N34" s="15">
+        <f t="shared" si="2"/>
+        <v>0.81600000000000006</v>
+      </c>
+      <c r="O34" s="7"/>
+    </row>
+    <row r="35" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="1"/>
+      <c r="B35" s="11">
         <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="C34" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D34" s="9" t="s">
+      <c r="D35" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E34" s="10" t="s">
-        <v>376</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="G34" s="10" t="s">
-        <v>377</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="I34" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="J34" s="9">
+      <c r="E35" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="J35" s="9">
         <v>1</v>
       </c>
-      <c r="K34" s="7">
+      <c r="K35" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L34" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M34" s="16">
+      <c r="L35" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M35" s="15">
         <v>25.25</v>
       </c>
-      <c r="N34" s="16">
+      <c r="N35" s="15">
         <f t="shared" si="2"/>
         <v>126.25</v>
       </c>
-      <c r="O34" s="9"/>
-    </row>
-    <row r="35" spans="1:15" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="1"/>
-      <c r="B35" s="11">
-        <f>ROW(B35) - ROW($B$2)</f>
-        <v>33</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="I35" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="J35" s="7">
-        <v>4</v>
-      </c>
-      <c r="K35" s="7">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="L35" s="17" t="s">
-        <v>371</v>
-      </c>
-      <c r="M35" s="16">
-        <v>0.1754</v>
-      </c>
-      <c r="N35" s="16">
-        <f t="shared" si="2"/>
-        <v>3.508</v>
-      </c>
-      <c r="O35" s="7"/>
+      <c r="O35" s="9"/>
     </row>
     <row r="36" spans="1:15" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B36) - ROW($B$2)</f>
         <v>34</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D36" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>131</v>
+      <c r="D36" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>127</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="G36" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>302</v>
+        <v>360</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>299</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="J36" s="9">
+        <v>355</v>
+      </c>
+      <c r="J36" s="7">
         <v>4</v>
       </c>
       <c r="K36" s="7">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L36" s="17" t="s">
-        <v>371</v>
-      </c>
-      <c r="M36" s="16">
-        <v>0.29749999999999999</v>
-      </c>
-      <c r="N36" s="16">
-        <f t="shared" si="2"/>
-        <v>5.9499999999999993</v>
-      </c>
-      <c r="O36" s="9"/>
-    </row>
-    <row r="37" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L36" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="M36" s="15">
+        <v>0.1754</v>
+      </c>
+      <c r="N36" s="15">
+        <f t="shared" si="2"/>
+        <v>3.508</v>
+      </c>
+      <c r="O36" s="7"/>
+    </row>
+    <row r="37" spans="1:15" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="11">
-        <f>ROW(B37) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C37" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>132</v>
+      <c r="C37" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>128</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>300</v>
+        <v>360</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>299</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="J37" s="7">
-        <v>1</v>
+        <v>355</v>
+      </c>
+      <c r="J37" s="9">
+        <v>4</v>
       </c>
       <c r="K37" s="7">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L37" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M37" s="16">
-        <v>1.56</v>
-      </c>
-      <c r="N37" s="16">
-        <f t="shared" si="2"/>
-        <v>7.8000000000000007</v>
-      </c>
-      <c r="O37" s="7"/>
+        <v>20</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="M37" s="15">
+        <v>0.29749999999999999</v>
+      </c>
+      <c r="N37" s="15">
+        <f t="shared" si="2"/>
+        <v>5.9499999999999993</v>
+      </c>
+      <c r="O37" s="9"/>
     </row>
     <row r="38" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B38) - ROW($B$2)</f>
         <v>36</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D38" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>133</v>
+      <c r="D38" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>129</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="G38" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="H38" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="I38" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="J38" s="9">
+        <v>360</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="J38" s="7">
         <v>1</v>
       </c>
       <c r="K38" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L38" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M38" s="16">
-        <v>1.19</v>
-      </c>
-      <c r="N38" s="16">
-        <f t="shared" si="2"/>
-        <v>5.9499999999999993</v>
-      </c>
-      <c r="O38" s="9"/>
+      <c r="L38" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M38" s="15">
+        <v>1.56</v>
+      </c>
+      <c r="N38" s="15">
+        <f t="shared" si="2"/>
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="O38" s="7"/>
     </row>
     <row r="39" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="11">
-        <f>ROW(B39) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C39" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>134</v>
+      <c r="C39" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>130</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="G39" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="I39" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="J39" s="7">
+        <v>360</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="J39" s="9">
         <v>1</v>
       </c>
       <c r="K39" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L39" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M39" s="16">
-        <v>1.85</v>
-      </c>
-      <c r="N39" s="16">
-        <f t="shared" si="2"/>
-        <v>9.25</v>
-      </c>
-      <c r="O39" s="7"/>
-    </row>
-    <row r="40" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L39" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M39" s="15">
+        <v>1.19</v>
+      </c>
+      <c r="N39" s="15">
+        <f t="shared" si="2"/>
+        <v>5.9499999999999993</v>
+      </c>
+      <c r="O39" s="9"/>
+    </row>
+    <row r="40" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B40) - ROW($B$2)</f>
         <v>38</v>
       </c>
-      <c r="C40" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="E40" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="G40" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="H40" s="9" t="s">
-        <v>305</v>
+      <c r="C40" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>301</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="J40" s="9">
-        <v>4</v>
+        <v>355</v>
+      </c>
+      <c r="J40" s="7">
+        <v>1</v>
       </c>
       <c r="K40" s="7">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="L40" s="17" t="s">
-        <v>371</v>
-      </c>
-      <c r="M40" s="16">
-        <v>2.0799999999999999E-2</v>
-      </c>
-      <c r="N40" s="16">
-        <f t="shared" si="2"/>
-        <v>0.41599999999999998</v>
-      </c>
-      <c r="O40" s="9"/>
+        <v>5</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M40" s="15">
+        <v>1.85</v>
+      </c>
+      <c r="N40" s="15">
+        <f t="shared" si="2"/>
+        <v>9.25</v>
+      </c>
+      <c r="O40" s="7"/>
     </row>
     <row r="41" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="11">
-        <f>ROW(B41) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C41" s="12" t="s">
+      <c r="C41" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D41" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="G41" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="H41" s="7" t="s">
-        <v>305</v>
+      <c r="D41" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>302</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="J41" s="7">
-        <v>2</v>
+        <v>355</v>
+      </c>
+      <c r="J41" s="9">
+        <v>4</v>
       </c>
       <c r="K41" s="7">
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L41" s="17" t="s">
-        <v>371</v>
-      </c>
-      <c r="M41" s="16">
-        <v>2.1700000000000001E-2</v>
-      </c>
-      <c r="N41" s="16">
-        <f t="shared" si="2"/>
-        <v>0.434</v>
-      </c>
-      <c r="O41" s="7"/>
+      <c r="L41" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="M41" s="15">
+        <v>2.0799999999999999E-2</v>
+      </c>
+      <c r="N41" s="15">
+        <f t="shared" si="2"/>
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="O41" s="9"/>
     </row>
     <row r="42" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B42) - ROW($B$2)</f>
         <v>40</v>
       </c>
-      <c r="C42" s="13" t="s">
+      <c r="C42" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D42" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="E42" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="G42" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="H42" s="9" t="s">
-        <v>305</v>
+      <c r="D42" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>302</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="J42" s="9">
-        <v>1</v>
+        <v>355</v>
+      </c>
+      <c r="J42" s="7">
+        <v>2</v>
       </c>
       <c r="K42" s="7">
         <v>20</v>
       </c>
-      <c r="L42" s="17" t="s">
-        <v>371</v>
-      </c>
-      <c r="M42" s="16">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="N42" s="16">
-        <f t="shared" si="2"/>
-        <v>0.43999999999999995</v>
-      </c>
-      <c r="O42" s="9"/>
+      <c r="L42" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="M42" s="15">
+        <v>2.1700000000000001E-2</v>
+      </c>
+      <c r="N42" s="15">
+        <f t="shared" si="2"/>
+        <v>0.434</v>
+      </c>
+      <c r="O42" s="7"/>
     </row>
     <row r="43" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="11">
-        <f>ROW(B43) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="C43" s="12" t="s">
+      <c r="C43" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D43" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="G43" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="H43" s="7" t="s">
-        <v>305</v>
+      <c r="D43" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>302</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="J43" s="7">
+        <v>355</v>
+      </c>
+      <c r="J43" s="9">
         <v>1</v>
       </c>
       <c r="K43" s="7">
         <v>20</v>
       </c>
-      <c r="L43" s="17" t="s">
-        <v>371</v>
-      </c>
-      <c r="M43" s="16">
-        <v>3.1300000000000001E-2</v>
-      </c>
-      <c r="N43" s="16">
-        <f t="shared" si="2"/>
-        <v>0.626</v>
-      </c>
-      <c r="O43" s="7"/>
-    </row>
-    <row r="44" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L43" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="M43" s="15">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="N43" s="15">
+        <f t="shared" si="2"/>
+        <v>0.43999999999999995</v>
+      </c>
+      <c r="O43" s="9"/>
+    </row>
+    <row r="44" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B44) - ROW($B$2)</f>
         <v>42</v>
       </c>
-      <c r="C44" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E44" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="G44" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="H44" s="9" t="s">
-        <v>306</v>
+      <c r="C44" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>302</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="J44" s="9">
+        <v>355</v>
+      </c>
+      <c r="J44" s="7">
         <v>1</v>
       </c>
       <c r="K44" s="7">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L44" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M44" s="16">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="N44" s="16">
-        <f t="shared" si="2"/>
-        <v>5.45</v>
-      </c>
-      <c r="O44" s="9"/>
+        <v>20</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="M44" s="15">
+        <v>3.1300000000000001E-2</v>
+      </c>
+      <c r="N44" s="15">
+        <f t="shared" si="2"/>
+        <v>0.626</v>
+      </c>
+      <c r="O44" s="7"/>
     </row>
     <row r="45" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="11">
-        <f>ROW(B45) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="C45" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="G45" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>306</v>
+      <c r="C45" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>303</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="J45" s="7">
+        <v>355</v>
+      </c>
+      <c r="J45" s="9">
         <v>1</v>
       </c>
       <c r="K45" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L45" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M45" s="16">
+      <c r="L45" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M45" s="15">
         <v>1.0900000000000001</v>
       </c>
-      <c r="N45" s="16">
+      <c r="N45" s="15">
         <f t="shared" si="2"/>
         <v>5.45</v>
       </c>
-      <c r="O45" s="7"/>
-    </row>
-    <row r="46" spans="1:15" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O45" s="9"/>
+    </row>
+    <row r="46" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B46) - ROW($B$2)</f>
         <v>44</v>
       </c>
       <c r="C46" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D46" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="G46" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="H46" s="9" t="s">
-        <v>307</v>
+      <c r="D46" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>303</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="J46" s="9">
-        <v>2</v>
+        <v>355</v>
+      </c>
+      <c r="J46" s="7">
+        <v>1</v>
       </c>
       <c r="K46" s="7">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L46" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M46" s="16">
-        <v>0.2</v>
-      </c>
-      <c r="N46" s="16">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="O46" s="9"/>
-    </row>
-    <row r="47" spans="1:15" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M46" s="15">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="N46" s="15">
+        <f t="shared" si="2"/>
+        <v>5.45</v>
+      </c>
+      <c r="O46" s="7"/>
+    </row>
+    <row r="47" spans="1:15" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="11">
-        <f>ROW(B47) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="C47" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D47" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="G47" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>308</v>
+      <c r="D47" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E47" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>304</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="J47" s="7">
-        <v>1</v>
+        <v>355</v>
+      </c>
+      <c r="J47" s="9">
+        <v>2</v>
       </c>
       <c r="K47" s="7">
-        <v>20</v>
-      </c>
-      <c r="L47" s="17" t="s">
-        <v>371</v>
-      </c>
-      <c r="M47" s="16">
-        <v>3.3500000000000002E-2</v>
-      </c>
-      <c r="N47" s="16">
-        <f t="shared" si="2"/>
-        <v>0.67</v>
-      </c>
-      <c r="O47" s="7"/>
-    </row>
-    <row r="48" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M47" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="N47" s="15">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="O47" s="9"/>
+    </row>
+    <row r="48" spans="1:15" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B48) - ROW($B$2)</f>
         <v>46</v>
       </c>
-      <c r="C48" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="G48" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="H48" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="I48" s="10" t="s">
-        <v>332</v>
-      </c>
-      <c r="J48" s="9">
+      <c r="C48" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="J48" s="7">
         <v>1</v>
       </c>
       <c r="K48" s="7">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L48" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M48" s="16">
-        <v>0.15</v>
-      </c>
-      <c r="N48" s="16">
-        <f t="shared" si="2"/>
-        <v>0.75</v>
-      </c>
-      <c r="O48" s="9"/>
+        <v>20</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="M48" s="15">
+        <v>3.3500000000000002E-2</v>
+      </c>
+      <c r="N48" s="15">
+        <f t="shared" si="2"/>
+        <v>0.67</v>
+      </c>
+      <c r="O48" s="7"/>
     </row>
     <row r="49" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="11">
-        <f>ROW(B49) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="C49" s="12" t="s">
+      <c r="C49" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D49" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="G49" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="I49" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="J49" s="7">
+      <c r="D49" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="G49" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="I49" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="J49" s="9">
         <v>1</v>
       </c>
       <c r="K49" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L49" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M49" s="16">
-        <v>0.1</v>
-      </c>
-      <c r="N49" s="16">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
-      <c r="O49" s="7"/>
+      <c r="L49" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M49" s="15">
+        <v>0.15</v>
+      </c>
+      <c r="N49" s="15">
+        <f t="shared" si="2"/>
+        <v>0.75</v>
+      </c>
+      <c r="O49" s="9"/>
     </row>
     <row r="50" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B50) - ROW($B$2)</f>
         <v>48</v>
       </c>
-      <c r="C50" s="13" t="s">
+      <c r="C50" s="12" t="s">
         <v>17</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E50" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="G50" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="H50" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="I50" s="10" t="s">
-        <v>334</v>
-      </c>
-      <c r="J50" s="9">
-        <v>1</v>
+        <v>390</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="J50" s="7">
+        <v>2</v>
       </c>
       <c r="K50" s="7">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L50" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M50" s="16">
-        <v>0.15</v>
-      </c>
-      <c r="N50" s="16">
-        <f t="shared" si="2"/>
-        <v>0.75</v>
-      </c>
-      <c r="O50" s="9"/>
+        <v>10</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M50" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="N50" s="15">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O50" s="7"/>
     </row>
     <row r="51" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="11">
-        <f>ROW(B51) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="C51" s="12" t="s">
+      <c r="C51" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D51" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="G51" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="H51" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="I51" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="J51" s="7">
+      <c r="D51" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="G51" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="H51" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="I51" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="J51" s="9">
         <v>1</v>
       </c>
       <c r="K51" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L51" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M51" s="16">
-        <v>0.13</v>
-      </c>
-      <c r="N51" s="16">
-        <f t="shared" si="2"/>
-        <v>0.65</v>
-      </c>
-      <c r="O51" s="7"/>
+      <c r="L51" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M51" s="15">
+        <v>0.15</v>
+      </c>
+      <c r="N51" s="15">
+        <f t="shared" si="2"/>
+        <v>0.75</v>
+      </c>
+      <c r="O51" s="9"/>
     </row>
     <row r="52" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B52) - ROW($B$2)</f>
         <v>50</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="C52" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D52" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E52" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="F52" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="G52" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="H52" s="9" t="s">
-        <v>300</v>
-      </c>
-      <c r="I52" s="10" t="s">
-        <v>336</v>
-      </c>
-      <c r="J52" s="9">
+      <c r="D52" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="J52" s="7">
         <v>1</v>
       </c>
       <c r="K52" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L52" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M52" s="16">
-        <v>0.64</v>
-      </c>
-      <c r="N52" s="16">
-        <f t="shared" si="2"/>
-        <v>3.2</v>
-      </c>
-      <c r="O52" s="9"/>
+      <c r="L52" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M52" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="N52" s="15">
+        <f t="shared" si="2"/>
+        <v>0.65</v>
+      </c>
+      <c r="O52" s="7"/>
     </row>
     <row r="53" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="11">
-        <f>ROW(B53) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="C53" s="12" t="s">
+      <c r="C53" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D53" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="G53" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="H53" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="I53" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="J53" s="7">
+      <c r="D53" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="H53" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="I53" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="J53" s="9">
         <v>1</v>
       </c>
       <c r="K53" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L53" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M53" s="16">
-        <v>0.15</v>
-      </c>
-      <c r="N53" s="16">
-        <f t="shared" si="2"/>
-        <v>0.75</v>
-      </c>
-      <c r="O53" s="7"/>
+      <c r="L53" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M53" s="15">
+        <v>0.64</v>
+      </c>
+      <c r="N53" s="15">
+        <f t="shared" si="2"/>
+        <v>3.2</v>
+      </c>
+      <c r="O53" s="9"/>
     </row>
     <row r="54" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B54) - ROW($B$2)</f>
         <v>52</v>
       </c>
-      <c r="C54" s="13" t="s">
+      <c r="C54" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D54" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E54" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="F54" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="G54" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="H54" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="I54" s="10" t="s">
-        <v>338</v>
-      </c>
-      <c r="J54" s="9">
+      <c r="D54" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="H54" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="J54" s="7">
         <v>1</v>
       </c>
       <c r="K54" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L54" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M54" s="16">
+      <c r="L54" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M54" s="15">
         <v>0.15</v>
       </c>
-      <c r="N54" s="16">
+      <c r="N54" s="15">
         <f t="shared" si="2"/>
         <v>0.75</v>
       </c>
-      <c r="O54" s="9"/>
+      <c r="O54" s="7"/>
     </row>
     <row r="55" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="11">
-        <f>ROW(B55) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="C55" s="12" t="s">
+      <c r="C55" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D55" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="G55" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="H55" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="I55" s="8" t="s">
-        <v>339</v>
-      </c>
-      <c r="J55" s="7">
+      <c r="D55" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E55" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="I55" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="J55" s="9">
         <v>1</v>
       </c>
       <c r="K55" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L55" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M55" s="16">
+      <c r="L55" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M55" s="15">
         <v>0.15</v>
       </c>
-      <c r="N55" s="16">
+      <c r="N55" s="15">
         <f t="shared" si="2"/>
         <v>0.75</v>
       </c>
-      <c r="O55" s="7"/>
+      <c r="O55" s="9"/>
     </row>
     <row r="56" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B56) - ROW($B$2)</f>
         <v>54</v>
       </c>
-      <c r="C56" s="13" t="s">
+      <c r="C56" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D56" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E56" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="F56" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="G56" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="H56" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="I56" s="10" t="s">
-        <v>340</v>
-      </c>
-      <c r="J56" s="9">
+      <c r="D56" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="H56" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="J56" s="7">
         <v>1</v>
       </c>
       <c r="K56" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L56" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M56" s="16">
+      <c r="L56" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M56" s="15">
         <v>0.15</v>
       </c>
-      <c r="N56" s="16">
+      <c r="N56" s="15">
         <f t="shared" si="2"/>
         <v>0.75</v>
       </c>
-      <c r="O56" s="9"/>
+      <c r="O56" s="7"/>
     </row>
     <row r="57" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="11">
-        <f>ROW(B57) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>55</v>
       </c>
       <c r="C57" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D57" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="G57" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="H57" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="I57" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="J57" s="7">
+      <c r="D57" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="I57" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="J57" s="9">
         <v>1</v>
       </c>
       <c r="K57" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L57" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M57" s="16">
-        <v>0.1</v>
-      </c>
-      <c r="N57" s="16">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
-      <c r="O57" s="7"/>
+      <c r="L57" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M57" s="15">
+        <v>0.15</v>
+      </c>
+      <c r="N57" s="15">
+        <f t="shared" si="2"/>
+        <v>0.75</v>
+      </c>
+      <c r="O57" s="9"/>
     </row>
     <row r="58" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B58) - ROW($B$2)</f>
         <v>56</v>
       </c>
       <c r="C58" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D58" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E58" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="F58" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="G58" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="H58" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="I58" s="10" t="s">
-        <v>342</v>
-      </c>
-      <c r="J58" s="9">
-        <v>5</v>
+      <c r="D58" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="H58" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="I58" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="J58" s="7">
+        <v>1</v>
       </c>
       <c r="K58" s="7">
         <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="L58" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M58" s="16">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="N58" s="16">
-        <f t="shared" si="2"/>
-        <v>0.375</v>
-      </c>
-      <c r="O58" s="9"/>
+        <v>5</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M58" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="N58" s="15">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="O58" s="7"/>
     </row>
     <row r="59" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="11">
-        <f>ROW(B59) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="C59" s="12" t="s">
+      <c r="C59" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D59" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="F59" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="G59" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="H59" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="I59" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="J59" s="7">
-        <v>1</v>
+      <c r="D59" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E59" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="H59" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="I59" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="J59" s="9">
+        <v>5</v>
       </c>
       <c r="K59" s="7">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L59" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M59" s="16">
-        <v>0.1</v>
-      </c>
-      <c r="N59" s="16">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
-      <c r="O59" s="7"/>
+        <v>25</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M59" s="15">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N59" s="15">
+        <f t="shared" si="2"/>
+        <v>0.375</v>
+      </c>
+      <c r="O59" s="9"/>
     </row>
     <row r="60" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B60) - ROW($B$2)</f>
         <v>58</v>
       </c>
       <c r="C60" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D60" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="E60" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="F60" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="G60" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="H60" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="I60" s="10" t="s">
-        <v>344</v>
-      </c>
-      <c r="J60" s="9">
+      <c r="D60" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="H60" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="J60" s="7">
         <v>1</v>
       </c>
       <c r="K60" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L60" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M60" s="16">
+      <c r="L60" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M60" s="15">
         <v>0.1</v>
       </c>
-      <c r="N60" s="16">
+      <c r="N60" s="15">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="O60" s="9"/>
+      <c r="O60" s="7"/>
     </row>
     <row r="61" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="11">
-        <f>ROW(B61) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>59</v>
       </c>
       <c r="C61" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D61" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E61" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="G61" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="H61" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="I61" s="8" t="s">
-        <v>345</v>
-      </c>
-      <c r="J61" s="7">
-        <v>3</v>
+      <c r="D61" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="G61" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="H61" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="I61" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="J61" s="9">
+        <v>1</v>
       </c>
       <c r="K61" s="7">
         <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="L61" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M61" s="16">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="N61" s="16">
-        <f t="shared" si="2"/>
-        <v>0.22499999999999998</v>
-      </c>
-      <c r="O61" s="7"/>
+        <v>5</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M61" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="N61" s="15">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="O61" s="9"/>
     </row>
     <row r="62" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B62) - ROW($B$2)</f>
         <v>60</v>
       </c>
-      <c r="C62" s="13" t="s">
+      <c r="C62" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D62" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="E62" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="F62" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="G62" s="10" t="s">
-        <v>367</v>
-      </c>
-      <c r="H62" s="9" t="s">
-        <v>368</v>
-      </c>
-      <c r="I62" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="J62" s="9">
-        <v>1</v>
+      <c r="D62" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="H62" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="I62" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="J62" s="7">
+        <v>3</v>
       </c>
       <c r="K62" s="7">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L62" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M62" s="16">
-        <v>0.1</v>
-      </c>
-      <c r="N62" s="16">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
-      <c r="O62" s="9"/>
+        <v>15</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M62" s="15">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N62" s="15">
+        <f t="shared" si="2"/>
+        <v>0.22499999999999998</v>
+      </c>
+      <c r="O62" s="7"/>
     </row>
     <row r="63" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
@@ -4730,22 +4756,22 @@
         <v>17</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>270</v>
+        <v>364</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>292</v>
+        <v>365</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="J63" s="9">
         <v>1</v>
@@ -4754,13 +4780,13 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L63" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M63" s="16">
+      <c r="L63" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M63" s="15">
         <v>0.1</v>
       </c>
-      <c r="N63" s="16">
+      <c r="N63" s="15">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
@@ -4772,47 +4798,47 @@
         <f>ROW(B64) - ROW($B$2)</f>
         <v>62</v>
       </c>
-      <c r="C64" s="12" t="s">
+      <c r="C64" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D64" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="G64" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="H64" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="I64" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="J64" s="7">
-        <v>4</v>
+      <c r="D64" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="E64" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="G64" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="H64" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="I64" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="J64" s="9">
+        <v>3</v>
       </c>
       <c r="K64" s="7">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="L64" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M64" s="16">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="N64" s="16">
-        <f t="shared" si="2"/>
-        <v>0.3</v>
-      </c>
-      <c r="O64" s="7"/>
-    </row>
-    <row r="65" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <f>J64*5</f>
+        <v>15</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M64" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="N64" s="15">
+        <f>M64*K64</f>
+        <v>1.5</v>
+      </c>
+      <c r="O64" s="9"/>
+    </row>
+    <row r="65" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="11">
         <f t="shared" si="0"/>
@@ -4822,43 +4848,43 @@
         <v>17</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="J65" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K65" s="7">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L65" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M65" s="16">
-        <v>1.9E-2</v>
-      </c>
-      <c r="N65" s="16">
-        <f t="shared" si="2"/>
-        <v>0.19</v>
+        <v>5</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M65" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="N65" s="15">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="O65" s="9"/>
     </row>
-    <row r="66" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="11">
         <f>ROW(B66) - ROW($B$2)</f>
@@ -4867,44 +4893,44 @@
       <c r="C66" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D66" s="7" t="s">
-        <v>82</v>
+      <c r="D66" s="9" t="s">
+        <v>392</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I66" s="8" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="J66" s="7">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K66" s="7">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L66" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M66" s="16">
-        <v>0.1</v>
-      </c>
-      <c r="N66" s="16">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>30</v>
+      </c>
+      <c r="L66" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M66" s="15">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N66" s="15">
+        <f t="shared" si="2"/>
+        <v>0.44999999999999996</v>
       </c>
       <c r="O66" s="7"/>
     </row>
-    <row r="67" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="11">
         <f t="shared" si="0"/>
@@ -4914,43 +4940,43 @@
         <v>17</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="J67" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K67" s="7">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L67" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M67" s="16">
-        <v>0.1</v>
-      </c>
-      <c r="N67" s="16">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>10</v>
+      </c>
+      <c r="L67" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M67" s="15">
+        <v>1.9E-2</v>
+      </c>
+      <c r="N67" s="15">
+        <f t="shared" si="2"/>
+        <v>0.19</v>
       </c>
       <c r="O67" s="9"/>
     </row>
-    <row r="68" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
       <c r="B68" s="11">
         <f>ROW(B68) - ROW($B$2)</f>
@@ -4960,43 +4986,43 @@
         <v>17</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="H68" s="7" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I68" s="8" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="J68" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K68" s="7">
-        <f t="shared" ref="K68:K87" si="3">J68*5</f>
-        <v>10</v>
-      </c>
-      <c r="L68" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M68" s="16">
-        <v>9.4030000000000002E-2</v>
-      </c>
-      <c r="N68" s="16">
-        <f t="shared" si="2"/>
-        <v>0.94030000000000002</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="L68" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M68" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="N68" s="15">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="O68" s="7"/>
     </row>
-    <row r="69" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="11">
         <f t="shared" si="0"/>
@@ -5006,43 +5032,43 @@
         <v>17</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="F69" s="9" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="J69" s="9">
         <v>1</v>
       </c>
       <c r="K69" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L69" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M69" s="16">
+      <c r="L69" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M69" s="15">
         <v>0.1</v>
       </c>
-      <c r="N69" s="16">
-        <f t="shared" ref="N69:N87" si="4">M69*K69</f>
+      <c r="N69" s="15">
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="O69" s="9"/>
     </row>
-    <row r="70" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
       <c r="B70" s="11">
         <f>ROW(B70) - ROW($B$2)</f>
@@ -5052,299 +5078,299 @@
         <v>17</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F70" s="7" t="s">
         <v>208</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="H70" s="7" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="J70" s="7">
+        <v>2</v>
+      </c>
+      <c r="K70" s="7">
+        <f t="shared" ref="K70:K89" si="3">J70*5</f>
+        <v>10</v>
+      </c>
+      <c r="L70" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M70" s="15">
+        <v>9.4030000000000002E-2</v>
+      </c>
+      <c r="N70" s="15">
+        <f t="shared" si="2"/>
+        <v>0.94030000000000002</v>
+      </c>
+      <c r="O70" s="7"/>
+    </row>
+    <row r="71" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="1"/>
+      <c r="B71" s="11">
+        <f>ROW(B71) - ROW($B$2)</f>
+        <v>69</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="H71" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="I71" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="J71" s="7">
         <v>1</v>
       </c>
-      <c r="K70" s="7">
+      <c r="K71" s="7">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="L70" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M70" s="16">
+      <c r="L71" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M71" s="15">
         <v>0.1</v>
       </c>
-      <c r="N70" s="16">
-        <f t="shared" si="4"/>
+      <c r="N71" s="15">
+        <f t="shared" ref="N71:N89" si="4">M71*K71</f>
         <v>0.5</v>
       </c>
-      <c r="O70" s="7"/>
-    </row>
-    <row r="71" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="1"/>
-      <c r="B71" s="11">
+      <c r="O71" s="7"/>
+    </row>
+    <row r="72" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="1"/>
+      <c r="B72" s="11">
         <f t="shared" si="0"/>
-        <v>69</v>
-      </c>
-      <c r="C71" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C72" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D71" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="E71" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="F71" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="G71" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="I71" s="10" t="s">
-        <v>353</v>
-      </c>
-      <c r="J71" s="9">
+      <c r="D72" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="F72" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="G72" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="H72" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="I72" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="J72" s="9">
         <v>4</v>
       </c>
-      <c r="K71" s="7">
+      <c r="K72" s="7">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="L71" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M71" s="16">
+      <c r="L72" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M72" s="15">
         <v>1.9E-2</v>
       </c>
-      <c r="N71" s="16">
+      <c r="N72" s="15">
         <f t="shared" si="4"/>
         <v>0.38</v>
       </c>
-      <c r="O71" s="9"/>
-    </row>
-    <row r="72" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="1"/>
-      <c r="B72" s="11">
-        <f>ROW(B72) - ROW($B$2)</f>
-        <v>70</v>
-      </c>
-      <c r="C72" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D72" s="18" t="s">
-        <v>392</v>
-      </c>
-      <c r="E72" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="F72" s="18" t="s">
-        <v>363</v>
-      </c>
-      <c r="G72" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="H72" s="18" t="s">
-        <v>358</v>
-      </c>
-      <c r="I72" s="19" t="s">
-        <v>358</v>
-      </c>
-      <c r="J72" s="18">
-        <v>1</v>
-      </c>
-      <c r="K72" s="18">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="L72" s="20" t="s">
-        <v>358</v>
-      </c>
-      <c r="M72" s="21" t="s">
-        <v>358</v>
-      </c>
-      <c r="N72" s="21" t="s">
-        <v>358</v>
-      </c>
-      <c r="O72" s="18" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="73" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O72" s="9"/>
+    </row>
+    <row r="73" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="11">
         <f t="shared" si="0"/>
         <v>71</v>
       </c>
-      <c r="C73" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D73" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="E73" s="10" t="s">
-        <v>168</v>
+      <c r="C73" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>400</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="G73" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>309</v>
+        <v>205</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="H73" s="7" t="s">
+        <v>289</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="J73" s="9">
+        <v>401</v>
+      </c>
+      <c r="J73" s="7">
         <v>2</v>
       </c>
       <c r="K73" s="7">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="L73" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M73" s="16">
-        <v>0.98299999999999998</v>
-      </c>
-      <c r="N73" s="16">
+      <c r="L73" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M73" s="15">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="N73" s="15">
         <f t="shared" si="4"/>
-        <v>9.83</v>
-      </c>
-      <c r="O73" s="9"/>
-    </row>
-    <row r="74" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.10999999999999999</v>
+      </c>
+      <c r="O73" s="7"/>
+    </row>
+    <row r="74" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="11">
         <f>ROW(B74) - ROW($B$2)</f>
         <v>72</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="E74" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="F74" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="G74" s="8">
-        <v>760390015</v>
-      </c>
-      <c r="H74" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="I74" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="J74" s="7">
-        <v>1</v>
-      </c>
-      <c r="K74" s="7">
+        <v>18</v>
+      </c>
+      <c r="D74" s="17" t="s">
+        <v>394</v>
+      </c>
+      <c r="E74" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="F74" s="17" t="s">
+        <v>360</v>
+      </c>
+      <c r="G74" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="H74" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="I74" s="18" t="s">
+        <v>355</v>
+      </c>
+      <c r="J74" s="17">
+        <v>2</v>
+      </c>
+      <c r="K74" s="17">
         <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="L74" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M74" s="16">
-        <v>1.9</v>
-      </c>
-      <c r="N74" s="16">
-        <f t="shared" si="4"/>
-        <v>9.5</v>
-      </c>
-      <c r="O74" s="7"/>
-    </row>
-    <row r="75" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="L74" s="19" t="s">
+        <v>355</v>
+      </c>
+      <c r="M74" s="20" t="s">
+        <v>355</v>
+      </c>
+      <c r="N74" s="20" t="s">
+        <v>355</v>
+      </c>
+      <c r="O74" s="17" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="11">
         <f t="shared" si="0"/>
         <v>73</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F75" s="9" t="s">
-        <v>214</v>
+        <v>165</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>360</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>279</v>
+        <v>210</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="J75" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K75" s="7">
         <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="L75" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M75" s="16">
-        <v>6.11</v>
-      </c>
-      <c r="N75" s="16">
+        <v>10</v>
+      </c>
+      <c r="L75" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M75" s="15">
+        <v>0.98299999999999998</v>
+      </c>
+      <c r="N75" s="15">
         <f t="shared" si="4"/>
-        <v>30.55</v>
+        <v>9.83</v>
       </c>
       <c r="O75" s="9"/>
     </row>
-    <row r="76" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="11">
         <f>ROW(B76) - ROW($B$2)</f>
         <v>74</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="G76" s="8" t="s">
-        <v>280</v>
+        <v>360</v>
+      </c>
+      <c r="G76" s="8">
+        <v>760390015</v>
       </c>
       <c r="H76" s="7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I76" s="8" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="J76" s="7">
         <v>1</v>
@@ -5353,19 +5379,19 @@
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="L76" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M76" s="16">
-        <v>2.41</v>
-      </c>
-      <c r="N76" s="16">
+      <c r="L76" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M76" s="15">
+        <v>1.9</v>
+      </c>
+      <c r="N76" s="15">
         <f t="shared" si="4"/>
-        <v>12.05</v>
+        <v>9.5</v>
       </c>
       <c r="O76" s="7"/>
     </row>
-    <row r="77" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="11">
         <f t="shared" si="0"/>
@@ -5375,22 +5401,22 @@
         <v>21</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="J77" s="9">
         <v>1</v>
@@ -5399,19 +5425,19 @@
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="L77" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M77" s="16">
-        <v>1.43</v>
-      </c>
-      <c r="N77" s="16">
+      <c r="L77" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M77" s="15">
+        <v>6.11</v>
+      </c>
+      <c r="N77" s="15">
         <f t="shared" si="4"/>
-        <v>7.1499999999999995</v>
+        <v>30.55</v>
       </c>
       <c r="O77" s="9"/>
     </row>
-    <row r="78" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="11">
         <f>ROW(B78) - ROW($B$2)</f>
@@ -5421,22 +5447,22 @@
         <v>21</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="H78" s="7" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I78" s="8" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="J78" s="7">
         <v>1</v>
@@ -5445,19 +5471,19 @@
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="L78" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M78" s="16">
-        <v>2.27</v>
-      </c>
-      <c r="N78" s="16">
+      <c r="L78" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M78" s="15">
+        <v>2.41</v>
+      </c>
+      <c r="N78" s="15">
         <f t="shared" si="4"/>
-        <v>11.35</v>
+        <v>12.05</v>
       </c>
       <c r="O78" s="7"/>
     </row>
-    <row r="79" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="11">
         <f t="shared" si="0"/>
@@ -5467,22 +5493,22 @@
         <v>21</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="F79" s="9" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="J79" s="9">
         <v>1</v>
@@ -5491,44 +5517,44 @@
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="L79" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M79" s="16">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="N79" s="16">
+      <c r="L79" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M79" s="15">
+        <v>1.43</v>
+      </c>
+      <c r="N79" s="15">
         <f t="shared" si="4"/>
-        <v>5.8</v>
+        <v>7.1499999999999995</v>
       </c>
       <c r="O79" s="9"/>
     </row>
-    <row r="80" spans="1:19" s="23" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="22"/>
+    <row r="80" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="1"/>
       <c r="B80" s="11">
         <f>ROW(B80) - ROW($B$2)</f>
         <v>78</v>
       </c>
-      <c r="C80" s="13" t="s">
+      <c r="C80" s="12" t="s">
         <v>21</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="H80" s="7" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="I80" s="8" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="J80" s="7">
         <v>1</v>
@@ -5537,23 +5563,19 @@
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="L80" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M80" s="16">
-        <v>4.66</v>
-      </c>
-      <c r="N80" s="16">
+      <c r="L80" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M80" s="15">
+        <v>2.27</v>
+      </c>
+      <c r="N80" s="15">
         <f t="shared" si="4"/>
-        <v>23.3</v>
+        <v>11.35</v>
       </c>
       <c r="O80" s="7"/>
-      <c r="P80"/>
-      <c r="Q80"/>
-      <c r="R80"/>
-      <c r="S80"/>
-    </row>
-    <row r="81" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="81" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="11">
         <f t="shared" si="0"/>
@@ -5563,22 +5585,22 @@
         <v>21</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F81" s="9" t="s">
-        <v>363</v>
+        <v>214</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>219</v>
+        <v>280</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="J81" s="9">
         <v>1</v>
@@ -5587,19 +5609,19 @@
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="L81" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M81" s="16">
-        <v>3</v>
-      </c>
-      <c r="N81" s="16">
+      <c r="L81" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M81" s="15">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="N81" s="15">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>5.8</v>
       </c>
       <c r="O81" s="9"/>
     </row>
-    <row r="82" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:20" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="11">
         <f>ROW(B82) - ROW($B$2)</f>
@@ -5609,22 +5631,22 @@
         <v>21</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="F82" s="9" t="s">
-        <v>363</v>
+        <v>172</v>
+      </c>
+      <c r="F82" s="7" t="s">
+        <v>215</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>220</v>
+        <v>281</v>
       </c>
       <c r="H82" s="7" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="I82" s="8" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="J82" s="7">
         <v>1</v>
@@ -5633,20 +5655,20 @@
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="L82" s="17" t="s">
-        <v>371</v>
-      </c>
-      <c r="M82" s="16">
-        <v>2.6663999999999999</v>
-      </c>
-      <c r="N82" s="16">
+      <c r="L82" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M82" s="15">
+        <v>4.66</v>
+      </c>
+      <c r="N82" s="15">
         <f t="shared" si="4"/>
-        <v>13.331999999999999</v>
+        <v>23.3</v>
       </c>
       <c r="O82" s="7"/>
     </row>
-    <row r="83" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="1"/>
+    <row r="83" spans="1:20" s="22" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="21"/>
       <c r="B83" s="11">
         <f t="shared" si="0"/>
         <v>81</v>
@@ -5655,22 +5677,22 @@
         <v>21</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F83" s="9" t="s">
-        <v>221</v>
+        <v>360</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>285</v>
+        <v>216</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="J83" s="9">
         <v>1</v>
@@ -5679,65 +5701,70 @@
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="L83" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M83" s="16">
-        <v>4.51</v>
-      </c>
-      <c r="N83" s="16">
+      <c r="L83" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M83" s="15">
+        <v>3</v>
+      </c>
+      <c r="N83" s="15">
         <f t="shared" si="4"/>
-        <v>22.549999999999997</v>
+        <v>15</v>
       </c>
       <c r="O83" s="9"/>
-    </row>
-    <row r="84" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P83"/>
+      <c r="Q83"/>
+      <c r="R83"/>
+      <c r="S83"/>
+      <c r="T83"/>
+    </row>
+    <row r="84" spans="1:20" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="11">
         <f>ROW(B84) - ROW($B$2)</f>
         <v>82</v>
       </c>
-      <c r="C84" s="12" t="s">
+      <c r="C84" s="13" t="s">
         <v>21</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="F84" s="7" t="s">
-        <v>222</v>
+        <v>174</v>
+      </c>
+      <c r="F84" s="9" t="s">
+        <v>360</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>286</v>
+        <v>217</v>
       </c>
       <c r="H84" s="7" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="I84" s="8" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="J84" s="7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K84" s="7">
         <f t="shared" si="3"/>
-        <v>20</v>
-      </c>
-      <c r="L84" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M84" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="N84" s="16">
+        <v>5</v>
+      </c>
+      <c r="L84" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="M84" s="15">
+        <v>2.6663999999999999</v>
+      </c>
+      <c r="N84" s="15">
         <f t="shared" si="4"/>
-        <v>13.600000000000001</v>
+        <v>13.331999999999999</v>
       </c>
       <c r="O84" s="7"/>
     </row>
-    <row r="85" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="11">
         <f t="shared" si="0"/>
@@ -5747,43 +5774,43 @@
         <v>21</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F85" s="9" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="J85" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K85" s="7">
         <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="L85" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M85" s="16">
-        <v>5.2880000000000003</v>
-      </c>
-      <c r="N85" s="16">
+        <v>5</v>
+      </c>
+      <c r="L85" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M85" s="15">
+        <v>4.51</v>
+      </c>
+      <c r="N85" s="15">
         <f t="shared" si="4"/>
-        <v>52.88</v>
+        <v>22.549999999999997</v>
       </c>
       <c r="O85" s="9"/>
     </row>
-    <row r="86" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="11">
         <f>ROW(B86) - ROW($B$2)</f>
@@ -5793,137 +5820,232 @@
         <v>21</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="H86" s="7" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I86" s="8" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="J86" s="7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K86" s="7">
         <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="L86" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="M86" s="16">
-        <v>0.95</v>
-      </c>
-      <c r="N86" s="16">
+        <v>20</v>
+      </c>
+      <c r="L86" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M86" s="15">
+        <v>0.68</v>
+      </c>
+      <c r="N86" s="15">
         <f t="shared" si="4"/>
-        <v>4.75</v>
+        <v>13.600000000000001</v>
       </c>
       <c r="O86" s="7"/>
     </row>
-    <row r="87" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="11">
-        <f>ROW(B87) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>85</v>
       </c>
-      <c r="C87" s="32" t="s">
-        <v>379</v>
-      </c>
-      <c r="D87" s="33" t="s">
-        <v>358</v>
-      </c>
-      <c r="E87" s="34" t="s">
-        <v>380</v>
-      </c>
-      <c r="F87" s="33" t="s">
-        <v>358</v>
-      </c>
-      <c r="G87" s="34" t="s">
-        <v>381</v>
-      </c>
-      <c r="H87" s="33" t="s">
-        <v>382</v>
-      </c>
-      <c r="I87" s="34" t="s">
-        <v>358</v>
-      </c>
-      <c r="J87" s="33">
+      <c r="C87" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="G87" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="H87" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="I87" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="J87" s="9">
         <v>2</v>
       </c>
       <c r="K87" s="7">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="L87" s="35" t="s">
-        <v>359</v>
-      </c>
-      <c r="M87" s="36">
+      <c r="L87" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M87" s="15">
+        <v>5.2880000000000003</v>
+      </c>
+      <c r="N87" s="15">
+        <f t="shared" si="4"/>
+        <v>52.88</v>
+      </c>
+      <c r="O87" s="9"/>
+    </row>
+    <row r="88" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="1"/>
+      <c r="B88" s="11">
+        <f>ROW(B88) - ROW($B$2)</f>
+        <v>86</v>
+      </c>
+      <c r="C88" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="G88" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="H88" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="I88" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="J88" s="7">
+        <v>1</v>
+      </c>
+      <c r="K88" s="7">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="L88" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M88" s="15">
+        <v>0.95</v>
+      </c>
+      <c r="N88" s="15">
+        <f t="shared" si="4"/>
+        <v>4.75</v>
+      </c>
+      <c r="O88" s="7"/>
+    </row>
+    <row r="89" spans="1:20" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="1"/>
+      <c r="B89" s="11">
+        <f>ROW(B89) - ROW($B$2)</f>
+        <v>87</v>
+      </c>
+      <c r="C89" s="25" t="s">
+        <v>376</v>
+      </c>
+      <c r="D89" s="26" t="s">
+        <v>355</v>
+      </c>
+      <c r="E89" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="F89" s="26" t="s">
+        <v>355</v>
+      </c>
+      <c r="G89" s="27" t="s">
+        <v>378</v>
+      </c>
+      <c r="H89" s="26" t="s">
+        <v>379</v>
+      </c>
+      <c r="I89" s="27" t="s">
+        <v>355</v>
+      </c>
+      <c r="J89" s="26">
+        <v>2</v>
+      </c>
+      <c r="K89" s="7">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="L89" s="28" t="s">
+        <v>356</v>
+      </c>
+      <c r="M89" s="29">
         <v>0.35</v>
       </c>
-      <c r="N87" s="36">
+      <c r="N89" s="29">
         <f t="shared" si="4"/>
         <v>3.5</v>
       </c>
-      <c r="O87" s="33"/>
-    </row>
-    <row r="88" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="1"/>
-      <c r="B88" s="1"/>
-      <c r="C88" s="1"/>
-      <c r="D88" s="1"/>
-      <c r="E88" s="1"/>
-      <c r="F88" s="1"/>
-      <c r="G88" s="1"/>
-      <c r="H88" s="1"/>
-      <c r="I88" s="1"/>
-      <c r="J88" s="1"/>
-      <c r="K88" s="28" t="s">
-        <v>372</v>
-      </c>
-      <c r="L88" s="29"/>
-      <c r="M88" s="30"/>
-      <c r="N88" s="31">
-        <f>SUM(N10:N87)</f>
-        <v>597.84579999999994</v>
-      </c>
-      <c r="O88" s="1"/>
-    </row>
-    <row r="89" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="1"/>
-      <c r="B89" s="1"/>
-      <c r="C89" s="1"/>
-      <c r="D89" s="1"/>
-      <c r="E89" s="1"/>
-      <c r="F89" s="1"/>
-      <c r="G89" s="1"/>
-      <c r="H89" s="1"/>
-      <c r="I89" s="1"/>
-      <c r="J89" s="1"/>
-      <c r="K89" s="25" t="s">
-        <v>370</v>
-      </c>
-      <c r="L89" s="26"/>
-      <c r="M89" s="27"/>
-      <c r="N89" s="24">
-        <f>N88/5</f>
-        <v>119.56915999999998</v>
-      </c>
-      <c r="O89" s="1"/>
+      <c r="O89" s="26"/>
+    </row>
+    <row r="90" spans="1:20" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="1"/>
+      <c r="B90" s="1"/>
+      <c r="C90" s="1"/>
+      <c r="D90" s="1"/>
+      <c r="E90" s="1"/>
+      <c r="F90" s="1"/>
+      <c r="G90" s="1"/>
+      <c r="H90" s="1"/>
+      <c r="I90" s="1"/>
+      <c r="J90" s="1"/>
+      <c r="K90" s="31" t="s">
+        <v>369</v>
+      </c>
+      <c r="L90" s="32"/>
+      <c r="M90" s="33"/>
+      <c r="N90" s="24">
+        <f>SUM(N10:N89)</f>
+        <v>601.46579999999994</v>
+      </c>
+      <c r="O90" s="1"/>
+    </row>
+    <row r="91" spans="1:20" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="1"/>
+      <c r="B91" s="1"/>
+      <c r="C91" s="1"/>
+      <c r="D91" s="1"/>
+      <c r="E91" s="1"/>
+      <c r="F91" s="1"/>
+      <c r="G91" s="1"/>
+      <c r="H91" s="1"/>
+      <c r="I91" s="1"/>
+      <c r="J91" s="1"/>
+      <c r="K91" s="34" t="s">
+        <v>367</v>
+      </c>
+      <c r="L91" s="35"/>
+      <c r="M91" s="36"/>
+      <c r="N91" s="23">
+        <f>N90/5</f>
+        <v>120.29315999999999</v>
+      </c>
+      <c r="O91" s="1"/>
+    </row>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A92" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="I1:O1"/>
-    <mergeCell ref="K88:M88"/>
-    <mergeCell ref="K89:M89"/>
+    <mergeCell ref="K90:M90"/>
+    <mergeCell ref="K91:M91"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="L3" r:id="rId1"/>
@@ -5950,68 +6072,70 @@
     <hyperlink ref="L25" r:id="rId22"/>
     <hyperlink ref="L27" r:id="rId23"/>
     <hyperlink ref="L28" r:id="rId24"/>
-    <hyperlink ref="L30" r:id="rId25"/>
-    <hyperlink ref="L37" r:id="rId26"/>
-    <hyperlink ref="L38" r:id="rId27"/>
-    <hyperlink ref="L39" r:id="rId28"/>
-    <hyperlink ref="L44" r:id="rId29"/>
-    <hyperlink ref="L45" r:id="rId30"/>
-    <hyperlink ref="L46" r:id="rId31"/>
-    <hyperlink ref="L48" r:id="rId32"/>
-    <hyperlink ref="L49" r:id="rId33"/>
-    <hyperlink ref="L50" r:id="rId34"/>
-    <hyperlink ref="L51" r:id="rId35"/>
-    <hyperlink ref="L52" r:id="rId36"/>
-    <hyperlink ref="L53" r:id="rId37"/>
-    <hyperlink ref="L54" r:id="rId38"/>
-    <hyperlink ref="L55" r:id="rId39"/>
-    <hyperlink ref="L56" r:id="rId40"/>
-    <hyperlink ref="L57" r:id="rId41"/>
-    <hyperlink ref="L58" r:id="rId42"/>
-    <hyperlink ref="L59" r:id="rId43"/>
-    <hyperlink ref="L60" r:id="rId44"/>
-    <hyperlink ref="L61" r:id="rId45"/>
-    <hyperlink ref="L62" r:id="rId46"/>
-    <hyperlink ref="L63" r:id="rId47"/>
-    <hyperlink ref="L64" r:id="rId48"/>
-    <hyperlink ref="L65" r:id="rId49"/>
-    <hyperlink ref="L66" r:id="rId50"/>
-    <hyperlink ref="L67" r:id="rId51"/>
-    <hyperlink ref="L68" r:id="rId52"/>
-    <hyperlink ref="L69" r:id="rId53"/>
-    <hyperlink ref="L70" r:id="rId54"/>
-    <hyperlink ref="L71" r:id="rId55"/>
-    <hyperlink ref="L73" r:id="rId56"/>
-    <hyperlink ref="L74" r:id="rId57"/>
-    <hyperlink ref="L75" r:id="rId58"/>
-    <hyperlink ref="L76" r:id="rId59"/>
-    <hyperlink ref="L77" r:id="rId60"/>
-    <hyperlink ref="L78" r:id="rId61"/>
-    <hyperlink ref="L79" r:id="rId62"/>
-    <hyperlink ref="L80" r:id="rId63"/>
-    <hyperlink ref="L81" r:id="rId64"/>
-    <hyperlink ref="L83" r:id="rId65"/>
-    <hyperlink ref="L84" r:id="rId66"/>
-    <hyperlink ref="L85" r:id="rId67"/>
-    <hyperlink ref="L86" r:id="rId68"/>
+    <hyperlink ref="L31" r:id="rId25"/>
+    <hyperlink ref="L38" r:id="rId26"/>
+    <hyperlink ref="L39" r:id="rId27"/>
+    <hyperlink ref="L40" r:id="rId28"/>
+    <hyperlink ref="L45" r:id="rId29"/>
+    <hyperlink ref="L46" r:id="rId30"/>
+    <hyperlink ref="L47" r:id="rId31"/>
+    <hyperlink ref="L49" r:id="rId32"/>
+    <hyperlink ref="L50" r:id="rId33"/>
+    <hyperlink ref="L51" r:id="rId34"/>
+    <hyperlink ref="L52" r:id="rId35"/>
+    <hyperlink ref="L53" r:id="rId36"/>
+    <hyperlink ref="L54" r:id="rId37"/>
+    <hyperlink ref="L55" r:id="rId38"/>
+    <hyperlink ref="L56" r:id="rId39"/>
+    <hyperlink ref="L57" r:id="rId40"/>
+    <hyperlink ref="L58" r:id="rId41"/>
+    <hyperlink ref="L59" r:id="rId42"/>
+    <hyperlink ref="L60" r:id="rId43"/>
+    <hyperlink ref="L61" r:id="rId44"/>
+    <hyperlink ref="L62" r:id="rId45"/>
+    <hyperlink ref="L63" r:id="rId46"/>
+    <hyperlink ref="L65" r:id="rId47"/>
+    <hyperlink ref="L66" r:id="rId48"/>
+    <hyperlink ref="L67" r:id="rId49"/>
+    <hyperlink ref="L68" r:id="rId50"/>
+    <hyperlink ref="L69" r:id="rId51"/>
+    <hyperlink ref="L70" r:id="rId52"/>
+    <hyperlink ref="L64" r:id="rId53"/>
+    <hyperlink ref="L71" r:id="rId54"/>
+    <hyperlink ref="L72" r:id="rId55"/>
+    <hyperlink ref="L75" r:id="rId56"/>
+    <hyperlink ref="L76" r:id="rId57"/>
+    <hyperlink ref="L77" r:id="rId58"/>
+    <hyperlink ref="L78" r:id="rId59"/>
+    <hyperlink ref="L79" r:id="rId60"/>
+    <hyperlink ref="L80" r:id="rId61"/>
+    <hyperlink ref="L81" r:id="rId62"/>
+    <hyperlink ref="L82" r:id="rId63"/>
+    <hyperlink ref="L83" r:id="rId64"/>
+    <hyperlink ref="L85" r:id="rId65"/>
+    <hyperlink ref="L86" r:id="rId66"/>
+    <hyperlink ref="L87" r:id="rId67"/>
+    <hyperlink ref="L88" r:id="rId68"/>
     <hyperlink ref="L26" r:id="rId69"/>
-    <hyperlink ref="L31" r:id="rId70"/>
-    <hyperlink ref="L33" r:id="rId71"/>
-    <hyperlink ref="L35" r:id="rId72"/>
-    <hyperlink ref="L36" r:id="rId73"/>
-    <hyperlink ref="L40" r:id="rId74"/>
-    <hyperlink ref="L41" r:id="rId75"/>
-    <hyperlink ref="L42" r:id="rId76"/>
-    <hyperlink ref="L43" r:id="rId77"/>
-    <hyperlink ref="L47" r:id="rId78"/>
-    <hyperlink ref="L82" r:id="rId79"/>
-    <hyperlink ref="L32" r:id="rId80"/>
-    <hyperlink ref="L34" r:id="rId81"/>
-    <hyperlink ref="L87" r:id="rId82"/>
+    <hyperlink ref="L32" r:id="rId70"/>
+    <hyperlink ref="L34" r:id="rId71"/>
+    <hyperlink ref="L36" r:id="rId72"/>
+    <hyperlink ref="L37" r:id="rId73"/>
+    <hyperlink ref="L41" r:id="rId74"/>
+    <hyperlink ref="L42" r:id="rId75"/>
+    <hyperlink ref="L43" r:id="rId76"/>
+    <hyperlink ref="L44" r:id="rId77"/>
+    <hyperlink ref="L48" r:id="rId78"/>
+    <hyperlink ref="L84" r:id="rId79"/>
+    <hyperlink ref="L33" r:id="rId80"/>
+    <hyperlink ref="L35" r:id="rId81"/>
+    <hyperlink ref="L89" r:id="rId82"/>
     <hyperlink ref="L19" r:id="rId83"/>
     <hyperlink ref="L29" r:id="rId84"/>
+    <hyperlink ref="L30" r:id="rId85"/>
+    <hyperlink ref="L73" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId85"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId87"/>
 </worksheet>
 </file>
--- a/Design-Files/FMM-v1.0/BOM/Client-BOM-FMM-v1.0.xlsx
+++ b/Design-Files/FMM-v1.0/BOM/Client-BOM-FMM-v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="404">
   <si>
     <t>#</t>
   </si>
@@ -90,21 +90,12 @@
     <t>Designator</t>
   </si>
   <si>
-    <t>C1, C24, C32, C45, C48</t>
-  </si>
-  <si>
-    <t>C2, C5, C14, C15, C18, C19, C22, C27, C29, C31, C34, C36, C37, C38, C39, C46, C49, C50, C51, C52, C53, C54, C55</t>
-  </si>
-  <si>
     <t>C3, C4</t>
   </si>
   <si>
     <t>C6, C7</t>
   </si>
   <si>
-    <t>C8, C9</t>
-  </si>
-  <si>
     <t>C10</t>
   </si>
   <si>
@@ -174,9 +165,6 @@
     <t>J5</t>
   </si>
   <si>
-    <t>J6, J7, J8, J9</t>
-  </si>
-  <si>
     <t>J10, J11, J12, J13</t>
   </si>
   <si>
@@ -210,9 +198,6 @@
     <t>Q3, Q4</t>
   </si>
   <si>
-    <t>Q5</t>
-  </si>
-  <si>
     <t>R1</t>
   </si>
   <si>
@@ -249,9 +234,6 @@
     <t>R13</t>
   </si>
   <si>
-    <t>R14, R26, R28</t>
-  </si>
-  <si>
     <t>R15</t>
   </si>
   <si>
@@ -270,9 +252,6 @@
     <t>R29, R31</t>
   </si>
   <si>
-    <t>R32</t>
-  </si>
-  <si>
     <t>R33, R34, R35, R36</t>
   </si>
   <si>
@@ -396,18 +375,9 @@
     <t>FUSE HOLDER BLADE 80V PCB</t>
   </si>
   <si>
-    <t>1x2P 10A -40℃~+105℃ 300V Red 16~26 Straight 3.81mm 0.5~1 1 2 Plugin,P=3.81mm Screw terminal ROHS</t>
-  </si>
-  <si>
     <t>1x6P SH 1 1mm 6 SMD,P=1mm Wire To Board / Wire To Wire Connector ROHS</t>
   </si>
   <si>
-    <t>1x2P 10A -40℃~+105℃ 300V Black 16~26 Straight 3.81mm 0.5~1 1 2 Plugin,P=3.81mm Screw terminal ROHS</t>
-  </si>
-  <si>
-    <t>1x4P 10A -40℃~+105℃ 300V Green 16~26 Straight 3.81mm 0.5~1 1 4 Plugin,P=3.81mm Screw terminal ROHS</t>
-  </si>
-  <si>
     <t>FIXED IND 8.2UH 10.5A 15.5 MOHM</t>
   </si>
   <si>
@@ -438,9 +408,6 @@
     <t>25V 300mW 120@100mA,1V 1.5A NPN SOT-23 Bipolar Transistors - BJT ROHS</t>
   </si>
   <si>
-    <t>40V 100mW 100@10mA,1V 200mA 300MHz 300mV@50mA,5mA NPN -55℃~+150℃@(Tj) SOT-723 Bipolar Transistors - BJT ROHS</t>
-  </si>
-  <si>
     <t>RES SMD 34.8KOHM 0.1% 1/16W 0402</t>
   </si>
   <si>
@@ -507,9 +474,6 @@
     <t>RES 4.7K OHM 1% 1/16W 0402</t>
   </si>
   <si>
-    <t>RES 47K OHM 1% 1/16W 0402</t>
-  </si>
-  <si>
     <t>RES 120 OHM 1% 1/10W 0603</t>
   </si>
   <si>
@@ -606,15 +570,6 @@
     <t>178.6165.0002</t>
   </si>
   <si>
-    <t>DB125-3.81-2P-RD-S</t>
-  </si>
-  <si>
-    <t>DB125-3.81-2P-BK-S</t>
-  </si>
-  <si>
-    <t>DB125-3.81-4P-GN-S</t>
-  </si>
-  <si>
     <t>SRP1265A-8R2M</t>
   </si>
   <si>
@@ -633,9 +588,6 @@
     <t>8-VSON-CLIP (3.3x3.3)</t>
   </si>
   <si>
-    <t>SOT-723</t>
-  </si>
-  <si>
     <t>Res-0402</t>
   </si>
   <si>
@@ -777,9 +729,6 @@
     <t>SS8050-G</t>
   </si>
   <si>
-    <t>MMBT3904M</t>
-  </si>
-  <si>
     <t>RT0402BRD0734K8L</t>
   </si>
   <si>
@@ -843,9 +792,6 @@
     <t>RC0402FR-074K7L</t>
   </si>
   <si>
-    <t>RC0402FR-0747KL</t>
-  </si>
-  <si>
     <t>RC0603FR-07120RL</t>
   </si>
   <si>
@@ -936,9 +882,6 @@
     <t>Jiangsu Changjing Electronics Technology</t>
   </si>
   <si>
-    <t>TECH PUBLIC</t>
-  </si>
-  <si>
     <t>Omron</t>
   </si>
   <si>
@@ -1131,15 +1074,6 @@
     <t xml:space="preserve">5 Boards Component Cost </t>
   </si>
   <si>
-    <t>MUSBRA111R5</t>
-  </si>
-  <si>
-    <t>Amphenol ICC (Commercial Products)</t>
-  </si>
-  <si>
-    <t>CONN RCPT USB2.0 TYPEA 4P PCB RA</t>
-  </si>
-  <si>
     <t>M12 RA M PNL REAR A 5P PCB SHLD</t>
   </si>
   <si>
@@ -1161,51 +1095,18 @@
     <t>Littelfuse Inc.</t>
   </si>
   <si>
-    <t>CC1206KKX7RCBB472</t>
-  </si>
-  <si>
-    <t>SS34</t>
-  </si>
-  <si>
-    <t>C56</t>
-  </si>
-  <si>
     <t>D8, D15, D16</t>
   </si>
   <si>
-    <t>D14</t>
-  </si>
-  <si>
-    <t>J1, J14</t>
-  </si>
-  <si>
-    <t>CAP CER 4700PF 1KV X7R 1206</t>
-  </si>
-  <si>
-    <t>0.5mA@40V 40V Single 3A 0.55V@3A SMA(DO-214AC) Schottky Barrier Diodes (SBD) ROHS</t>
-  </si>
-  <si>
-    <t>MDD</t>
-  </si>
-  <si>
     <t>FB1, FB2, FB3, FB4, FB5</t>
   </si>
   <si>
-    <t>R2, R16</t>
-  </si>
-  <si>
-    <t>R17, R30, R41</t>
-  </si>
-  <si>
     <t>R19, R23, R24, R27, R42, R43</t>
   </si>
   <si>
     <t>R44, R45</t>
   </si>
   <si>
-    <t>SB1, SB2</t>
-  </si>
-  <si>
     <t>MMZ2012R102ATD25</t>
   </si>
   <si>
@@ -1225,6 +1126,111 @@
   </si>
   <si>
     <t>0R</t>
+  </si>
+  <si>
+    <t>DB128A-5.08-2*2P-OG-S</t>
+  </si>
+  <si>
+    <t>DB128A-5.08-2*2P-BK-S</t>
+  </si>
+  <si>
+    <t>DB128A-5.08-2*2P-GN-S</t>
+  </si>
+  <si>
+    <t>RT0603BRD07240RL</t>
+  </si>
+  <si>
+    <t>RC0603FR-0722RL</t>
+  </si>
+  <si>
+    <t>C1, C24, C32, C45, C48, C52, C55, C58, C60</t>
+  </si>
+  <si>
+    <t>J1</t>
+  </si>
+  <si>
+    <t>J7, J8</t>
+  </si>
+  <si>
+    <t>R14</t>
+  </si>
+  <si>
+    <t>R17, R41</t>
+  </si>
+  <si>
+    <t>R26</t>
+  </si>
+  <si>
+    <t>R28</t>
+  </si>
+  <si>
+    <t>SB1</t>
+  </si>
+  <si>
+    <t>Plugin,P=5.08mm Screw terminal ROHS</t>
+  </si>
+  <si>
+    <t>2x2P 20A -40℃~+105℃ 300V Black 12~28 Straight 5.08mm 1~2.5 2 2 Plugin,P=5.08mm Screw terminal ROHS</t>
+  </si>
+  <si>
+    <t>2x2P 20A -40℃~+105℃ 300V Green 12~28 Straight 5.08mm 1~2.5 2 2 Plugin,P=5.08mm Screw terminal ROHS</t>
+  </si>
+  <si>
+    <t>RES SMD 240 OHM 0.1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>RES 22 OHM 1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>22R</t>
+  </si>
+  <si>
+    <t>C2, C5, C9, C14, C15, C18, C19, C22, C27, C29, C31, C34, C36, C37, C39, C46, C49, C50, C51, C53, C54, C57, C59</t>
+  </si>
+  <si>
+    <t>C8, C38</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>R16, R30</t>
+  </si>
+  <si>
+    <t>MC-318FB</t>
+  </si>
+  <si>
+    <t>RC0402FR-075K1L</t>
+  </si>
+  <si>
+    <t>USB 3.0 3A 1 Brick nogging 24 Female -35℃~+75℃ Type-C SMD USB Connectors ROHS</t>
+  </si>
+  <si>
+    <t>SOFNG</t>
+  </si>
+  <si>
+    <t>RES 5.1K OHM 1% 1/16W 0402</t>
+  </si>
+  <si>
+    <t>5.1K</t>
+  </si>
+  <si>
+    <t>18cm SMA to IPEX 4Gen - Radio Frequency Cable ROHS</t>
+  </si>
+  <si>
+    <t>KH-FL2SMAK-IPEX4-RG0.81-B180</t>
+  </si>
+  <si>
+    <t>Shenzhen Kinghelm Elec</t>
+  </si>
+  <si>
+    <t>5dBi - Antennas ROHS</t>
+  </si>
+  <si>
+    <t>HJ-2.4GHz 5dBi-SMA</t>
+  </si>
+  <si>
+    <t>HJ Tech</t>
   </si>
 </sst>
 </file>
@@ -1330,7 +1336,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -1498,6 +1504,89 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -1511,7 +1600,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1548,22 +1637,13 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1581,19 +1661,13 @@
     <xf numFmtId="164" fontId="8" fillId="3" borderId="13" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1622,6 +1696,60 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1911,7 +2039,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:T92"/>
+  <dimension ref="A1:V94"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="4" customWidth="1"/>
@@ -1941,13 +2069,13 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
     </row>
     <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1960,38 +2088,38 @@
       <c r="D2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>99</v>
+      <c r="E2" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>352</v>
+        <v>333</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>351</v>
+        <v>332</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>354</v>
+        <v>340</v>
+      </c>
+      <c r="L2" s="36" t="s">
+        <v>335</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>358</v>
+        <v>338</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>339</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>353</v>
+        <v>334</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2004,83 +2132,83 @@
         <v>2</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>100</v>
+        <v>374</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>93</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>312</v>
+        <v>293</v>
       </c>
       <c r="J3" s="7">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K3" s="7">
         <f>J3*5</f>
-        <v>25</v>
-      </c>
-      <c r="L3" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="M3" s="15">
+        <v>45</v>
+      </c>
+      <c r="L3" s="37" t="s">
+        <v>337</v>
+      </c>
+      <c r="M3" s="14">
         <v>0.124</v>
       </c>
-      <c r="N3" s="15">
+      <c r="N3" s="45">
         <f>M3*K3</f>
-        <v>3.1</v>
+        <v>5.58</v>
       </c>
       <c r="O3" s="7"/>
     </row>
     <row r="4" spans="1:15" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="11">
-        <f t="shared" ref="B4:B87" si="0">ROW(B4) - ROW($B$2)</f>
+        <f t="shared" ref="B4:B86" si="0">ROW(B4) - ROW($B$2)</f>
         <v>2</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>101</v>
+        <v>388</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>94</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>313</v>
+        <v>294</v>
       </c>
       <c r="J4" s="9">
         <v>23</v>
       </c>
       <c r="K4" s="7">
-        <f t="shared" ref="K4:K69" si="1">J4*5</f>
+        <f t="shared" ref="K4:K67" si="1">J4*5</f>
         <v>115</v>
       </c>
-      <c r="L4" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M4" s="15">
+      <c r="L4" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M4" s="14">
         <v>1.9400000000000001E-2</v>
       </c>
-      <c r="N4" s="15">
+      <c r="N4" s="45">
         <f t="shared" ref="N4:N70" si="2">M4*K4</f>
         <v>2.2309999999999999</v>
       </c>
@@ -2096,22 +2224,22 @@
         <v>2</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>102</v>
+        <v>23</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>314</v>
+        <v>295</v>
       </c>
       <c r="J5" s="7">
         <v>2</v>
@@ -2120,13 +2248,13 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L5" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M5" s="15">
+      <c r="L5" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M5" s="14">
         <v>0.92100000000000004</v>
       </c>
-      <c r="N5" s="15">
+      <c r="N5" s="45">
         <f t="shared" si="2"/>
         <v>9.2100000000000009</v>
       </c>
@@ -2142,22 +2270,22 @@
         <v>2</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>103</v>
+        <v>24</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>96</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>315</v>
+        <v>296</v>
       </c>
       <c r="J6" s="9">
         <v>2</v>
@@ -2166,13 +2294,13 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L6" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M6" s="15">
+      <c r="L6" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M6" s="14">
         <v>1.0389999999999999</v>
       </c>
-      <c r="N6" s="15">
+      <c r="N6" s="45">
         <f t="shared" si="2"/>
         <v>10.389999999999999</v>
       </c>
@@ -2188,22 +2316,22 @@
         <v>2</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>361</v>
+        <v>389</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>342</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>316</v>
+        <v>297</v>
       </c>
       <c r="J7" s="7">
         <v>2</v>
@@ -2212,13 +2340,13 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L7" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M7" s="15">
+      <c r="L7" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M7" s="14">
         <v>0.22</v>
       </c>
-      <c r="N7" s="15">
+      <c r="N7" s="45">
         <f t="shared" si="2"/>
         <v>2.2000000000000002</v>
       </c>
@@ -2234,22 +2362,22 @@
         <v>2</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>104</v>
+        <v>25</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>97</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="J8" s="9">
         <v>1</v>
@@ -2258,13 +2386,13 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L8" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M8" s="15">
+      <c r="L8" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M8" s="14">
         <v>0.1</v>
       </c>
-      <c r="N8" s="15">
+      <c r="N8" s="45">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
@@ -2280,22 +2408,22 @@
         <v>2</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>105</v>
+        <v>26</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>98</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>318</v>
+        <v>299</v>
       </c>
       <c r="J9" s="7">
         <v>1</v>
@@ -2304,13 +2432,13 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L9" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M9" s="15">
+      <c r="L9" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M9" s="14">
         <v>0.1</v>
       </c>
-      <c r="N9" s="15">
+      <c r="N9" s="45">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
@@ -2326,22 +2454,22 @@
         <v>2</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>106</v>
+        <v>27</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>319</v>
+        <v>300</v>
       </c>
       <c r="J10" s="9">
         <v>1</v>
@@ -2350,13 +2478,13 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L10" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M10" s="15">
+      <c r="L10" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M10" s="14">
         <v>0.1</v>
       </c>
-      <c r="N10" s="15">
+      <c r="N10" s="45">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
@@ -2372,22 +2500,22 @@
         <v>2</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>107</v>
+        <v>28</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="J11" s="7">
         <v>1</v>
@@ -2396,13 +2524,13 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L11" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M11" s="15">
+      <c r="L11" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M11" s="14">
         <v>0.1</v>
       </c>
-      <c r="N11" s="15">
+      <c r="N11" s="45">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
@@ -2418,22 +2546,22 @@
         <v>2</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>108</v>
+        <v>29</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>101</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>321</v>
+        <v>302</v>
       </c>
       <c r="J12" s="9">
         <v>3</v>
@@ -2442,13 +2570,13 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="L12" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M12" s="15">
+      <c r="L12" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M12" s="14">
         <v>0.22600000000000001</v>
       </c>
-      <c r="N12" s="15">
+      <c r="N12" s="45">
         <f t="shared" si="2"/>
         <v>3.39</v>
       </c>
@@ -2464,22 +2592,22 @@
         <v>2</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>109</v>
+        <v>30</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>322</v>
+        <v>303</v>
       </c>
       <c r="J13" s="7">
         <v>2</v>
@@ -2488,13 +2616,13 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L13" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M13" s="15">
+      <c r="L13" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M13" s="14">
         <v>0.73699999999999999</v>
       </c>
-      <c r="N13" s="15">
+      <c r="N13" s="45">
         <f t="shared" si="2"/>
         <v>7.37</v>
       </c>
@@ -2510,22 +2638,22 @@
         <v>2</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>110</v>
+        <v>31</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>103</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>312</v>
+        <v>293</v>
       </c>
       <c r="J14" s="9">
         <v>1</v>
@@ -2534,13 +2662,13 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L14" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M14" s="15">
+      <c r="L14" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M14" s="14">
         <v>0.22</v>
       </c>
-      <c r="N14" s="15">
+      <c r="N14" s="45">
         <f t="shared" si="2"/>
         <v>1.1000000000000001</v>
       </c>
@@ -2556,22 +2684,22 @@
         <v>2</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>111</v>
+        <v>32</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>104</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>314</v>
+        <v>295</v>
       </c>
       <c r="J15" s="7">
         <v>7</v>
@@ -2580,13 +2708,13 @@
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="L15" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M15" s="15">
+      <c r="L15" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M15" s="14">
         <v>0.26</v>
       </c>
-      <c r="N15" s="15">
+      <c r="N15" s="45">
         <f t="shared" si="2"/>
         <v>9.1</v>
       </c>
@@ -2602,22 +2730,22 @@
         <v>2</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>112</v>
+        <v>33</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>105</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>362</v>
+        <v>343</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="J16" s="9">
         <v>1</v>
@@ -2626,13 +2754,13 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L16" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M16" s="15">
+      <c r="L16" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M16" s="14">
         <v>0.45</v>
       </c>
-      <c r="N16" s="15">
+      <c r="N16" s="45">
         <f t="shared" si="2"/>
         <v>2.25</v>
       </c>
@@ -2648,22 +2776,22 @@
         <v>2</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>113</v>
+        <v>34</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>106</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>324</v>
+        <v>305</v>
       </c>
       <c r="J17" s="7">
         <v>2</v>
@@ -2672,13 +2800,13 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L17" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M17" s="15">
+      <c r="L17" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M17" s="14">
         <v>0.11899999999999999</v>
       </c>
-      <c r="N17" s="15">
+      <c r="N17" s="45">
         <f t="shared" si="2"/>
         <v>1.19</v>
       </c>
@@ -2694,22 +2822,22 @@
         <v>2</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>114</v>
+        <v>35</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>107</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>325</v>
+        <v>306</v>
       </c>
       <c r="J18" s="9">
         <v>1</v>
@@ -2718,13 +2846,13 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L18" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M18" s="15">
+      <c r="L18" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M18" s="14">
         <v>0.48</v>
       </c>
-      <c r="N18" s="15">
+      <c r="N18" s="45">
         <f t="shared" si="2"/>
         <v>2.4</v>
       </c>
@@ -2733,29 +2861,29 @@
     <row r="19" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B19) - ROW($B$2)</f>
         <v>17</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>386</v>
+        <v>36</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>108</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>380</v>
+        <v>220</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>289</v>
+        <v>273</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="J19" s="7">
         <v>1</v>
@@ -2764,593 +2892,596 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L19" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M19" s="15">
-        <v>0.37</v>
-      </c>
-      <c r="N19" s="15">
-        <f t="shared" si="2"/>
-        <v>1.85</v>
+      <c r="L19" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M19" s="14">
+        <v>2.96</v>
+      </c>
+      <c r="N19" s="45">
+        <f t="shared" si="2"/>
+        <v>14.8</v>
       </c>
       <c r="O19" s="7"/>
     </row>
     <row r="20" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="11">
-        <f>ROW(B20) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D20" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>291</v>
+      <c r="D20" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>274</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="J20" s="7">
+        <v>336</v>
+      </c>
+      <c r="J20" s="9">
         <v>1</v>
       </c>
       <c r="K20" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L20" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M20" s="15">
-        <v>2.96</v>
-      </c>
-      <c r="N20" s="15">
-        <f t="shared" si="2"/>
-        <v>14.8</v>
-      </c>
-      <c r="O20" s="7"/>
-    </row>
-    <row r="21" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L20" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M20" s="14">
+        <v>0.91</v>
+      </c>
+      <c r="N20" s="45">
+        <f t="shared" si="2"/>
+        <v>4.55</v>
+      </c>
+      <c r="O20" s="9"/>
+    </row>
+    <row r="21" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B21) - ROW($B$2)</f>
         <v>19</v>
       </c>
       <c r="C21" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D21" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>237</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>292</v>
+      <c r="D21" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>275</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="J21" s="9">
+        <v>336</v>
+      </c>
+      <c r="J21" s="7">
         <v>1</v>
       </c>
       <c r="K21" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L21" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M21" s="15">
-        <v>0.91</v>
-      </c>
-      <c r="N21" s="15">
-        <f t="shared" si="2"/>
-        <v>4.55</v>
-      </c>
-      <c r="O21" s="9"/>
-    </row>
-    <row r="22" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L21" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M21" s="14">
+        <v>0.21</v>
+      </c>
+      <c r="N21" s="45">
+        <f t="shared" si="2"/>
+        <v>1.05</v>
+      </c>
+      <c r="O21" s="7"/>
+    </row>
+    <row r="22" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="11">
-        <f>ROW(B22) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D22" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>293</v>
+      <c r="D22" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>274</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="J22" s="7">
+        <v>336</v>
+      </c>
+      <c r="J22" s="9">
         <v>1</v>
       </c>
       <c r="K22" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L22" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M22" s="15">
-        <v>0.21</v>
-      </c>
-      <c r="N22" s="15">
-        <f t="shared" si="2"/>
-        <v>1.05</v>
-      </c>
-      <c r="O22" s="7"/>
+      <c r="L22" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M22" s="14">
+        <v>0.38</v>
+      </c>
+      <c r="N22" s="45">
+        <f t="shared" si="2"/>
+        <v>1.9</v>
+      </c>
+      <c r="O22" s="9"/>
     </row>
     <row r="23" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B23) - ROW($B$2)</f>
         <v>21</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D23" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>292</v>
+      <c r="D23" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>276</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="J23" s="9">
-        <v>1</v>
+        <v>336</v>
+      </c>
+      <c r="J23" s="7">
+        <v>2</v>
       </c>
       <c r="K23" s="7">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L23" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M23" s="15">
-        <v>0.38</v>
-      </c>
-      <c r="N23" s="15">
-        <f t="shared" si="2"/>
-        <v>1.9</v>
-      </c>
-      <c r="O23" s="9"/>
+        <v>10</v>
+      </c>
+      <c r="L23" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M23" s="14">
+        <v>0.255</v>
+      </c>
+      <c r="N23" s="45">
+        <f t="shared" si="2"/>
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="O23" s="7"/>
     </row>
     <row r="24" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="11">
-        <f>ROW(B24) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D24" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>294</v>
+      <c r="D24" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>277</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="J24" s="7">
-        <v>2</v>
+        <v>336</v>
+      </c>
+      <c r="J24" s="9">
+        <v>1</v>
       </c>
       <c r="K24" s="7">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L24" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M24" s="15">
-        <v>0.255</v>
-      </c>
-      <c r="N24" s="15">
-        <f t="shared" si="2"/>
-        <v>2.5499999999999998</v>
-      </c>
-      <c r="O24" s="7"/>
-    </row>
-    <row r="25" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="L24" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M24" s="14">
+        <v>0.41</v>
+      </c>
+      <c r="N24" s="45">
+        <f t="shared" si="2"/>
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="O24" s="9"/>
+    </row>
+    <row r="25" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B25) - ROW($B$2)</f>
         <v>23</v>
       </c>
       <c r="C25" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="J25" s="7">
         <v>3</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="J25" s="9">
-        <v>1</v>
       </c>
       <c r="K25" s="7">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L25" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M25" s="15">
-        <v>0.41</v>
-      </c>
-      <c r="N25" s="15">
-        <f t="shared" si="2"/>
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="O25" s="9"/>
-    </row>
-    <row r="26" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L25" s="38" t="s">
+        <v>349</v>
+      </c>
+      <c r="M25" s="14">
+        <v>1.54E-2</v>
+      </c>
+      <c r="N25" s="45">
+        <f t="shared" si="2"/>
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="O25" s="7"/>
+    </row>
+    <row r="26" spans="1:15" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="11">
-        <f>ROW(B26) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C26" s="12" t="s">
-        <v>4</v>
+      <c r="C26" s="13" t="s">
+        <v>5</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>296</v>
+        <v>42</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>279</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="J26" s="7">
-        <v>3</v>
+        <v>336</v>
+      </c>
+      <c r="J26" s="9">
+        <v>1</v>
       </c>
       <c r="K26" s="7">
-        <v>50</v>
-      </c>
-      <c r="L26" s="16" t="s">
-        <v>368</v>
-      </c>
-      <c r="M26" s="15">
-        <v>1.54E-2</v>
-      </c>
-      <c r="N26" s="15">
-        <f t="shared" si="2"/>
-        <v>0.77</v>
-      </c>
-      <c r="O26" s="7"/>
-    </row>
-    <row r="27" spans="1:15" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="L26" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M26" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="N26" s="45">
+        <f t="shared" si="2"/>
+        <v>7.5</v>
+      </c>
+      <c r="O26" s="9"/>
+    </row>
+    <row r="27" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B27) - ROW($B$2)</f>
         <v>25</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="G27" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>297</v>
+      <c r="C27" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>344</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="J27" s="9">
-        <v>1</v>
+        <v>336</v>
+      </c>
+      <c r="J27" s="7">
+        <v>4</v>
       </c>
       <c r="K27" s="7">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L27" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M27" s="15">
-        <v>1.5</v>
-      </c>
-      <c r="N27" s="15">
-        <f t="shared" si="2"/>
-        <v>7.5</v>
-      </c>
-      <c r="O27" s="9"/>
-    </row>
-    <row r="28" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="L27" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M27" s="14">
+        <v>0.26900000000000002</v>
+      </c>
+      <c r="N27" s="45">
+        <f t="shared" si="2"/>
+        <v>5.3800000000000008</v>
+      </c>
+      <c r="O27" s="7"/>
+    </row>
+    <row r="28" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="11">
         <f>ROW(B28) - ROW($B$2)</f>
         <v>26</v>
       </c>
-      <c r="C28" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>363</v>
+      <c r="C28" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>283</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="J28" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K28" s="7">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="L28" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M28" s="15">
-        <v>0.26900000000000002</v>
-      </c>
-      <c r="N28" s="15">
-        <f t="shared" si="2"/>
-        <v>5.3800000000000008</v>
+        <v>25</v>
+      </c>
+      <c r="L28" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M28" s="14">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="N28" s="45">
+        <f t="shared" si="2"/>
+        <v>2.3250000000000002</v>
       </c>
       <c r="O28" s="7"/>
     </row>
-    <row r="29" spans="1:15" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="11">
-        <f>ROW(B29) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C29" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>381</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>388</v>
+      <c r="C29" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>280</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="J29" s="7">
+        <v>336</v>
+      </c>
+      <c r="J29" s="9">
         <v>1</v>
       </c>
       <c r="K29" s="7">
-        <v>20</v>
-      </c>
-      <c r="L29" s="16" t="s">
-        <v>368</v>
-      </c>
-      <c r="M29" s="15">
-        <v>2.3300000000000001E-2</v>
-      </c>
-      <c r="N29" s="15">
-        <f t="shared" si="2"/>
-        <v>0.46600000000000003</v>
-      </c>
-      <c r="O29" s="7"/>
-    </row>
-    <row r="30" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="L29" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M29" s="14">
+        <v>4.3280000000000003</v>
+      </c>
+      <c r="N29" s="45">
+        <f t="shared" si="2"/>
+        <v>21.64</v>
+      </c>
+      <c r="O29" s="9"/>
+    </row>
+    <row r="30" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="11">
         <f>ROW(B30) - ROW($B$2)</f>
         <v>28</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>397</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>389</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>398</v>
+      <c r="C30" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>382</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>399</v>
-      </c>
-      <c r="G30" s="10" t="s">
-        <v>395</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>301</v>
+        <v>341</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>281</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="J30" s="7">
+        <v>1</v>
+      </c>
+      <c r="K30" s="7">
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="K30" s="7">
-        <v>20</v>
-      </c>
-      <c r="L30" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M30" s="15">
-        <v>9.2999999999999999E-2</v>
-      </c>
-      <c r="N30" s="15">
-        <f t="shared" si="2"/>
-        <v>1.8599999999999999</v>
+      <c r="L30" s="38" t="s">
+        <v>349</v>
+      </c>
+      <c r="M30" s="14">
+        <v>0.3725</v>
+      </c>
+      <c r="N30" s="45">
+        <f t="shared" si="2"/>
+        <v>1.8625</v>
       </c>
       <c r="O30" s="7"/>
     </row>
-    <row r="31" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="11">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="G31" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>298</v>
+        <v>9</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>395</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="J31" s="9">
-        <v>2</v>
+        <v>336</v>
+      </c>
+      <c r="J31" s="7">
+        <v>1</v>
       </c>
       <c r="K31" s="7">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L31" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M31" s="15">
-        <v>4.3280000000000003</v>
-      </c>
-      <c r="N31" s="15">
-        <f t="shared" si="2"/>
-        <v>43.28</v>
+        <v>5</v>
+      </c>
+      <c r="L31" s="38" t="s">
+        <v>349</v>
+      </c>
+      <c r="M31" s="14">
+        <v>0.60940000000000005</v>
+      </c>
+      <c r="N31" s="45">
+        <f t="shared" si="2"/>
+        <v>3.0470000000000002</v>
       </c>
       <c r="O31" s="9"/>
     </row>
-    <row r="32" spans="1:15" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="11">
         <f>ROW(B32) - ROW($B$2)</f>
         <v>30</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>125</v>
+        <v>46</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>118</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>195</v>
+        <v>228</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="J32" s="7">
         <v>1</v>
@@ -3359,15 +3490,15 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L32" s="16" t="s">
-        <v>368</v>
-      </c>
-      <c r="M32" s="15">
-        <v>0.16750000000000001</v>
-      </c>
-      <c r="N32" s="15">
-        <f t="shared" si="2"/>
-        <v>0.83750000000000002</v>
+      <c r="L32" s="38" t="s">
+        <v>349</v>
+      </c>
+      <c r="M32" s="14">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="N32" s="45">
+        <f t="shared" si="2"/>
+        <v>0.34</v>
       </c>
       <c r="O32" s="7"/>
     </row>
@@ -3378,25 +3509,25 @@
         <v>31</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>372</v>
+        <v>47</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>351</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>371</v>
+        <v>353</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="J33" s="9">
         <v>1</v>
@@ -3405,196 +3536,197 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L33" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M33" s="15">
-        <v>11.43</v>
-      </c>
-      <c r="N33" s="15">
-        <f t="shared" si="2"/>
-        <v>57.15</v>
+      <c r="L33" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M33" s="14">
+        <v>25.25</v>
+      </c>
+      <c r="N33" s="45">
+        <f t="shared" si="2"/>
+        <v>126.25</v>
       </c>
       <c r="O33" s="9"/>
     </row>
-    <row r="34" spans="1:15" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="11">
         <f>ROW(B34) - ROW($B$2)</f>
         <v>32</v>
       </c>
       <c r="C34" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="J34" s="7">
+        <v>2</v>
+      </c>
+      <c r="K34" s="7">
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="D34" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="I34" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="J34" s="7">
-        <v>1</v>
-      </c>
-      <c r="K34" s="7">
-        <v>12</v>
-      </c>
-      <c r="L34" s="16" t="s">
-        <v>368</v>
-      </c>
-      <c r="M34" s="15">
-        <v>6.8000000000000005E-2</v>
-      </c>
-      <c r="N34" s="15">
-        <f t="shared" si="2"/>
-        <v>0.81600000000000006</v>
+      <c r="L34" s="38" t="s">
+        <v>349</v>
+      </c>
+      <c r="M34" s="14">
+        <v>0.30809999999999998</v>
+      </c>
+      <c r="N34" s="45">
+        <f t="shared" si="2"/>
+        <v>3.081</v>
       </c>
       <c r="O34" s="7"/>
     </row>
-    <row r="35" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="11">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>373</v>
+        <v>48</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>384</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>375</v>
+        <v>281</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="J35" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K35" s="7">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L35" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M35" s="15">
-        <v>25.25</v>
-      </c>
-      <c r="N35" s="15">
-        <f t="shared" si="2"/>
-        <v>126.25</v>
+        <v>20</v>
+      </c>
+      <c r="L35" s="38" t="s">
+        <v>349</v>
+      </c>
+      <c r="M35" s="14">
+        <v>0.30669999999999997</v>
+      </c>
+      <c r="N35" s="45">
+        <f t="shared" si="2"/>
+        <v>6.1339999999999995</v>
       </c>
       <c r="O35" s="9"/>
     </row>
-    <row r="36" spans="1:15" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="11">
         <f>ROW(B36) - ROW($B$2)</f>
         <v>34</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>127</v>
+        <v>49</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>119</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>355</v>
+        <v>308</v>
       </c>
       <c r="J36" s="7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K36" s="7">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="L36" s="16" t="s">
-        <v>368</v>
-      </c>
-      <c r="M36" s="15">
-        <v>0.1754</v>
-      </c>
-      <c r="N36" s="15">
-        <f t="shared" si="2"/>
-        <v>3.508</v>
+        <v>5</v>
+      </c>
+      <c r="L36" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M36" s="14">
+        <v>1.56</v>
+      </c>
+      <c r="N36" s="45">
+        <f t="shared" si="2"/>
+        <v>7.8000000000000007</v>
       </c>
       <c r="O36" s="7"/>
     </row>
-    <row r="37" spans="1:15" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="11">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>128</v>
+        <v>50</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>120</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="I37" s="8" t="s">
-        <v>355</v>
+        <v>283</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>309</v>
       </c>
       <c r="J37" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K37" s="7">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="L37" s="16" t="s">
-        <v>368</v>
-      </c>
-      <c r="M37" s="15">
-        <v>0.29749999999999999</v>
-      </c>
-      <c r="N37" s="15">
+        <v>5</v>
+      </c>
+      <c r="L37" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M37" s="14">
+        <v>1.19</v>
+      </c>
+      <c r="N37" s="45">
         <f t="shared" si="2"/>
         <v>5.9499999999999993</v>
       </c>
@@ -3607,25 +3739,25 @@
         <v>36</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>129</v>
+        <v>51</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>121</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="J38" s="7">
         <v>1</v>
@@ -3634,107 +3766,107 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L38" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M38" s="15">
-        <v>1.56</v>
-      </c>
-      <c r="N38" s="15">
-        <f t="shared" si="2"/>
-        <v>7.8000000000000007</v>
+      <c r="L38" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M38" s="14">
+        <v>1.85</v>
+      </c>
+      <c r="N38" s="45">
+        <f t="shared" si="2"/>
+        <v>9.25</v>
       </c>
       <c r="O38" s="7"/>
     </row>
-    <row r="39" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="11">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="E39" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>360</v>
+        <v>52</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>186</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="I39" s="10" t="s">
-        <v>328</v>
+        <v>284</v>
+      </c>
+      <c r="I39" s="8" t="s">
+        <v>336</v>
       </c>
       <c r="J39" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K39" s="7">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L39" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M39" s="15">
-        <v>1.19</v>
-      </c>
-      <c r="N39" s="15">
-        <f t="shared" si="2"/>
-        <v>5.9499999999999993</v>
+        <v>20</v>
+      </c>
+      <c r="L39" s="38" t="s">
+        <v>349</v>
+      </c>
+      <c r="M39" s="14">
+        <v>2.0799999999999999E-2</v>
+      </c>
+      <c r="N39" s="45">
+        <f t="shared" si="2"/>
+        <v>0.41599999999999998</v>
       </c>
       <c r="O39" s="9"/>
     </row>
-    <row r="40" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="11">
         <f>ROW(B40) - ROW($B$2)</f>
         <v>38</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>131</v>
+        <v>53</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>360</v>
+        <v>186</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>301</v>
+        <v>284</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="J40" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K40" s="7">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L40" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M40" s="15">
-        <v>1.85</v>
-      </c>
-      <c r="N40" s="15">
-        <f t="shared" si="2"/>
-        <v>9.25</v>
+        <v>10</v>
+      </c>
+      <c r="L40" s="38" t="s">
+        <v>349</v>
+      </c>
+      <c r="M40" s="14">
+        <v>2.1700000000000001E-2</v>
+      </c>
+      <c r="N40" s="45">
+        <f t="shared" si="2"/>
+        <v>0.217</v>
       </c>
       <c r="O40" s="7"/>
     </row>
@@ -3748,39 +3880,39 @@
         <v>14</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="E41" s="10" t="s">
-        <v>132</v>
+        <v>54</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>124</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="J41" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K41" s="7">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="L41" s="16" t="s">
-        <v>368</v>
-      </c>
-      <c r="M41" s="15">
-        <v>2.0799999999999999E-2</v>
-      </c>
-      <c r="N41" s="15">
-        <f t="shared" si="2"/>
-        <v>0.41599999999999998</v>
+        <v>5</v>
+      </c>
+      <c r="L41" s="38" t="s">
+        <v>349</v>
+      </c>
+      <c r="M41" s="14">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="N41" s="45">
+        <f t="shared" si="2"/>
+        <v>0.10999999999999999</v>
       </c>
       <c r="O41" s="9"/>
     </row>
@@ -3794,865 +3926,869 @@
         <v>14</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>133</v>
+        <v>55</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>125</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="J42" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K42" s="7">
-        <v>20</v>
-      </c>
-      <c r="L42" s="16" t="s">
-        <v>368</v>
-      </c>
-      <c r="M42" s="15">
-        <v>2.1700000000000001E-2</v>
-      </c>
-      <c r="N42" s="15">
-        <f t="shared" si="2"/>
-        <v>0.434</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="L42" s="38" t="s">
+        <v>349</v>
+      </c>
+      <c r="M42" s="14">
+        <v>3.1300000000000001E-2</v>
+      </c>
+      <c r="N42" s="45">
+        <f t="shared" si="2"/>
+        <v>0.1565</v>
       </c>
       <c r="O42" s="7"/>
     </row>
-    <row r="43" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="11">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="E43" s="10" t="s">
-        <v>134</v>
+        <v>56</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>126</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="J43" s="9">
         <v>1</v>
       </c>
       <c r="K43" s="7">
-        <v>20</v>
-      </c>
-      <c r="L43" s="16" t="s">
-        <v>368</v>
-      </c>
-      <c r="M43" s="15">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="N43" s="15">
-        <f t="shared" si="2"/>
-        <v>0.43999999999999995</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="L43" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M43" s="14">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="N43" s="45">
+        <f t="shared" si="2"/>
+        <v>5.45</v>
       </c>
       <c r="O43" s="9"/>
     </row>
-    <row r="44" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="11">
         <f>ROW(B44) - ROW($B$2)</f>
         <v>42</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>135</v>
+        <v>57</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>127</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="J44" s="7">
         <v>1</v>
       </c>
       <c r="K44" s="7">
-        <v>20</v>
-      </c>
-      <c r="L44" s="16" t="s">
-        <v>368</v>
-      </c>
-      <c r="M44" s="15">
-        <v>3.1300000000000001E-2</v>
-      </c>
-      <c r="N44" s="15">
-        <f t="shared" si="2"/>
-        <v>0.626</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="L44" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M44" s="14">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="N44" s="45">
+        <f t="shared" si="2"/>
+        <v>5.45</v>
       </c>
       <c r="O44" s="7"/>
     </row>
-    <row r="45" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="11">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="C45" s="13" t="s">
-        <v>15</v>
+      <c r="C45" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>136</v>
+        <v>58</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>128</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="J45" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K45" s="7">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L45" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M45" s="15">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="N45" s="15">
-        <f t="shared" si="2"/>
-        <v>5.45</v>
+        <v>10</v>
+      </c>
+      <c r="L45" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M45" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="N45" s="45">
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
       <c r="O45" s="9"/>
     </row>
     <row r="46" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="11">
-        <f>ROW(B46) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="C46" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="G46" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="I46" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="J46" s="7">
+      <c r="C46" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="G46" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="I46" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="J46" s="9">
         <v>1</v>
       </c>
       <c r="K46" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L46" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M46" s="15">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="N46" s="15">
-        <f t="shared" si="2"/>
-        <v>5.45</v>
-      </c>
-      <c r="O46" s="7"/>
-    </row>
-    <row r="47" spans="1:15" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L46" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M46" s="14">
+        <v>0.15</v>
+      </c>
+      <c r="N46" s="45">
+        <f t="shared" si="2"/>
+        <v>0.75</v>
+      </c>
+      <c r="O46" s="9"/>
+    </row>
+    <row r="47" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B47) - ROW($B$2)</f>
         <v>45</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="F47" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="G47" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>304</v>
+        <v>390</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>271</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="J47" s="9">
-        <v>2</v>
+        <v>311</v>
+      </c>
+      <c r="J47" s="7">
+        <v>1</v>
       </c>
       <c r="K47" s="7">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L47" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M47" s="15">
-        <v>0.2</v>
-      </c>
-      <c r="N47" s="15">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="O47" s="9"/>
-    </row>
-    <row r="48" spans="1:15" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="L47" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M47" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="N47" s="45">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="O47" s="7"/>
+    </row>
+    <row r="48" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="11">
-        <f>ROW(B48) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="C48" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="G48" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="H48" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="I48" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="J48" s="7">
+      <c r="C48" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="I48" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="J48" s="9">
         <v>1</v>
       </c>
       <c r="K48" s="7">
-        <v>20</v>
-      </c>
-      <c r="L48" s="16" t="s">
-        <v>368</v>
-      </c>
-      <c r="M48" s="15">
-        <v>3.3500000000000002E-2</v>
-      </c>
-      <c r="N48" s="15">
-        <f t="shared" si="2"/>
-        <v>0.67</v>
-      </c>
-      <c r="O48" s="7"/>
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="L48" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M48" s="14">
+        <v>0.15</v>
+      </c>
+      <c r="N48" s="45">
+        <f t="shared" si="2"/>
+        <v>0.75</v>
+      </c>
+      <c r="O48" s="9"/>
     </row>
     <row r="49" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B49) - ROW($B$2)</f>
         <v>47</v>
       </c>
-      <c r="C49" s="13" t="s">
+      <c r="C49" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D49" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E49" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="F49" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="G49" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="I49" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="J49" s="9">
+      <c r="D49" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="J49" s="7">
         <v>1</v>
       </c>
       <c r="K49" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L49" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M49" s="15">
-        <v>0.15</v>
-      </c>
-      <c r="N49" s="15">
-        <f t="shared" si="2"/>
-        <v>0.75</v>
-      </c>
-      <c r="O49" s="9"/>
+      <c r="L49" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M49" s="14">
+        <v>0.13</v>
+      </c>
+      <c r="N49" s="45">
+        <f t="shared" si="2"/>
+        <v>0.65</v>
+      </c>
+      <c r="O49" s="7"/>
     </row>
     <row r="50" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="11">
-        <f>ROW(B50) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="C50" s="12" t="s">
+      <c r="C50" s="13" t="s">
         <v>17</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>390</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="G50" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="H50" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="I50" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="J50" s="7">
-        <v>2</v>
+        <v>62</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="G50" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="I50" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="J50" s="9">
+        <v>1</v>
       </c>
       <c r="K50" s="7">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L50" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M50" s="15">
-        <v>0.1</v>
-      </c>
-      <c r="N50" s="15">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="O50" s="7"/>
+        <v>5</v>
+      </c>
+      <c r="L50" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M50" s="14">
+        <v>0.64</v>
+      </c>
+      <c r="N50" s="45">
+        <f t="shared" si="2"/>
+        <v>3.2</v>
+      </c>
+      <c r="O50" s="9"/>
     </row>
     <row r="51" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B51) - ROW($B$2)</f>
         <v>49</v>
       </c>
-      <c r="C51" s="13" t="s">
+      <c r="C51" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D51" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E51" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="G51" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="I51" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="J51" s="9">
+      <c r="D51" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="J51" s="7">
         <v>1</v>
       </c>
       <c r="K51" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L51" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M51" s="15">
+      <c r="L51" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M51" s="14">
         <v>0.15</v>
       </c>
-      <c r="N51" s="15">
+      <c r="N51" s="45">
         <f t="shared" si="2"/>
         <v>0.75</v>
       </c>
-      <c r="O51" s="9"/>
+      <c r="O51" s="7"/>
     </row>
     <row r="52" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="11">
-        <f>ROW(B52) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D52" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="G52" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="H52" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="I52" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="J52" s="7">
+      <c r="D52" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="G52" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="I52" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="J52" s="9">
         <v>1</v>
       </c>
       <c r="K52" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L52" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M52" s="15">
-        <v>0.13</v>
-      </c>
-      <c r="N52" s="15">
-        <f t="shared" si="2"/>
-        <v>0.65</v>
-      </c>
-      <c r="O52" s="7"/>
+      <c r="L52" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M52" s="14">
+        <v>0.15</v>
+      </c>
+      <c r="N52" s="45">
+        <f t="shared" si="2"/>
+        <v>0.75</v>
+      </c>
+      <c r="O52" s="9"/>
     </row>
     <row r="53" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B53) - ROW($B$2)</f>
         <v>51</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="C53" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D53" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E53" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="F53" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="G53" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="I53" s="10" t="s">
-        <v>333</v>
-      </c>
-      <c r="J53" s="9">
+      <c r="D53" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="H53" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="J53" s="7">
         <v>1</v>
       </c>
       <c r="K53" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L53" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M53" s="15">
-        <v>0.64</v>
-      </c>
-      <c r="N53" s="15">
-        <f t="shared" si="2"/>
-        <v>3.2</v>
-      </c>
-      <c r="O53" s="9"/>
+      <c r="L53" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M53" s="14">
+        <v>0.15</v>
+      </c>
+      <c r="N53" s="45">
+        <f t="shared" si="2"/>
+        <v>0.75</v>
+      </c>
+      <c r="O53" s="7"/>
     </row>
     <row r="54" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="11">
-        <f>ROW(B54) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="C54" s="12" t="s">
+      <c r="C54" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D54" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="G54" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="H54" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="I54" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="J54" s="7">
+      <c r="D54" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E54" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="G54" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="H54" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="I54" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="J54" s="9">
         <v>1</v>
       </c>
       <c r="K54" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L54" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M54" s="15">
+      <c r="L54" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M54" s="14">
         <v>0.15</v>
       </c>
-      <c r="N54" s="15">
+      <c r="N54" s="45">
         <f t="shared" si="2"/>
         <v>0.75</v>
       </c>
-      <c r="O54" s="7"/>
+      <c r="O54" s="9"/>
     </row>
     <row r="55" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B55) - ROW($B$2)</f>
         <v>53</v>
       </c>
       <c r="C55" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D55" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E55" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="F55" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="G55" s="10" t="s">
-        <v>259</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="I55" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="J55" s="9">
+      <c r="D55" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="H55" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="J55" s="7">
         <v>1</v>
       </c>
       <c r="K55" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L55" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M55" s="15">
-        <v>0.15</v>
-      </c>
-      <c r="N55" s="15">
-        <f t="shared" si="2"/>
-        <v>0.75</v>
-      </c>
-      <c r="O55" s="9"/>
+      <c r="L55" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M55" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="N55" s="45">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="O55" s="7"/>
     </row>
     <row r="56" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="11">
-        <f>ROW(B56) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="C56" s="12" t="s">
+      <c r="C56" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D56" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="G56" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="H56" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="I56" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="J56" s="7">
-        <v>1</v>
+      <c r="D56" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E56" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="G56" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="I56" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="J56" s="9">
+        <v>5</v>
       </c>
       <c r="K56" s="7">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L56" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M56" s="15">
-        <v>0.15</v>
-      </c>
-      <c r="N56" s="15">
-        <f t="shared" si="2"/>
-        <v>0.75</v>
-      </c>
-      <c r="O56" s="7"/>
+        <v>25</v>
+      </c>
+      <c r="L56" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M56" s="14">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N56" s="45">
+        <f t="shared" si="2"/>
+        <v>0.375</v>
+      </c>
+      <c r="O56" s="9"/>
     </row>
     <row r="57" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B57) - ROW($B$2)</f>
         <v>55</v>
       </c>
-      <c r="C57" s="13" t="s">
+      <c r="C57" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D57" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E57" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="F57" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="G57" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="I57" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="J57" s="9">
+      <c r="D57" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="I57" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="J57" s="7">
         <v>1</v>
       </c>
       <c r="K57" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L57" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M57" s="15">
-        <v>0.15</v>
-      </c>
-      <c r="N57" s="15">
-        <f t="shared" si="2"/>
-        <v>0.75</v>
-      </c>
-      <c r="O57" s="9"/>
+      <c r="L57" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M57" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="N57" s="45">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="O57" s="7"/>
     </row>
     <row r="58" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="11">
-        <f>ROW(B58) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="C58" s="13" t="s">
+      <c r="C58" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D58" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="G58" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="H58" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="I58" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="J58" s="7">
+      <c r="D58" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E58" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="G58" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="I58" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="J58" s="9">
         <v>1</v>
       </c>
       <c r="K58" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L58" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M58" s="15">
+      <c r="L58" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M58" s="14">
         <v>0.1</v>
       </c>
-      <c r="N58" s="15">
+      <c r="N58" s="45">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="O58" s="7"/>
+      <c r="O58" s="9"/>
     </row>
     <row r="59" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B59) - ROW($B$2)</f>
         <v>57</v>
       </c>
-      <c r="C59" s="13" t="s">
+      <c r="C59" s="12" t="s">
         <v>17</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E59" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="F59" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="G59" s="10" t="s">
-        <v>263</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="I59" s="10" t="s">
-        <v>339</v>
-      </c>
-      <c r="J59" s="9">
-        <v>5</v>
+        <v>377</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="I59" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="J59" s="7">
+        <v>1</v>
       </c>
       <c r="K59" s="7">
         <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="L59" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M59" s="15">
+        <v>5</v>
+      </c>
+      <c r="L59" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M59" s="14">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="N59" s="15">
-        <f t="shared" si="2"/>
-        <v>0.375</v>
-      </c>
-      <c r="O59" s="9"/>
+      <c r="N59" s="45">
+        <f t="shared" si="2"/>
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="O59" s="7"/>
     </row>
     <row r="60" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="11">
-        <f>ROW(B60) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="C60" s="12" t="s">
+      <c r="C60" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D60" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="G60" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="H60" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="I60" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="J60" s="7">
+      <c r="D60" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="G60" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="H60" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="I60" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="J60" s="9">
         <v>1</v>
       </c>
       <c r="K60" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L60" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M60" s="15">
+      <c r="L60" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M60" s="14">
         <v>0.1</v>
       </c>
-      <c r="N60" s="15">
+      <c r="N60" s="45">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="O60" s="7"/>
+      <c r="O60" s="9"/>
     </row>
     <row r="61" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
@@ -4663,40 +4799,40 @@
       <c r="C61" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D61" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E61" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="F61" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="G61" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="I61" s="10" t="s">
-        <v>341</v>
-      </c>
-      <c r="J61" s="9">
-        <v>1</v>
+      <c r="D61" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="J61" s="7">
+        <v>2</v>
       </c>
       <c r="K61" s="7">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L61" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M61" s="15">
+        <v>10</v>
+      </c>
+      <c r="L61" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M61" s="14">
         <v>0.1</v>
       </c>
-      <c r="N61" s="15">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
+      <c r="N61" s="45">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="O61" s="9"/>
     </row>
@@ -4706,45 +4842,45 @@
         <f>ROW(B62) - ROW($B$2)</f>
         <v>60</v>
       </c>
-      <c r="C62" s="12" t="s">
+      <c r="C62" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D62" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="F62" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="G62" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="H62" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="I62" s="8" t="s">
-        <v>342</v>
-      </c>
-      <c r="J62" s="7">
-        <v>3</v>
+      <c r="D62" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="G62" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="H62" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="I62" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="J62" s="9">
+        <v>2</v>
       </c>
       <c r="K62" s="7">
         <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="L62" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M62" s="15">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="N62" s="15">
-        <f t="shared" si="2"/>
-        <v>0.22499999999999998</v>
-      </c>
-      <c r="O62" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="L62" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M62" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="N62" s="45">
+        <f>M62*K62</f>
+        <v>1</v>
+      </c>
+      <c r="O62" s="9"/>
     </row>
     <row r="63" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
@@ -4756,22 +4892,22 @@
         <v>17</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="E63" s="10" t="s">
-        <v>154</v>
+        <v>72</v>
+      </c>
+      <c r="E63" s="9" t="s">
+        <v>144</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>364</v>
+        <v>250</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>365</v>
+        <v>271</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>343</v>
+        <v>325</v>
       </c>
       <c r="J63" s="9">
         <v>1</v>
@@ -4780,13 +4916,13 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L63" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M63" s="15">
+      <c r="L63" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M63" s="14">
         <v>0.1</v>
       </c>
-      <c r="N63" s="15">
+      <c r="N63" s="45">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
@@ -4798,45 +4934,45 @@
         <f>ROW(B64) - ROW($B$2)</f>
         <v>62</v>
       </c>
-      <c r="C64" s="13" t="s">
+      <c r="C64" s="12" t="s">
         <v>17</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>391</v>
-      </c>
-      <c r="E64" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="F64" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="G64" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="H64" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="I64" s="10" t="s">
-        <v>349</v>
-      </c>
-      <c r="J64" s="9">
-        <v>3</v>
+        <v>360</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="H64" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="I64" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="J64" s="7">
+        <v>6</v>
       </c>
       <c r="K64" s="7">
-        <f>J64*5</f>
-        <v>15</v>
-      </c>
-      <c r="L64" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M64" s="15">
-        <v>0.1</v>
-      </c>
-      <c r="N64" s="15">
-        <f>M64*K64</f>
-        <v>1.5</v>
-      </c>
-      <c r="O64" s="9"/>
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="L64" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M64" s="14">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N64" s="45">
+        <f t="shared" si="2"/>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="O64" s="7"/>
     </row>
     <row r="65" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
@@ -4848,39 +4984,39 @@
         <v>17</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="E65" s="10" t="s">
-        <v>155</v>
+        <v>73</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>146</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="J65" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K65" s="7">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L65" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M65" s="15">
-        <v>0.1</v>
-      </c>
-      <c r="N65" s="15">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>10</v>
+      </c>
+      <c r="L65" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M65" s="14">
+        <v>1.9E-2</v>
+      </c>
+      <c r="N65" s="45">
+        <f t="shared" si="2"/>
+        <v>0.19</v>
       </c>
       <c r="O65" s="9"/>
     </row>
@@ -4893,40 +5029,40 @@
       <c r="C66" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D66" s="9" t="s">
-        <v>392</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>156</v>
+      <c r="D66" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>147</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="I66" s="8" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="J66" s="7">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K66" s="7">
         <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="L66" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M66" s="15">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="N66" s="15">
-        <f t="shared" si="2"/>
-        <v>0.44999999999999996</v>
+        <v>5</v>
+      </c>
+      <c r="L66" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M66" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="N66" s="45">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="O66" s="7"/>
     </row>
@@ -4940,85 +5076,85 @@
         <v>17</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="E67" s="10" t="s">
-        <v>157</v>
+        <v>75</v>
+      </c>
+      <c r="E67" s="9" t="s">
+        <v>148</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c r="J67" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K67" s="7">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L67" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M67" s="15">
-        <v>1.9E-2</v>
-      </c>
-      <c r="N67" s="15">
-        <f t="shared" si="2"/>
-        <v>0.19</v>
+        <v>5</v>
+      </c>
+      <c r="L67" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M67" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="N67" s="45">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="O67" s="9"/>
     </row>
     <row r="68" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
       <c r="B68" s="11">
-        <f>ROW(B68) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="C68" s="12" t="s">
+      <c r="C68" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D68" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="F68" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="G68" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="H68" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="I68" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="J68" s="7">
+      <c r="D68" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="E68" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="G68" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="H68" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="I68" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="J68" s="9">
         <v>1</v>
       </c>
       <c r="K68" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="K68:K90" si="3">J68*5</f>
         <v>5</v>
       </c>
-      <c r="L68" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M68" s="15">
-        <v>0.1</v>
-      </c>
-      <c r="N68" s="15">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
+      <c r="L68" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M68" s="14">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="N68" s="45">
+        <f t="shared" si="2"/>
+        <v>0.70000000000000007</v>
       </c>
       <c r="O68" s="7"/>
     </row>
@@ -5028,45 +5164,45 @@
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
-      <c r="C69" s="13" t="s">
+      <c r="C69" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D69" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="E69" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="F69" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="G69" s="10" t="s">
+      <c r="D69" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="G69" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="H69" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="H69" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="I69" s="10" t="s">
-        <v>347</v>
-      </c>
-      <c r="J69" s="9">
+      <c r="I69" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="J69" s="7">
         <v>1</v>
       </c>
       <c r="K69" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="L69" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M69" s="15">
+      <c r="L69" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M69" s="14">
         <v>0.1</v>
       </c>
-      <c r="N69" s="15">
+      <c r="N69" s="45">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="O69" s="9"/>
+      <c r="O69" s="7"/>
     </row>
     <row r="70" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
@@ -5078,37 +5214,37 @@
         <v>17</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E70" s="8" t="s">
-        <v>160</v>
+        <v>76</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>149</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="H70" s="7" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="J70" s="7">
         <v>2</v>
       </c>
       <c r="K70" s="7">
-        <f t="shared" ref="K70:K89" si="3">J70*5</f>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="L70" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M70" s="15">
+      <c r="L70" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M70" s="14">
         <v>9.4030000000000002E-2</v>
       </c>
-      <c r="N70" s="15">
+      <c r="N70" s="45">
         <f t="shared" si="2"/>
         <v>0.94030000000000002</v>
       </c>
@@ -5117,48 +5253,48 @@
     <row r="71" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
       <c r="B71" s="11">
-        <f>ROW(B71) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>69</v>
       </c>
       <c r="C71" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D71" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E71" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="F71" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="G71" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="H71" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="I71" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="J71" s="7">
-        <v>1</v>
+      <c r="D71" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E71" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="G71" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="H71" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="I71" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="J71" s="9">
+        <v>4</v>
       </c>
       <c r="K71" s="7">
         <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="L71" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M71" s="15">
-        <v>0.1</v>
-      </c>
-      <c r="N71" s="15">
-        <f t="shared" ref="N71:N89" si="4">M71*K71</f>
-        <v>0.5</v>
-      </c>
-      <c r="O71" s="7"/>
+        <v>20</v>
+      </c>
+      <c r="L71" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M71" s="14">
+        <v>1.9E-2</v>
+      </c>
+      <c r="N71" s="45">
+        <f t="shared" ref="N71:N90" si="4">M71*K71</f>
+        <v>0.38</v>
+      </c>
+      <c r="O71" s="9"/>
     </row>
     <row r="72" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
@@ -5169,854 +5305,880 @@
       <c r="C72" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D72" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E72" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="F72" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="G72" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="H72" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="I72" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="J72" s="9">
-        <v>4</v>
+      <c r="D72" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="H72" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="I72" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="J72" s="7">
+        <v>2</v>
       </c>
       <c r="K72" s="7">
         <f t="shared" si="3"/>
-        <v>20</v>
-      </c>
-      <c r="L72" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M72" s="15">
-        <v>1.9E-2</v>
-      </c>
-      <c r="N72" s="15">
+        <v>10</v>
+      </c>
+      <c r="L72" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M72" s="14">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="N72" s="45">
         <f t="shared" si="4"/>
-        <v>0.38</v>
-      </c>
-      <c r="O72" s="9"/>
+        <v>0.10999999999999999</v>
+      </c>
+      <c r="O72" s="7"/>
     </row>
     <row r="73" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B73) - ROW($B$2)</f>
         <v>71</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>400</v>
-      </c>
-      <c r="F73" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="G73" s="8" t="s">
-        <v>396</v>
-      </c>
-      <c r="H73" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="I73" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="J73" s="7">
-        <v>2</v>
+        <v>18</v>
+      </c>
+      <c r="D73" s="15" t="s">
+        <v>381</v>
+      </c>
+      <c r="E73" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="F73" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="G73" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="H73" s="15" t="s">
+        <v>336</v>
+      </c>
+      <c r="I73" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="J73" s="15">
+        <v>1</v>
       </c>
       <c r="K73" s="7">
         <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="L73" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M73" s="15">
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="N73" s="15">
-        <f t="shared" si="4"/>
-        <v>0.10999999999999999</v>
-      </c>
-      <c r="O73" s="7"/>
+        <v>5</v>
+      </c>
+      <c r="L73" s="39" t="s">
+        <v>336</v>
+      </c>
+      <c r="M73" s="17" t="s">
+        <v>336</v>
+      </c>
+      <c r="N73" s="46" t="s">
+        <v>336</v>
+      </c>
+      <c r="O73" s="15" t="s">
+        <v>347</v>
+      </c>
     </row>
     <row r="74" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="11">
-        <f>ROW(B74) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="C74" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D74" s="17" t="s">
-        <v>394</v>
-      </c>
-      <c r="E74" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="F74" s="17" t="s">
-        <v>360</v>
-      </c>
-      <c r="G74" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="H74" s="17" t="s">
-        <v>355</v>
-      </c>
-      <c r="I74" s="18" t="s">
-        <v>355</v>
-      </c>
-      <c r="J74" s="17">
+      <c r="C74" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E74" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="G74" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="H74" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="I74" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="J74" s="9">
         <v>2</v>
       </c>
-      <c r="K74" s="17">
+      <c r="K74" s="7">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="L74" s="19" t="s">
-        <v>355</v>
-      </c>
-      <c r="M74" s="20" t="s">
-        <v>355</v>
-      </c>
-      <c r="N74" s="20" t="s">
-        <v>355</v>
-      </c>
-      <c r="O74" s="17" t="s">
-        <v>366</v>
-      </c>
+      <c r="L74" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M74" s="14">
+        <v>0.98299999999999998</v>
+      </c>
+      <c r="N74" s="45">
+        <f t="shared" si="4"/>
+        <v>9.83</v>
+      </c>
+      <c r="O74" s="9"/>
     </row>
     <row r="75" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B75) - ROW($B$2)</f>
         <v>73</v>
       </c>
-      <c r="C75" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D75" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="E75" s="10" t="s">
-        <v>165</v>
+      <c r="C75" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E75" s="7" t="s">
+        <v>154</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="G75" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>306</v>
+        <v>341</v>
+      </c>
+      <c r="G75" s="8">
+        <v>760390015</v>
+      </c>
+      <c r="H75" s="7" t="s">
+        <v>288</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="J75" s="9">
-        <v>2</v>
+        <v>336</v>
+      </c>
+      <c r="J75" s="7">
+        <v>1</v>
       </c>
       <c r="K75" s="7">
         <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="L75" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M75" s="15">
-        <v>0.98299999999999998</v>
-      </c>
-      <c r="N75" s="15">
+        <v>5</v>
+      </c>
+      <c r="L75" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M75" s="14">
+        <v>1.9</v>
+      </c>
+      <c r="N75" s="45">
         <f t="shared" si="4"/>
-        <v>9.83</v>
-      </c>
-      <c r="O75" s="9"/>
-    </row>
-    <row r="76" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>9.5</v>
+      </c>
+      <c r="O75" s="7"/>
+    </row>
+    <row r="76" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="11">
-        <f>ROW(B76) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>74</v>
       </c>
-      <c r="C76" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E76" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="F76" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="G76" s="8">
-        <v>760390015</v>
-      </c>
-      <c r="H76" s="7" t="s">
-        <v>307</v>
+      <c r="C76" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E76" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="F76" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="G76" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="H76" s="9" t="s">
+        <v>289</v>
       </c>
       <c r="I76" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="J76" s="7">
+        <v>336</v>
+      </c>
+      <c r="J76" s="9">
         <v>1</v>
       </c>
       <c r="K76" s="7">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="L76" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M76" s="15">
-        <v>1.9</v>
-      </c>
-      <c r="N76" s="15">
+      <c r="L76" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M76" s="14">
+        <v>6.11</v>
+      </c>
+      <c r="N76" s="45">
         <f t="shared" si="4"/>
-        <v>9.5</v>
-      </c>
-      <c r="O76" s="7"/>
-    </row>
-    <row r="77" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>30.55</v>
+      </c>
+      <c r="O76" s="9"/>
+    </row>
+    <row r="77" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B77) - ROW($B$2)</f>
         <v>75</v>
       </c>
-      <c r="C77" s="13" t="s">
+      <c r="C77" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D77" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="E77" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="F77" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="G77" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>308</v>
+      <c r="D77" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="G77" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="H77" s="7" t="s">
+        <v>285</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="J77" s="9">
+        <v>336</v>
+      </c>
+      <c r="J77" s="7">
         <v>1</v>
       </c>
       <c r="K77" s="7">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="L77" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M77" s="15">
-        <v>6.11</v>
-      </c>
-      <c r="N77" s="15">
+      <c r="L77" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M77" s="14">
+        <v>2.41</v>
+      </c>
+      <c r="N77" s="45">
         <f t="shared" si="4"/>
-        <v>30.55</v>
-      </c>
-      <c r="O77" s="9"/>
+        <v>12.05</v>
+      </c>
+      <c r="O77" s="7"/>
     </row>
     <row r="78" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="11">
-        <f>ROW(B78) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>76</v>
       </c>
-      <c r="C78" s="12" t="s">
+      <c r="C78" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D78" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E78" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="F78" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="G78" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="H78" s="7" t="s">
-        <v>303</v>
+      <c r="D78" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E78" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="G78" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="H78" s="9" t="s">
+        <v>285</v>
       </c>
       <c r="I78" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="J78" s="7">
+        <v>336</v>
+      </c>
+      <c r="J78" s="9">
         <v>1</v>
       </c>
       <c r="K78" s="7">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="L78" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M78" s="15">
-        <v>2.41</v>
-      </c>
-      <c r="N78" s="15">
+      <c r="L78" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M78" s="14">
+        <v>1.43</v>
+      </c>
+      <c r="N78" s="45">
         <f t="shared" si="4"/>
-        <v>12.05</v>
-      </c>
-      <c r="O78" s="7"/>
+        <v>7.1499999999999995</v>
+      </c>
+      <c r="O78" s="9"/>
     </row>
     <row r="79" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B79) - ROW($B$2)</f>
         <v>77</v>
       </c>
-      <c r="C79" s="13" t="s">
+      <c r="C79" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D79" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E79" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="F79" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="G79" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>303</v>
+      <c r="D79" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="G79" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="H79" s="7" t="s">
+        <v>285</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="J79" s="9">
+        <v>336</v>
+      </c>
+      <c r="J79" s="7">
         <v>1</v>
       </c>
       <c r="K79" s="7">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="L79" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M79" s="15">
-        <v>1.43</v>
-      </c>
-      <c r="N79" s="15">
+      <c r="L79" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M79" s="14">
+        <v>2.27</v>
+      </c>
+      <c r="N79" s="45">
         <f t="shared" si="4"/>
-        <v>7.1499999999999995</v>
-      </c>
-      <c r="O79" s="9"/>
+        <v>11.35</v>
+      </c>
+      <c r="O79" s="7"/>
     </row>
     <row r="80" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="11">
-        <f>ROW(B80) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>78</v>
       </c>
-      <c r="C80" s="12" t="s">
+      <c r="C80" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D80" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="E80" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="F80" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="G80" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="H80" s="7" t="s">
-        <v>303</v>
+      <c r="D80" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E80" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="G80" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="H80" s="9" t="s">
+        <v>285</v>
       </c>
       <c r="I80" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="J80" s="7">
+        <v>336</v>
+      </c>
+      <c r="J80" s="9">
         <v>1</v>
       </c>
       <c r="K80" s="7">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="L80" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M80" s="15">
-        <v>2.27</v>
-      </c>
-      <c r="N80" s="15">
+      <c r="L80" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M80" s="14">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="N80" s="45">
         <f t="shared" si="4"/>
-        <v>11.35</v>
-      </c>
-      <c r="O80" s="7"/>
-    </row>
-    <row r="81" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>5.8</v>
+      </c>
+      <c r="O80" s="9"/>
+    </row>
+    <row r="81" spans="1:22" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B81) - ROW($B$2)</f>
         <v>79</v>
       </c>
       <c r="C81" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D81" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="E81" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F81" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="G81" s="10" t="s">
-        <v>280</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>303</v>
+      <c r="D81" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="G81" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="H81" s="7" t="s">
+        <v>290</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="J81" s="9">
+        <v>336</v>
+      </c>
+      <c r="J81" s="7">
         <v>1</v>
       </c>
       <c r="K81" s="7">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="L81" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M81" s="15">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="N81" s="15">
+      <c r="L81" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M81" s="14">
+        <v>4.66</v>
+      </c>
+      <c r="N81" s="45">
         <f t="shared" si="4"/>
-        <v>5.8</v>
-      </c>
-      <c r="O81" s="9"/>
-    </row>
-    <row r="82" spans="1:20" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>23.3</v>
+      </c>
+      <c r="O81" s="7"/>
+    </row>
+    <row r="82" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="11">
-        <f>ROW(B82) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>80</v>
       </c>
       <c r="C82" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D82" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="E82" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="F82" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="G82" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="H82" s="7" t="s">
-        <v>309</v>
+      <c r="D82" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="E82" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="F82" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="G82" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="H82" s="9" t="s">
+        <v>291</v>
       </c>
       <c r="I82" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="J82" s="7">
+        <v>336</v>
+      </c>
+      <c r="J82" s="9">
         <v>1</v>
       </c>
       <c r="K82" s="7">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="L82" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M82" s="15">
-        <v>4.66</v>
-      </c>
-      <c r="N82" s="15">
+      <c r="L82" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M82" s="14">
+        <v>3</v>
+      </c>
+      <c r="N82" s="45">
         <f t="shared" si="4"/>
-        <v>23.3</v>
-      </c>
-      <c r="O82" s="7"/>
-    </row>
-    <row r="83" spans="1:20" s="22" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="21"/>
+        <v>15</v>
+      </c>
+      <c r="O82" s="9"/>
+    </row>
+    <row r="83" spans="1:22" s="19" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="18"/>
       <c r="B83" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B83) - ROW($B$2)</f>
         <v>81</v>
       </c>
       <c r="C83" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D83" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="E83" s="10" t="s">
-        <v>173</v>
+      <c r="D83" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>162</v>
       </c>
       <c r="F83" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="G83" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>310</v>
+        <v>341</v>
+      </c>
+      <c r="G83" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="H83" s="7" t="s">
+        <v>292</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="J83" s="9">
+        <v>336</v>
+      </c>
+      <c r="J83" s="7">
         <v>1</v>
       </c>
       <c r="K83" s="7">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="L83" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M83" s="15">
-        <v>3</v>
-      </c>
-      <c r="N83" s="15">
+      <c r="L83" s="38" t="s">
+        <v>349</v>
+      </c>
+      <c r="M83" s="14">
+        <v>2.6663999999999999</v>
+      </c>
+      <c r="N83" s="45">
         <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="O83" s="9"/>
+        <v>13.331999999999999</v>
+      </c>
+      <c r="O83" s="7"/>
       <c r="P83"/>
       <c r="Q83"/>
       <c r="R83"/>
       <c r="S83"/>
       <c r="T83"/>
-    </row>
-    <row r="84" spans="1:20" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U83"/>
+      <c r="V83"/>
+    </row>
+    <row r="84" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="11">
-        <f>ROW(B84) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>82</v>
       </c>
       <c r="C84" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D84" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="E84" s="8" t="s">
-        <v>174</v>
+      <c r="D84" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E84" s="9" t="s">
+        <v>163</v>
       </c>
       <c r="F84" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="G84" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="H84" s="7" t="s">
-        <v>311</v>
+        <v>202</v>
+      </c>
+      <c r="G84" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="H84" s="9" t="s">
+        <v>285</v>
       </c>
       <c r="I84" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="J84" s="7">
+        <v>336</v>
+      </c>
+      <c r="J84" s="9">
         <v>1</v>
       </c>
       <c r="K84" s="7">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="L84" s="16" t="s">
-        <v>368</v>
-      </c>
-      <c r="M84" s="15">
-        <v>2.6663999999999999</v>
-      </c>
-      <c r="N84" s="15">
+      <c r="L84" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M84" s="14">
+        <v>4.51</v>
+      </c>
+      <c r="N84" s="45">
         <f t="shared" si="4"/>
-        <v>13.331999999999999</v>
-      </c>
-      <c r="O84" s="7"/>
-    </row>
-    <row r="85" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>22.549999999999997</v>
+      </c>
+      <c r="O84" s="9"/>
+    </row>
+    <row r="85" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B85) - ROW($B$2)</f>
         <v>83</v>
       </c>
-      <c r="C85" s="13" t="s">
+      <c r="C85" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D85" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E85" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F85" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="G85" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>303</v>
+      <c r="D85" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="G85" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="H85" s="7" t="s">
+        <v>285</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="J85" s="9">
-        <v>1</v>
+        <v>336</v>
+      </c>
+      <c r="J85" s="7">
+        <v>4</v>
       </c>
       <c r="K85" s="7">
         <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="L85" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M85" s="15">
-        <v>4.51</v>
-      </c>
-      <c r="N85" s="15">
+        <v>20</v>
+      </c>
+      <c r="L85" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M85" s="14">
+        <v>0.68</v>
+      </c>
+      <c r="N85" s="45">
         <f t="shared" si="4"/>
-        <v>22.549999999999997</v>
-      </c>
-      <c r="O85" s="9"/>
-    </row>
-    <row r="86" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>13.600000000000001</v>
+      </c>
+      <c r="O85" s="7"/>
+    </row>
+    <row r="86" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="11">
-        <f>ROW(B86) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>84</v>
       </c>
-      <c r="C86" s="12" t="s">
+      <c r="C86" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D86" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="E86" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="F86" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="G86" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="H86" s="7" t="s">
-        <v>303</v>
+      <c r="D86" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E86" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="F86" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="G86" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="H86" s="9" t="s">
+        <v>285</v>
       </c>
       <c r="I86" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="J86" s="7">
-        <v>4</v>
+        <v>336</v>
+      </c>
+      <c r="J86" s="9">
+        <v>2</v>
       </c>
       <c r="K86" s="7">
         <f t="shared" si="3"/>
-        <v>20</v>
-      </c>
-      <c r="L86" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M86" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="N86" s="15">
+        <v>10</v>
+      </c>
+      <c r="L86" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M86" s="14">
+        <v>5.2880000000000003</v>
+      </c>
+      <c r="N86" s="45">
         <f t="shared" si="4"/>
-        <v>13.600000000000001</v>
-      </c>
-      <c r="O86" s="7"/>
-    </row>
-    <row r="87" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>52.88</v>
+      </c>
+      <c r="O86" s="9"/>
+    </row>
+    <row r="87" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B87) - ROW($B$2)</f>
         <v>85</v>
       </c>
-      <c r="C87" s="13" t="s">
+      <c r="C87" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D87" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="E87" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="F87" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="G87" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>303</v>
+      <c r="D87" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="G87" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="H87" s="7" t="s">
+        <v>285</v>
       </c>
       <c r="I87" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="J87" s="9">
-        <v>2</v>
+        <v>336</v>
+      </c>
+      <c r="J87" s="7">
+        <v>1</v>
       </c>
       <c r="K87" s="7">
         <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="L87" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M87" s="15">
-        <v>5.2880000000000003</v>
-      </c>
-      <c r="N87" s="15">
+        <v>5</v>
+      </c>
+      <c r="L87" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="M87" s="14">
+        <v>0.95</v>
+      </c>
+      <c r="N87" s="45">
         <f t="shared" si="4"/>
-        <v>52.88</v>
-      </c>
-      <c r="O87" s="9"/>
-    </row>
-    <row r="88" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>4.75</v>
+      </c>
+      <c r="O87" s="7"/>
+    </row>
+    <row r="88" spans="1:22" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="11">
         <f>ROW(B88) - ROW($B$2)</f>
         <v>86</v>
       </c>
-      <c r="C88" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D88" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="E88" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="F88" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="G88" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="H88" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="I88" s="8" t="s">
+      <c r="C88" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="D88" s="23" t="s">
+        <v>336</v>
+      </c>
+      <c r="E88" s="23" t="s">
         <v>355</v>
       </c>
-      <c r="J88" s="7">
-        <v>1</v>
+      <c r="F88" s="23" t="s">
+        <v>336</v>
+      </c>
+      <c r="G88" s="22" t="s">
+        <v>356</v>
+      </c>
+      <c r="H88" s="23" t="s">
+        <v>357</v>
+      </c>
+      <c r="I88" s="22" t="s">
+        <v>336</v>
+      </c>
+      <c r="J88" s="23">
+        <v>2</v>
       </c>
       <c r="K88" s="7">
         <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="L88" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M88" s="15">
-        <v>0.95</v>
-      </c>
-      <c r="N88" s="15">
+        <v>10</v>
+      </c>
+      <c r="L88" s="40" t="s">
+        <v>337</v>
+      </c>
+      <c r="M88" s="24">
+        <v>0.35</v>
+      </c>
+      <c r="N88" s="47">
         <f t="shared" si="4"/>
-        <v>4.75</v>
-      </c>
-      <c r="O88" s="7"/>
-    </row>
-    <row r="89" spans="1:20" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>3.5</v>
+      </c>
+      <c r="O88" s="23"/>
+    </row>
+    <row r="89" spans="1:22" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="11">
-        <f>ROW(B89) - ROW($B$2)</f>
+        <f t="shared" ref="B89:B90" si="5">ROW(B89) - ROW($B$2)</f>
         <v>87</v>
       </c>
-      <c r="C89" s="25" t="s">
-        <v>376</v>
-      </c>
-      <c r="D89" s="26" t="s">
-        <v>355</v>
-      </c>
-      <c r="E89" s="27" t="s">
-        <v>377</v>
-      </c>
-      <c r="F89" s="26" t="s">
-        <v>355</v>
-      </c>
-      <c r="G89" s="27" t="s">
-        <v>378</v>
-      </c>
-      <c r="H89" s="26" t="s">
-        <v>379</v>
-      </c>
-      <c r="I89" s="27" t="s">
-        <v>355</v>
-      </c>
-      <c r="J89" s="26">
-        <v>2</v>
+      <c r="C89" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="E89" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="F89" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="G89" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="H89" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="I89" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="J89" s="9">
+        <v>1</v>
       </c>
       <c r="K89" s="7">
         <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="L89" s="28" t="s">
-        <v>356</v>
-      </c>
-      <c r="M89" s="29">
-        <v>0.35</v>
-      </c>
-      <c r="N89" s="29">
+        <v>5</v>
+      </c>
+      <c r="L89" s="41" t="s">
+        <v>349</v>
+      </c>
+      <c r="M89" s="43">
+        <v>1.5257000000000001</v>
+      </c>
+      <c r="N89" s="48">
         <f t="shared" si="4"/>
-        <v>3.5</v>
-      </c>
-      <c r="O89" s="26"/>
-    </row>
-    <row r="90" spans="1:20" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>7.6285000000000007</v>
+      </c>
+      <c r="O89" s="9"/>
+    </row>
+    <row r="90" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
-      <c r="B90" s="1"/>
-      <c r="C90" s="1"/>
-      <c r="D90" s="1"/>
-      <c r="E90" s="1"/>
-      <c r="F90" s="1"/>
-      <c r="G90" s="1"/>
-      <c r="H90" s="1"/>
-      <c r="I90" s="1"/>
-      <c r="J90" s="1"/>
-      <c r="K90" s="31" t="s">
-        <v>369</v>
-      </c>
-      <c r="L90" s="32"/>
-      <c r="M90" s="33"/>
-      <c r="N90" s="24">
-        <f>SUM(N10:N89)</f>
-        <v>601.46579999999994</v>
-      </c>
-      <c r="O90" s="1"/>
-    </row>
-    <row r="91" spans="1:20" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B90" s="11">
+        <f t="shared" si="5"/>
+        <v>88</v>
+      </c>
+      <c r="C90" s="32" t="s">
+        <v>354</v>
+      </c>
+      <c r="D90" s="34" t="s">
+        <v>336</v>
+      </c>
+      <c r="E90" s="34" t="s">
+        <v>401</v>
+      </c>
+      <c r="F90" s="34" t="s">
+        <v>336</v>
+      </c>
+      <c r="G90" s="35" t="s">
+        <v>402</v>
+      </c>
+      <c r="H90" s="34" t="s">
+        <v>403</v>
+      </c>
+      <c r="I90" s="35" t="s">
+        <v>336</v>
+      </c>
+      <c r="J90" s="34">
+        <v>1</v>
+      </c>
+      <c r="K90" s="33">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="L90" s="42" t="s">
+        <v>349</v>
+      </c>
+      <c r="M90" s="44">
+        <v>1.2457</v>
+      </c>
+      <c r="N90" s="49">
+        <f t="shared" si="4"/>
+        <v>6.2285000000000004</v>
+      </c>
+      <c r="O90" s="34"/>
+    </row>
+    <row r="91" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -6027,25 +6189,50 @@
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
       <c r="J91" s="1"/>
-      <c r="K91" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="L91" s="35"/>
-      <c r="M91" s="36"/>
-      <c r="N91" s="23">
-        <f>N90/5</f>
-        <v>120.29315999999999</v>
+      <c r="K91" s="26" t="s">
+        <v>350</v>
+      </c>
+      <c r="L91" s="27"/>
+      <c r="M91" s="28"/>
+      <c r="N91" s="21">
+        <f>SUM(N10:N90)</f>
+        <v>536.35930000000008</v>
       </c>
       <c r="O91" s="1"/>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
+      <c r="B92" s="1"/>
+      <c r="C92" s="1"/>
+      <c r="D92" s="1"/>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1"/>
+      <c r="G92" s="1"/>
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
+      <c r="J92" s="1"/>
+      <c r="K92" s="29" t="s">
+        <v>348</v>
+      </c>
+      <c r="L92" s="30"/>
+      <c r="M92" s="31"/>
+      <c r="N92" s="20">
+        <f>N91/5</f>
+        <v>107.27186000000002</v>
+      </c>
+      <c r="O92" s="1"/>
+    </row>
+    <row r="93" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A93" s="1"/>
+    </row>
+    <row r="94" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A94" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="I1:O1"/>
-    <mergeCell ref="K90:M90"/>
     <mergeCell ref="K91:M91"/>
+    <mergeCell ref="K92:M92"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="L3" r:id="rId1"/>
@@ -6064,45 +6251,45 @@
     <hyperlink ref="L16" r:id="rId14"/>
     <hyperlink ref="L17" r:id="rId15"/>
     <hyperlink ref="L18" r:id="rId16"/>
-    <hyperlink ref="L20" r:id="rId17"/>
-    <hyperlink ref="L21" r:id="rId18"/>
-    <hyperlink ref="L22" r:id="rId19"/>
-    <hyperlink ref="L23" r:id="rId20"/>
-    <hyperlink ref="L24" r:id="rId21"/>
-    <hyperlink ref="L25" r:id="rId22"/>
-    <hyperlink ref="L27" r:id="rId23"/>
-    <hyperlink ref="L28" r:id="rId24"/>
-    <hyperlink ref="L31" r:id="rId25"/>
-    <hyperlink ref="L38" r:id="rId26"/>
-    <hyperlink ref="L39" r:id="rId27"/>
-    <hyperlink ref="L40" r:id="rId28"/>
-    <hyperlink ref="L45" r:id="rId29"/>
-    <hyperlink ref="L46" r:id="rId30"/>
-    <hyperlink ref="L47" r:id="rId31"/>
-    <hyperlink ref="L49" r:id="rId32"/>
-    <hyperlink ref="L50" r:id="rId33"/>
-    <hyperlink ref="L51" r:id="rId34"/>
-    <hyperlink ref="L52" r:id="rId35"/>
-    <hyperlink ref="L53" r:id="rId36"/>
-    <hyperlink ref="L54" r:id="rId37"/>
-    <hyperlink ref="L55" r:id="rId38"/>
-    <hyperlink ref="L56" r:id="rId39"/>
-    <hyperlink ref="L57" r:id="rId40"/>
-    <hyperlink ref="L58" r:id="rId41"/>
-    <hyperlink ref="L59" r:id="rId42"/>
-    <hyperlink ref="L60" r:id="rId43"/>
-    <hyperlink ref="L61" r:id="rId44"/>
-    <hyperlink ref="L62" r:id="rId45"/>
-    <hyperlink ref="L63" r:id="rId46"/>
-    <hyperlink ref="L65" r:id="rId47"/>
-    <hyperlink ref="L66" r:id="rId48"/>
-    <hyperlink ref="L67" r:id="rId49"/>
-    <hyperlink ref="L68" r:id="rId50"/>
-    <hyperlink ref="L69" r:id="rId51"/>
+    <hyperlink ref="L19" r:id="rId17"/>
+    <hyperlink ref="L20" r:id="rId18"/>
+    <hyperlink ref="L21" r:id="rId19"/>
+    <hyperlink ref="L22" r:id="rId20"/>
+    <hyperlink ref="L23" r:id="rId21"/>
+    <hyperlink ref="L24" r:id="rId22"/>
+    <hyperlink ref="L26" r:id="rId23"/>
+    <hyperlink ref="L27" r:id="rId24"/>
+    <hyperlink ref="L29" r:id="rId25"/>
+    <hyperlink ref="L36" r:id="rId26"/>
+    <hyperlink ref="L37" r:id="rId27"/>
+    <hyperlink ref="L38" r:id="rId28"/>
+    <hyperlink ref="L43" r:id="rId29"/>
+    <hyperlink ref="L44" r:id="rId30"/>
+    <hyperlink ref="L45" r:id="rId31"/>
+    <hyperlink ref="L46" r:id="rId32"/>
+    <hyperlink ref="L47" r:id="rId33"/>
+    <hyperlink ref="L48" r:id="rId34"/>
+    <hyperlink ref="L49" r:id="rId35"/>
+    <hyperlink ref="L50" r:id="rId36"/>
+    <hyperlink ref="L51" r:id="rId37"/>
+    <hyperlink ref="L52" r:id="rId38"/>
+    <hyperlink ref="L53" r:id="rId39"/>
+    <hyperlink ref="L54" r:id="rId40"/>
+    <hyperlink ref="L55" r:id="rId41"/>
+    <hyperlink ref="L56" r:id="rId42"/>
+    <hyperlink ref="L57" r:id="rId43"/>
+    <hyperlink ref="L58" r:id="rId44"/>
+    <hyperlink ref="L59" r:id="rId45"/>
+    <hyperlink ref="L60" r:id="rId46"/>
+    <hyperlink ref="L63" r:id="rId47"/>
+    <hyperlink ref="L64" r:id="rId48"/>
+    <hyperlink ref="L65" r:id="rId49"/>
+    <hyperlink ref="L66" r:id="rId50"/>
+    <hyperlink ref="L67" r:id="rId51"/>
     <hyperlink ref="L70" r:id="rId52"/>
-    <hyperlink ref="L64" r:id="rId53"/>
+    <hyperlink ref="L62" r:id="rId53"/>
     <hyperlink ref="L71" r:id="rId54"/>
-    <hyperlink ref="L72" r:id="rId55"/>
+    <hyperlink ref="L74" r:id="rId55"/>
     <hyperlink ref="L75" r:id="rId56"/>
     <hyperlink ref="L76" r:id="rId57"/>
     <hyperlink ref="L77" r:id="rId58"/>
@@ -6111,31 +6298,32 @@
     <hyperlink ref="L80" r:id="rId61"/>
     <hyperlink ref="L81" r:id="rId62"/>
     <hyperlink ref="L82" r:id="rId63"/>
-    <hyperlink ref="L83" r:id="rId64"/>
+    <hyperlink ref="L84" r:id="rId64"/>
     <hyperlink ref="L85" r:id="rId65"/>
     <hyperlink ref="L86" r:id="rId66"/>
     <hyperlink ref="L87" r:id="rId67"/>
-    <hyperlink ref="L88" r:id="rId68"/>
-    <hyperlink ref="L26" r:id="rId69"/>
-    <hyperlink ref="L32" r:id="rId70"/>
-    <hyperlink ref="L34" r:id="rId71"/>
-    <hyperlink ref="L36" r:id="rId72"/>
-    <hyperlink ref="L37" r:id="rId73"/>
-    <hyperlink ref="L41" r:id="rId74"/>
-    <hyperlink ref="L42" r:id="rId75"/>
-    <hyperlink ref="L43" r:id="rId76"/>
-    <hyperlink ref="L44" r:id="rId77"/>
-    <hyperlink ref="L48" r:id="rId78"/>
-    <hyperlink ref="L84" r:id="rId79"/>
-    <hyperlink ref="L33" r:id="rId80"/>
-    <hyperlink ref="L35" r:id="rId81"/>
-    <hyperlink ref="L89" r:id="rId82"/>
-    <hyperlink ref="L19" r:id="rId83"/>
-    <hyperlink ref="L29" r:id="rId84"/>
-    <hyperlink ref="L30" r:id="rId85"/>
-    <hyperlink ref="L73" r:id="rId86"/>
+    <hyperlink ref="L25" r:id="rId68"/>
+    <hyperlink ref="L32" r:id="rId69"/>
+    <hyperlink ref="L39" r:id="rId70"/>
+    <hyperlink ref="L40" r:id="rId71"/>
+    <hyperlink ref="L41" r:id="rId72"/>
+    <hyperlink ref="L42" r:id="rId73"/>
+    <hyperlink ref="L83" r:id="rId74"/>
+    <hyperlink ref="L33" r:id="rId75"/>
+    <hyperlink ref="L88" r:id="rId76"/>
+    <hyperlink ref="L28" r:id="rId77"/>
+    <hyperlink ref="L72" r:id="rId78"/>
+    <hyperlink ref="L34" r:id="rId79"/>
+    <hyperlink ref="L35" r:id="rId80"/>
+    <hyperlink ref="L68" r:id="rId81"/>
+    <hyperlink ref="L69" r:id="rId82"/>
+    <hyperlink ref="L30" r:id="rId83"/>
+    <hyperlink ref="L31" r:id="rId84"/>
+    <hyperlink ref="L61" r:id="rId85"/>
+    <hyperlink ref="L89" r:id="rId86"/>
+    <hyperlink ref="L90" r:id="rId87"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId87"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId88"/>
 </worksheet>
 </file>
--- a/Design-Files/FMM-v1.0/BOM/Client-BOM-FMM-v1.0.xlsx
+++ b/Design-Files/FMM-v1.0/BOM/Client-BOM-FMM-v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="432">
   <si>
     <t>#</t>
   </si>
@@ -1185,52 +1185,136 @@
     <t>22R</t>
   </si>
   <si>
-    <t>C2, C5, C9, C14, C15, C18, C19, C22, C27, C29, C31, C34, C36, C37, C39, C46, C49, C50, C51, C53, C54, C57, C59</t>
-  </si>
-  <si>
     <t>C8, C38</t>
   </si>
   <si>
-    <t>R2</t>
-  </si>
-  <si>
     <t>R16, R30</t>
   </si>
   <si>
-    <t>MC-318FB</t>
-  </si>
-  <si>
     <t>RC0402FR-075K1L</t>
   </si>
   <si>
-    <t>USB 3.0 3A 1 Brick nogging 24 Female -35℃~+75℃ Type-C SMD USB Connectors ROHS</t>
-  </si>
-  <si>
-    <t>SOFNG</t>
-  </si>
-  <si>
     <t>RES 5.1K OHM 1% 1/16W 0402</t>
   </si>
   <si>
     <t>5.1K</t>
   </si>
   <si>
-    <t>18cm SMA to IPEX 4Gen - Radio Frequency Cable ROHS</t>
-  </si>
-  <si>
-    <t>KH-FL2SMAK-IPEX4-RG0.81-B180</t>
-  </si>
-  <si>
     <t>Shenzhen Kinghelm Elec</t>
   </si>
   <si>
-    <t>5dBi - Antennas ROHS</t>
-  </si>
-  <si>
-    <t>HJ-2.4GHz 5dBi-SMA</t>
-  </si>
-  <si>
     <t>HJ Tech</t>
+  </si>
+  <si>
+    <t>CC0402JRX7R7BB223</t>
+  </si>
+  <si>
+    <t>CC0402JRX7R7BB104</t>
+  </si>
+  <si>
+    <t>CC0402JRX7R7BB153</t>
+  </si>
+  <si>
+    <t>TYPE-C-31-D-07</t>
+  </si>
+  <si>
+    <t>RT0402BRE0727KL</t>
+  </si>
+  <si>
+    <t>RT0402BRD078K2L</t>
+  </si>
+  <si>
+    <t>RT0402BRD0722K1L</t>
+  </si>
+  <si>
+    <t>OPA350UA/2K5</t>
+  </si>
+  <si>
+    <t>C2, C5, C9, C14, C15, C18, C19, C22, C27, C29, C31, C34, C36, C37, C39, C46, C49, C50, C51, C53, C54, C56, C57, C59, C61, C67, C68, C74, C75, C81, C82</t>
+  </si>
+  <si>
+    <t>C62, C63, C64, C69, C70, C71, C76, C77, C78, C83, C84, C85</t>
+  </si>
+  <si>
+    <t>C65, C72, C79, C86</t>
+  </si>
+  <si>
+    <t>C66, C73, C80, C87</t>
+  </si>
+  <si>
+    <t>R46, R52, R58, R64</t>
+  </si>
+  <si>
+    <t>R47, R48, R53, R54, R59, R60, R65, R66</t>
+  </si>
+  <si>
+    <t>R49, R50, R55, R56, R61, R62, R67, R68</t>
+  </si>
+  <si>
+    <t>U17, U18, U19, U20, U21, U22, U23, U24</t>
+  </si>
+  <si>
+    <t>CAP CER 0.022UF 16V X7R 0402</t>
+  </si>
+  <si>
+    <t>CAP CER 0.1UF 16V X7R 0402</t>
+  </si>
+  <si>
+    <t>CAP CER 0.015UF 16V X7R 0402</t>
+  </si>
+  <si>
+    <t>15nF</t>
+  </si>
+  <si>
+    <t>RES SMD 27K OHM 0.1% 1/16W 0402</t>
+  </si>
+  <si>
+    <t>27K</t>
+  </si>
+  <si>
+    <t>RES SMD 8.2K OHM 0.1% 1/16W 0402</t>
+  </si>
+  <si>
+    <t>8.2K</t>
+  </si>
+  <si>
+    <t>RES SMD 22.1KOHM 0.1% 1/16W 0402</t>
+  </si>
+  <si>
+    <t>IC OPAMP GP 1 CIRCUIT 8SOIC</t>
+  </si>
+  <si>
+    <t>SOIC-8(0.154", 3.90mm Width)</t>
+  </si>
+  <si>
+    <t>1 Brick nogging 14P Female Type-C SMD USB Connectors ROHS</t>
+  </si>
+  <si>
+    <t>Korean Hroparts Elec</t>
+  </si>
+  <si>
+    <t>KHB135-38(11)-28-A/3</t>
+  </si>
+  <si>
+    <t>13.5cm IPEX to SMA 1Gen - Radio Frequency Cable ROHS</t>
+  </si>
+  <si>
+    <t>HJ-2.4GHz 3dBi-SMA</t>
+  </si>
+  <si>
+    <t>3dBi - Antennas ROHS</t>
+  </si>
+  <si>
+    <t>C88</t>
+  </si>
+  <si>
+    <t>CAP CER 4700PF 1KV X7R 1206</t>
+  </si>
+  <si>
+    <t>CC1206KKX7RCBB472</t>
+  </si>
+  <si>
+    <t>R2, R69</t>
   </si>
 </sst>
 </file>
@@ -1600,7 +1684,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1670,37 +1754,7 @@
     <xf numFmtId="164" fontId="4" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1750,6 +1804,33 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2039,7 +2120,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:V94"/>
+  <dimension ref="A1:W100"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="4" customWidth="1"/>
@@ -2069,13 +2150,13 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="42"/>
     </row>
     <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2109,7 +2190,7 @@
       <c r="K2" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="L2" s="36" t="s">
+      <c r="L2" s="28" t="s">
         <v>335</v>
       </c>
       <c r="M2" s="5" t="s">
@@ -2156,29 +2237,29 @@
         <f>J3*5</f>
         <v>45</v>
       </c>
-      <c r="L3" s="37" t="s">
+      <c r="L3" s="29" t="s">
         <v>337</v>
       </c>
       <c r="M3" s="14">
         <v>0.124</v>
       </c>
-      <c r="N3" s="45">
+      <c r="N3" s="37">
         <f>M3*K3</f>
         <v>5.58</v>
       </c>
       <c r="O3" s="7"/>
     </row>
-    <row r="4" spans="1:15" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="11">
-        <f t="shared" ref="B4:B86" si="0">ROW(B4) - ROW($B$2)</f>
+        <f t="shared" ref="B4:B93" si="0">ROW(B4) - ROW($B$2)</f>
         <v>2</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>94</v>
@@ -2196,21 +2277,21 @@
         <v>294</v>
       </c>
       <c r="J4" s="9">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="K4" s="7">
-        <f t="shared" ref="K4:K67" si="1">J4*5</f>
-        <v>115</v>
-      </c>
-      <c r="L4" s="38" t="s">
+        <f t="shared" ref="K4:K68" si="1">J4*5</f>
+        <v>155</v>
+      </c>
+      <c r="L4" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M4" s="14">
         <v>1.9400000000000001E-2</v>
       </c>
-      <c r="N4" s="45">
-        <f t="shared" ref="N4:N70" si="2">M4*K4</f>
-        <v>2.2309999999999999</v>
+      <c r="N4" s="37">
+        <f t="shared" ref="N4:N74" si="2">M4*K4</f>
+        <v>3.0070000000000001</v>
       </c>
       <c r="O4" s="9"/>
     </row>
@@ -2248,13 +2329,13 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L5" s="38" t="s">
+      <c r="L5" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M5" s="14">
         <v>0.92100000000000004</v>
       </c>
-      <c r="N5" s="45">
+      <c r="N5" s="37">
         <f t="shared" si="2"/>
         <v>9.2100000000000009</v>
       </c>
@@ -2294,13 +2375,13 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L6" s="38" t="s">
+      <c r="L6" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M6" s="14">
         <v>1.0389999999999999</v>
       </c>
-      <c r="N6" s="45">
+      <c r="N6" s="37">
         <f t="shared" si="2"/>
         <v>10.389999999999999</v>
       </c>
@@ -2316,7 +2397,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>342</v>
@@ -2340,13 +2421,13 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L7" s="38" t="s">
+      <c r="L7" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M7" s="14">
         <v>0.22</v>
       </c>
-      <c r="N7" s="45">
+      <c r="N7" s="37">
         <f t="shared" si="2"/>
         <v>2.2000000000000002</v>
       </c>
@@ -2386,13 +2467,13 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L8" s="38" t="s">
+      <c r="L8" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M8" s="14">
         <v>0.1</v>
       </c>
-      <c r="N8" s="45">
+      <c r="N8" s="37">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
@@ -2432,13 +2513,13 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L9" s="38" t="s">
+      <c r="L9" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M9" s="14">
         <v>0.1</v>
       </c>
-      <c r="N9" s="45">
+      <c r="N9" s="37">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
@@ -2478,13 +2559,13 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L10" s="38" t="s">
+      <c r="L10" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M10" s="14">
         <v>0.1</v>
       </c>
-      <c r="N10" s="45">
+      <c r="N10" s="37">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
@@ -2524,13 +2605,13 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L11" s="38" t="s">
+      <c r="L11" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M11" s="14">
         <v>0.1</v>
       </c>
-      <c r="N11" s="45">
+      <c r="N11" s="37">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
@@ -2570,13 +2651,13 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="L12" s="38" t="s">
+      <c r="L12" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M12" s="14">
         <v>0.22600000000000001</v>
       </c>
-      <c r="N12" s="45">
+      <c r="N12" s="37">
         <f t="shared" si="2"/>
         <v>3.39</v>
       </c>
@@ -2616,13 +2697,13 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L13" s="38" t="s">
+      <c r="L13" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M13" s="14">
         <v>0.73699999999999999</v>
       </c>
-      <c r="N13" s="45">
+      <c r="N13" s="37">
         <f t="shared" si="2"/>
         <v>7.37</v>
       </c>
@@ -2662,13 +2743,13 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L14" s="38" t="s">
+      <c r="L14" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M14" s="14">
         <v>0.22</v>
       </c>
-      <c r="N14" s="45">
+      <c r="N14" s="37">
         <f t="shared" si="2"/>
         <v>1.1000000000000001</v>
       </c>
@@ -2708,13 +2789,13 @@
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="L15" s="38" t="s">
+      <c r="L15" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M15" s="14">
         <v>0.26</v>
       </c>
-      <c r="N15" s="45">
+      <c r="N15" s="37">
         <f t="shared" si="2"/>
         <v>9.1</v>
       </c>
@@ -2754,13 +2835,13 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L16" s="38" t="s">
+      <c r="L16" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M16" s="14">
         <v>0.45</v>
       </c>
-      <c r="N16" s="45">
+      <c r="N16" s="37">
         <f t="shared" si="2"/>
         <v>2.25</v>
       </c>
@@ -2800,13 +2881,13 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L17" s="38" t="s">
+      <c r="L17" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M17" s="14">
         <v>0.11899999999999999</v>
       </c>
-      <c r="N17" s="45">
+      <c r="N17" s="37">
         <f t="shared" si="2"/>
         <v>1.19</v>
       </c>
@@ -2846,182 +2927,182 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L18" s="38" t="s">
+      <c r="L18" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M18" s="14">
         <v>0.48</v>
       </c>
-      <c r="N18" s="45">
+      <c r="N18" s="37">
         <f t="shared" si="2"/>
         <v>2.4</v>
       </c>
       <c r="O18" s="9"/>
     </row>
-    <row r="19" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="11">
         <f>ROW(B19) - ROW($B$2)</f>
         <v>17</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>108</v>
+        <v>404</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>411</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>220</v>
+        <v>395</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>336</v>
+        <v>298</v>
       </c>
       <c r="J19" s="7">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K19" s="7">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L19" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="L19" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M19" s="14">
-        <v>2.96</v>
-      </c>
-      <c r="N19" s="45">
-        <f t="shared" si="2"/>
-        <v>14.8</v>
+        <v>0.1</v>
+      </c>
+      <c r="N19" s="37">
+        <f t="shared" si="2"/>
+        <v>6</v>
       </c>
       <c r="O19" s="7"/>
     </row>
     <row r="20" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B20" si="3">ROW(B20) - ROW($B$2)</f>
         <v>18</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>109</v>
+        <v>405</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>412</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>221</v>
+        <v>396</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>336</v>
+        <v>271</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>294</v>
       </c>
       <c r="J20" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K20" s="7">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L20" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="L20" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M20" s="14">
-        <v>0.91</v>
-      </c>
-      <c r="N20" s="45">
-        <f t="shared" si="2"/>
-        <v>4.55</v>
-      </c>
-      <c r="O20" s="9"/>
-    </row>
-    <row r="21" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+      <c r="N20" s="37">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="O20" s="7"/>
+    </row>
+    <row r="21" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="11">
         <f>ROW(B21) - ROW($B$2)</f>
         <v>19</v>
       </c>
-      <c r="C21" s="13" t="s">
-        <v>3</v>
+      <c r="C21" s="12" t="s">
+        <v>2</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>110</v>
+        <v>406</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>413</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>222</v>
+        <v>397</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>336</v>
+        <v>414</v>
       </c>
       <c r="J21" s="7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K21" s="7">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L21" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="L21" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M21" s="14">
-        <v>0.21</v>
-      </c>
-      <c r="N21" s="45">
-        <f t="shared" si="2"/>
-        <v>1.05</v>
+        <v>0.1</v>
+      </c>
+      <c r="N21" s="37">
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
       <c r="O21" s="7"/>
     </row>
     <row r="22" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B22" si="4">ROW(B22) - ROW($B$2)</f>
         <v>20</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>111</v>
+        <v>428</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>429</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>223</v>
+        <v>430</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>336</v>
+        <v>271</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>306</v>
       </c>
       <c r="J22" s="9">
         <v>1</v>
@@ -3030,17 +3111,17 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L22" s="38" t="s">
+      <c r="L22" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M22" s="14">
-        <v>0.38</v>
-      </c>
-      <c r="N22" s="45">
-        <f t="shared" si="2"/>
-        <v>1.9</v>
-      </c>
-      <c r="O22" s="9"/>
+        <v>0.37</v>
+      </c>
+      <c r="N22" s="37">
+        <f t="shared" si="2"/>
+        <v>1.85</v>
+      </c>
+      <c r="O22" s="7"/>
     </row>
     <row r="23" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
@@ -3052,39 +3133,39 @@
         <v>3</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I23" s="8" t="s">
         <v>336</v>
       </c>
       <c r="J23" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K23" s="7">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L23" s="38" t="s">
+        <v>5</v>
+      </c>
+      <c r="L23" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M23" s="14">
-        <v>0.255</v>
-      </c>
-      <c r="N23" s="45">
-        <f t="shared" si="2"/>
-        <v>2.5499999999999998</v>
+        <v>2.96</v>
+      </c>
+      <c r="N23" s="37">
+        <f t="shared" si="2"/>
+        <v>14.8</v>
       </c>
       <c r="O23" s="7"/>
     </row>
@@ -3094,23 +3175,23 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="I24" s="8" t="s">
         <v>336</v>
@@ -3122,15 +3203,15 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L24" s="38" t="s">
+      <c r="L24" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M24" s="14">
-        <v>0.41</v>
-      </c>
-      <c r="N24" s="45">
-        <f t="shared" si="2"/>
-        <v>2.0499999999999998</v>
+        <v>0.91</v>
+      </c>
+      <c r="N24" s="37">
+        <f t="shared" si="2"/>
+        <v>4.55</v>
       </c>
       <c r="O24" s="9"/>
     </row>
@@ -3140,69 +3221,69 @@
         <f>ROW(B25) - ROW($B$2)</f>
         <v>23</v>
       </c>
-      <c r="C25" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>358</v>
+      <c r="C25" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I25" s="8" t="s">
         <v>336</v>
       </c>
       <c r="J25" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K25" s="7">
         <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="L25" s="38" t="s">
-        <v>349</v>
+        <v>5</v>
+      </c>
+      <c r="L25" s="30" t="s">
+        <v>337</v>
       </c>
       <c r="M25" s="14">
-        <v>1.54E-2</v>
-      </c>
-      <c r="N25" s="45">
-        <f t="shared" si="2"/>
-        <v>0.23100000000000001</v>
+        <v>0.21</v>
+      </c>
+      <c r="N25" s="37">
+        <f t="shared" si="2"/>
+        <v>1.05</v>
       </c>
       <c r="O25" s="7"/>
     </row>
-    <row r="26" spans="1:15" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="11">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="I26" s="8" t="s">
         <v>336</v>
@@ -3214,317 +3295,317 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L26" s="38" t="s">
+      <c r="L26" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M26" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="N26" s="45">
-        <f t="shared" si="2"/>
-        <v>7.5</v>
+        <v>0.38</v>
+      </c>
+      <c r="N26" s="37">
+        <f t="shared" si="2"/>
+        <v>1.9</v>
       </c>
       <c r="O26" s="9"/>
     </row>
-    <row r="27" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="11">
         <f>ROW(B27) - ROW($B$2)</f>
         <v>25</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>307</v>
+        <v>224</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>344</v>
+        <v>276</v>
       </c>
       <c r="I27" s="8" t="s">
         <v>336</v>
       </c>
       <c r="J27" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K27" s="7">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="L27" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="L27" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M27" s="14">
-        <v>0.26900000000000002</v>
-      </c>
-      <c r="N27" s="45">
-        <f t="shared" si="2"/>
-        <v>5.3800000000000008</v>
+        <v>0.255</v>
+      </c>
+      <c r="N27" s="37">
+        <f t="shared" si="2"/>
+        <v>2.5499999999999998</v>
       </c>
       <c r="O27" s="7"/>
     </row>
     <row r="28" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="11">
-        <f>ROW(B28) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>364</v>
+      <c r="C28" s="12" t="s">
+        <v>3</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>359</v>
+        <v>41</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>365</v>
+        <v>113</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>366</v>
+        <v>178</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>362</v>
+        <v>225</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="I28" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="J28" s="7">
-        <v>5</v>
+      <c r="J28" s="9">
+        <v>1</v>
       </c>
       <c r="K28" s="7">
         <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="L28" s="38" t="s">
+        <v>5</v>
+      </c>
+      <c r="L28" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M28" s="14">
-        <v>9.2999999999999999E-2</v>
-      </c>
-      <c r="N28" s="45">
-        <f t="shared" si="2"/>
-        <v>2.3250000000000002</v>
-      </c>
-      <c r="O28" s="7"/>
-    </row>
-    <row r="29" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.41</v>
+      </c>
+      <c r="N28" s="37">
+        <f t="shared" si="2"/>
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="O28" s="9"/>
+    </row>
+    <row r="29" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B29) - ROW($B$2)</f>
         <v>27</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>7</v>
+      <c r="C29" s="12" t="s">
+        <v>4</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>341</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>280</v>
+        <v>358</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>278</v>
       </c>
       <c r="I29" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="J29" s="9">
-        <v>1</v>
+      <c r="J29" s="7">
+        <v>3</v>
       </c>
       <c r="K29" s="7">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L29" s="38" t="s">
-        <v>337</v>
+        <v>15</v>
+      </c>
+      <c r="L29" s="30" t="s">
+        <v>349</v>
       </c>
       <c r="M29" s="14">
-        <v>4.3280000000000003</v>
-      </c>
-      <c r="N29" s="45">
-        <f t="shared" si="2"/>
-        <v>21.64</v>
-      </c>
-      <c r="O29" s="9"/>
-    </row>
-    <row r="30" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1.54E-2</v>
+      </c>
+      <c r="N29" s="37">
+        <f t="shared" si="2"/>
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="O29" s="7"/>
+    </row>
+    <row r="30" spans="1:15" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="11">
-        <f>ROW(B30) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C30" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>382</v>
+      <c r="C30" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>115</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>341</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>369</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>281</v>
+        <v>180</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>279</v>
       </c>
       <c r="I30" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="J30" s="7">
+      <c r="J30" s="9">
         <v>1</v>
       </c>
       <c r="K30" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L30" s="38" t="s">
-        <v>349</v>
+      <c r="L30" s="30" t="s">
+        <v>337</v>
       </c>
       <c r="M30" s="14">
-        <v>0.3725</v>
-      </c>
-      <c r="N30" s="45">
-        <f t="shared" si="2"/>
-        <v>1.8625</v>
-      </c>
-      <c r="O30" s="7"/>
-    </row>
-    <row r="31" spans="1:15" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1.5</v>
+      </c>
+      <c r="N30" s="37">
+        <f t="shared" si="2"/>
+        <v>7.5</v>
+      </c>
+      <c r="O30" s="9"/>
+    </row>
+    <row r="31" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B31) - ROW($B$2)</f>
         <v>29</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>9</v>
+      <c r="C31" s="12" t="s">
+        <v>6</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>394</v>
+        <v>116</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>341</v>
+        <v>181</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>392</v>
+        <v>307</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>395</v>
+        <v>344</v>
       </c>
       <c r="I31" s="8" t="s">
         <v>336</v>
       </c>
       <c r="J31" s="7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K31" s="7">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L31" s="38" t="s">
-        <v>349</v>
+        <v>20</v>
+      </c>
+      <c r="L31" s="30" t="s">
+        <v>337</v>
       </c>
       <c r="M31" s="14">
-        <v>0.60940000000000005</v>
-      </c>
-      <c r="N31" s="45">
-        <f t="shared" si="2"/>
-        <v>3.0470000000000002</v>
-      </c>
-      <c r="O31" s="9"/>
-    </row>
-    <row r="32" spans="1:15" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.26900000000000002</v>
+      </c>
+      <c r="N31" s="37">
+        <f t="shared" si="2"/>
+        <v>5.3800000000000008</v>
+      </c>
+      <c r="O31" s="7"/>
+    </row>
+    <row r="32" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="11">
         <f>ROW(B32) - ROW($B$2)</f>
         <v>30</v>
       </c>
-      <c r="C32" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>282</v>
+      <c r="C32" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>283</v>
       </c>
       <c r="I32" s="8" t="s">
         <v>336</v>
       </c>
       <c r="J32" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K32" s="7">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L32" s="38" t="s">
-        <v>349</v>
+        <v>25</v>
+      </c>
+      <c r="L32" s="30" t="s">
+        <v>337</v>
       </c>
       <c r="M32" s="14">
-        <v>6.8000000000000005E-2</v>
-      </c>
-      <c r="N32" s="45">
-        <f t="shared" si="2"/>
-        <v>0.34</v>
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="N32" s="37">
+        <f t="shared" si="2"/>
+        <v>2.3250000000000002</v>
       </c>
       <c r="O32" s="7"/>
     </row>
-    <row r="33" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="11">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>47</v>
+        <v>375</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>351</v>
-      </c>
-      <c r="F33" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="F33" s="9" t="s">
         <v>341</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>352</v>
+        <v>182</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>353</v>
+        <v>280</v>
       </c>
       <c r="I33" s="8" t="s">
         <v>336</v>
@@ -3536,19 +3617,19 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L33" s="38" t="s">
+      <c r="L33" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M33" s="14">
-        <v>25.25</v>
-      </c>
-      <c r="N33" s="45">
-        <f t="shared" si="2"/>
-        <v>126.25</v>
+        <v>4.3280000000000003</v>
+      </c>
+      <c r="N33" s="37">
+        <f t="shared" si="2"/>
+        <v>21.64</v>
       </c>
       <c r="O33" s="9"/>
     </row>
-    <row r="34" spans="1:15" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="11">
         <f>ROW(B34) - ROW($B$2)</f>
@@ -3558,16 +3639,16 @@
         <v>8</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>376</v>
+        <v>44</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="F34" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="F34" s="9" t="s">
         <v>341</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H34" s="7" t="s">
         <v>281</v>
@@ -3576,96 +3657,96 @@
         <v>336</v>
       </c>
       <c r="J34" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K34" s="7">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L34" s="38" t="s">
+        <v>5</v>
+      </c>
+      <c r="L34" s="30" t="s">
         <v>349</v>
       </c>
       <c r="M34" s="14">
-        <v>0.30809999999999998</v>
-      </c>
-      <c r="N34" s="45">
-        <f t="shared" si="2"/>
-        <v>3.081</v>
+        <v>0.3725</v>
+      </c>
+      <c r="N34" s="37">
+        <f t="shared" si="2"/>
+        <v>1.8625</v>
       </c>
       <c r="O34" s="7"/>
     </row>
-    <row r="35" spans="1:15" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="11">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>341</v>
+        <v>45</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>398</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>371</v>
+        <v>398</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="I35" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="I35" s="10" t="s">
         <v>336</v>
       </c>
       <c r="J35" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K35" s="7">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="L35" s="38" t="s">
+        <v>5</v>
+      </c>
+      <c r="L35" s="30" t="s">
         <v>349</v>
       </c>
       <c r="M35" s="14">
-        <v>0.30669999999999997</v>
-      </c>
-      <c r="N35" s="45">
-        <f t="shared" si="2"/>
-        <v>6.1339999999999995</v>
+        <v>0.57599999999999996</v>
+      </c>
+      <c r="N35" s="37">
+        <f t="shared" si="2"/>
+        <v>2.88</v>
       </c>
       <c r="O35" s="9"/>
     </row>
-    <row r="36" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="11">
         <f>ROW(B36) - ROW($B$2)</f>
         <v>34</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>341</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>183</v>
+        <v>228</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>308</v>
+        <v>336</v>
       </c>
       <c r="J36" s="7">
         <v>1</v>
@@ -3674,44 +3755,44 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L36" s="38" t="s">
-        <v>337</v>
+      <c r="L36" s="30" t="s">
+        <v>349</v>
       </c>
       <c r="M36" s="14">
-        <v>1.56</v>
-      </c>
-      <c r="N36" s="45">
-        <f t="shared" si="2"/>
-        <v>7.8000000000000007</v>
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="N36" s="37">
+        <f t="shared" si="2"/>
+        <v>0.34</v>
       </c>
       <c r="O36" s="7"/>
     </row>
-    <row r="37" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="11">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>120</v>
+        <v>351</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>341</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>184</v>
+        <v>352</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="I37" s="10" t="s">
-        <v>309</v>
+        <v>353</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>336</v>
       </c>
       <c r="J37" s="9">
         <v>1</v>
@@ -3720,87 +3801,87 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L37" s="38" t="s">
+      <c r="L37" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M37" s="14">
-        <v>1.19</v>
-      </c>
-      <c r="N37" s="45">
-        <f t="shared" si="2"/>
-        <v>5.9499999999999993</v>
+        <v>25.25</v>
+      </c>
+      <c r="N37" s="37">
+        <f t="shared" si="2"/>
+        <v>126.25</v>
       </c>
       <c r="O37" s="9"/>
     </row>
-    <row r="38" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="11">
         <f>ROW(B38) - ROW($B$2)</f>
         <v>36</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>51</v>
+        <v>376</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>121</v>
+        <v>383</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>341</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>185</v>
+        <v>370</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I38" s="8" t="s">
         <v>336</v>
       </c>
       <c r="J38" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K38" s="7">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L38" s="38" t="s">
-        <v>337</v>
+        <v>10</v>
+      </c>
+      <c r="L38" s="30" t="s">
+        <v>349</v>
       </c>
       <c r="M38" s="14">
-        <v>1.85</v>
-      </c>
-      <c r="N38" s="45">
-        <f t="shared" si="2"/>
-        <v>9.25</v>
+        <v>0.30809999999999998</v>
+      </c>
+      <c r="N38" s="37">
+        <f t="shared" si="2"/>
+        <v>3.081</v>
       </c>
       <c r="O38" s="7"/>
     </row>
-    <row r="39" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="11">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>186</v>
+        <v>384</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>341</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>229</v>
+        <v>371</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="I39" s="8" t="s">
         <v>336</v>
@@ -3812,90 +3893,90 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L39" s="38" t="s">
+      <c r="L39" s="30" t="s">
         <v>349</v>
       </c>
       <c r="M39" s="14">
-        <v>2.0799999999999999E-2</v>
-      </c>
-      <c r="N39" s="45">
-        <f t="shared" si="2"/>
-        <v>0.41599999999999998</v>
+        <v>0.30669999999999997</v>
+      </c>
+      <c r="N39" s="37">
+        <f t="shared" si="2"/>
+        <v>6.1339999999999995</v>
       </c>
       <c r="O39" s="9"/>
     </row>
-    <row r="40" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="11">
         <f>ROW(B40) - ROW($B$2)</f>
         <v>38</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>186</v>
+        <v>341</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>230</v>
+        <v>183</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>336</v>
+        <v>308</v>
       </c>
       <c r="J40" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K40" s="7">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L40" s="38" t="s">
-        <v>349</v>
+        <v>5</v>
+      </c>
+      <c r="L40" s="30" t="s">
+        <v>337</v>
       </c>
       <c r="M40" s="14">
-        <v>2.1700000000000001E-2</v>
-      </c>
-      <c r="N40" s="45">
-        <f t="shared" si="2"/>
-        <v>0.217</v>
+        <v>1.56</v>
+      </c>
+      <c r="N40" s="37">
+        <f t="shared" si="2"/>
+        <v>7.8000000000000007</v>
       </c>
       <c r="O40" s="7"/>
     </row>
-    <row r="41" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="11">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>186</v>
+        <v>120</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>341</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>231</v>
+        <v>184</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="I41" s="8" t="s">
-        <v>336</v>
+        <v>283</v>
+      </c>
+      <c r="I41" s="10" t="s">
+        <v>309</v>
       </c>
       <c r="J41" s="9">
         <v>1</v>
@@ -3904,41 +3985,41 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L41" s="38" t="s">
-        <v>349</v>
+      <c r="L41" s="30" t="s">
+        <v>337</v>
       </c>
       <c r="M41" s="14">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="N41" s="45">
-        <f t="shared" si="2"/>
-        <v>0.10999999999999999</v>
+        <v>1.19</v>
+      </c>
+      <c r="N41" s="37">
+        <f t="shared" si="2"/>
+        <v>5.9499999999999993</v>
       </c>
       <c r="O41" s="9"/>
     </row>
-    <row r="42" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="11">
         <f>ROW(B42) - ROW($B$2)</f>
         <v>40</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>186</v>
+        <v>341</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>232</v>
+        <v>185</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I42" s="8" t="s">
         <v>336</v>
@@ -3950,339 +4031,339 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L42" s="38" t="s">
-        <v>349</v>
+      <c r="L42" s="30" t="s">
+        <v>337</v>
       </c>
       <c r="M42" s="14">
-        <v>3.1300000000000001E-2</v>
-      </c>
-      <c r="N42" s="45">
-        <f t="shared" si="2"/>
-        <v>0.1565</v>
+        <v>1.85</v>
+      </c>
+      <c r="N42" s="37">
+        <f t="shared" si="2"/>
+        <v>9.25</v>
       </c>
       <c r="O42" s="7"/>
     </row>
-    <row r="43" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="11">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I43" s="8" t="s">
         <v>336</v>
       </c>
       <c r="J43" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K43" s="7">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L43" s="38" t="s">
-        <v>337</v>
+        <v>20</v>
+      </c>
+      <c r="L43" s="30" t="s">
+        <v>349</v>
       </c>
       <c r="M43" s="14">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="N43" s="45">
-        <f t="shared" si="2"/>
-        <v>5.45</v>
+        <v>2.0799999999999999E-2</v>
+      </c>
+      <c r="N43" s="37">
+        <f t="shared" si="2"/>
+        <v>0.41599999999999998</v>
       </c>
       <c r="O43" s="9"/>
     </row>
-    <row r="44" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="11">
         <f>ROW(B44) - ROW($B$2)</f>
         <v>42</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I44" s="8" t="s">
         <v>336</v>
       </c>
       <c r="J44" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K44" s="7">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L44" s="38" t="s">
-        <v>337</v>
+        <v>10</v>
+      </c>
+      <c r="L44" s="30" t="s">
+        <v>349</v>
       </c>
       <c r="M44" s="14">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="N44" s="45">
-        <f t="shared" si="2"/>
-        <v>5.45</v>
+        <v>2.1700000000000001E-2</v>
+      </c>
+      <c r="N44" s="37">
+        <f t="shared" si="2"/>
+        <v>0.217</v>
       </c>
       <c r="O44" s="7"/>
     </row>
-    <row r="45" spans="1:15" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="11">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="C45" s="12" t="s">
-        <v>16</v>
+      <c r="C45" s="13" t="s">
+        <v>14</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="I45" s="8" t="s">
         <v>336</v>
       </c>
       <c r="J45" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K45" s="7">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L45" s="38" t="s">
-        <v>337</v>
+        <v>5</v>
+      </c>
+      <c r="L45" s="30" t="s">
+        <v>349</v>
       </c>
       <c r="M45" s="14">
-        <v>0.2</v>
-      </c>
-      <c r="N45" s="45">
-        <f t="shared" si="2"/>
-        <v>2</v>
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="N45" s="37">
+        <f t="shared" si="2"/>
+        <v>0.10999999999999999</v>
       </c>
       <c r="O45" s="9"/>
     </row>
-    <row r="46" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B46) - ROW($B$2)</f>
         <v>44</v>
       </c>
-      <c r="C46" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="E46" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="G46" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="H46" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="I46" s="10" t="s">
-        <v>310</v>
-      </c>
-      <c r="J46" s="9">
+      <c r="C46" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="J46" s="7">
         <v>1</v>
       </c>
       <c r="K46" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L46" s="38" t="s">
-        <v>337</v>
+      <c r="L46" s="30" t="s">
+        <v>349</v>
       </c>
       <c r="M46" s="14">
-        <v>0.15</v>
-      </c>
-      <c r="N46" s="45">
-        <f t="shared" si="2"/>
-        <v>0.75</v>
-      </c>
-      <c r="O46" s="9"/>
+        <v>3.1300000000000001E-2</v>
+      </c>
+      <c r="N46" s="37">
+        <f t="shared" si="2"/>
+        <v>0.1565</v>
+      </c>
+      <c r="O46" s="7"/>
     </row>
     <row r="47" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="11">
-        <f>ROW(B47) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="C47" s="12" t="s">
-        <v>17</v>
+      <c r="C47" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>390</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="G47" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>271</v>
+        <v>56</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>285</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="J47" s="7">
+        <v>336</v>
+      </c>
+      <c r="J47" s="9">
         <v>1</v>
       </c>
       <c r="K47" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L47" s="38" t="s">
+      <c r="L47" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M47" s="14">
-        <v>0.1</v>
-      </c>
-      <c r="N47" s="45">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
-      <c r="O47" s="7"/>
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="N47" s="37">
+        <f t="shared" si="2"/>
+        <v>5.45</v>
+      </c>
+      <c r="O47" s="9"/>
     </row>
     <row r="48" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B48) - ROW($B$2)</f>
         <v>46</v>
       </c>
-      <c r="C48" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E48" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="G48" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="H48" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="I48" s="10" t="s">
-        <v>312</v>
-      </c>
-      <c r="J48" s="9">
+      <c r="C48" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="J48" s="7">
         <v>1</v>
       </c>
       <c r="K48" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L48" s="38" t="s">
+      <c r="L48" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M48" s="14">
-        <v>0.15</v>
-      </c>
-      <c r="N48" s="45">
-        <f t="shared" si="2"/>
-        <v>0.75</v>
-      </c>
-      <c r="O48" s="9"/>
-    </row>
-    <row r="49" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="N48" s="37">
+        <f t="shared" si="2"/>
+        <v>5.45</v>
+      </c>
+      <c r="O48" s="7"/>
+    </row>
+    <row r="49" spans="1:15" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="11">
-        <f>ROW(B49) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="G49" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>271</v>
+        <v>16</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="G49" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>286</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="J49" s="7">
-        <v>1</v>
+        <v>336</v>
+      </c>
+      <c r="J49" s="9">
+        <v>2</v>
       </c>
       <c r="K49" s="7">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L49" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="L49" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M49" s="14">
-        <v>0.13</v>
-      </c>
-      <c r="N49" s="45">
-        <f t="shared" si="2"/>
-        <v>0.65</v>
-      </c>
-      <c r="O49" s="7"/>
+        <v>0.2</v>
+      </c>
+      <c r="N49" s="37">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="O49" s="9"/>
     </row>
     <row r="50" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
@@ -4294,22 +4375,22 @@
         <v>17</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J50" s="9">
         <v>1</v>
@@ -4318,15 +4399,15 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L50" s="38" t="s">
+      <c r="L50" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M50" s="14">
-        <v>0.64</v>
-      </c>
-      <c r="N50" s="45">
-        <f t="shared" si="2"/>
-        <v>3.2</v>
+        <v>0.15</v>
+      </c>
+      <c r="N50" s="37">
+        <f t="shared" si="2"/>
+        <v>0.75</v>
       </c>
       <c r="O50" s="9"/>
     </row>
@@ -4340,39 +4421,39 @@
         <v>17</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>63</v>
+        <v>431</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="H51" s="7" t="s">
         <v>271</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="J51" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K51" s="7">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L51" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="L51" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M51" s="14">
-        <v>0.15</v>
-      </c>
-      <c r="N51" s="45">
-        <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.1</v>
+      </c>
+      <c r="N51" s="37">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="O51" s="7"/>
     </row>
@@ -4386,22 +4467,22 @@
         <v>17</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>189</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="H52" s="9" t="s">
         <v>271</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="J52" s="9">
         <v>1</v>
@@ -4410,13 +4491,13 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L52" s="38" t="s">
+      <c r="L52" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M52" s="14">
         <v>0.15</v>
       </c>
-      <c r="N52" s="45">
+      <c r="N52" s="37">
         <f t="shared" si="2"/>
         <v>0.75</v>
       </c>
@@ -4432,22 +4513,22 @@
         <v>17</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H53" s="7" t="s">
         <v>271</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="J53" s="7">
         <v>1</v>
@@ -4456,15 +4537,15 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L53" s="38" t="s">
+      <c r="L53" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M53" s="14">
-        <v>0.15</v>
-      </c>
-      <c r="N53" s="45">
-        <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.13</v>
+      </c>
+      <c r="N53" s="37">
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
       <c r="O53" s="7"/>
     </row>
@@ -4478,22 +4559,22 @@
         <v>17</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="J54" s="9">
         <v>1</v>
@@ -4502,15 +4583,15 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L54" s="38" t="s">
+      <c r="L54" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M54" s="14">
-        <v>0.15</v>
-      </c>
-      <c r="N54" s="45">
-        <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.64</v>
+      </c>
+      <c r="N54" s="37">
+        <f t="shared" si="2"/>
+        <v>3.2</v>
       </c>
       <c r="O54" s="9"/>
     </row>
@@ -4520,26 +4601,26 @@
         <f>ROW(B55) - ROW($B$2)</f>
         <v>53</v>
       </c>
-      <c r="C55" s="13" t="s">
+      <c r="C55" s="12" t="s">
         <v>17</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F55" s="7" t="s">
         <v>189</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="H55" s="7" t="s">
         <v>271</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="J55" s="7">
         <v>1</v>
@@ -4548,15 +4629,15 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L55" s="38" t="s">
+      <c r="L55" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M55" s="14">
-        <v>0.1</v>
-      </c>
-      <c r="N55" s="45">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.15</v>
+      </c>
+      <c r="N55" s="37">
+        <f t="shared" si="2"/>
+        <v>0.75</v>
       </c>
       <c r="O55" s="7"/>
     </row>
@@ -4570,39 +4651,39 @@
         <v>17</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>189</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="H56" s="9" t="s">
         <v>271</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="J56" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K56" s="7">
         <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="L56" s="38" t="s">
+        <v>5</v>
+      </c>
+      <c r="L56" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M56" s="14">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="N56" s="45">
-        <f t="shared" si="2"/>
-        <v>0.375</v>
+        <v>0.15</v>
+      </c>
+      <c r="N56" s="37">
+        <f t="shared" si="2"/>
+        <v>0.75</v>
       </c>
       <c r="O56" s="9"/>
     </row>
@@ -4616,22 +4697,22 @@
         <v>17</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F57" s="7" t="s">
         <v>189</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="H57" s="7" t="s">
         <v>271</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="J57" s="7">
         <v>1</v>
@@ -4640,15 +4721,15 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L57" s="38" t="s">
+      <c r="L57" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M57" s="14">
-        <v>0.1</v>
-      </c>
-      <c r="N57" s="45">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.15</v>
+      </c>
+      <c r="N57" s="37">
+        <f t="shared" si="2"/>
+        <v>0.75</v>
       </c>
       <c r="O57" s="7"/>
     </row>
@@ -4658,26 +4739,26 @@
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="C58" s="12" t="s">
+      <c r="C58" s="13" t="s">
         <v>17</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>189</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="H58" s="9" t="s">
         <v>271</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="J58" s="9">
         <v>1</v>
@@ -4686,15 +4767,15 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L58" s="38" t="s">
+      <c r="L58" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M58" s="14">
-        <v>0.1</v>
-      </c>
-      <c r="N58" s="45">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.15</v>
+      </c>
+      <c r="N58" s="37">
+        <f t="shared" si="2"/>
+        <v>0.75</v>
       </c>
       <c r="O58" s="9"/>
     </row>
@@ -4704,26 +4785,26 @@
         <f>ROW(B59) - ROW($B$2)</f>
         <v>57</v>
       </c>
-      <c r="C59" s="12" t="s">
+      <c r="C59" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D59" s="9" t="s">
-        <v>377</v>
+      <c r="D59" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F59" s="7" t="s">
         <v>189</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="H59" s="7" t="s">
         <v>271</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="J59" s="7">
         <v>1</v>
@@ -4732,15 +4813,15 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L59" s="38" t="s">
+      <c r="L59" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M59" s="14">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="N59" s="45">
-        <f t="shared" si="2"/>
-        <v>7.4999999999999997E-2</v>
+        <v>0.1</v>
+      </c>
+      <c r="N59" s="37">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="O59" s="7"/>
     </row>
@@ -4754,225 +4835,225 @@
         <v>17</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>189</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>345</v>
+        <v>246</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>346</v>
+        <v>271</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="J60" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K60" s="7">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L60" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="L60" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M60" s="14">
-        <v>0.1</v>
-      </c>
-      <c r="N60" s="45">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N60" s="37">
+        <f t="shared" si="2"/>
+        <v>0.375</v>
       </c>
       <c r="O60" s="9"/>
     </row>
     <row r="61" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B61) - ROW($B$2)</f>
         <v>59</v>
       </c>
       <c r="C61" s="12" t="s">
         <v>17</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>391</v>
+        <v>69</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>396</v>
+        <v>140</v>
       </c>
       <c r="F61" s="7" t="s">
         <v>189</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>393</v>
+        <v>247</v>
       </c>
       <c r="H61" s="7" t="s">
         <v>271</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>397</v>
+        <v>321</v>
       </c>
       <c r="J61" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K61" s="7">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L61" s="38" t="s">
+        <v>5</v>
+      </c>
+      <c r="L61" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M61" s="14">
         <v>0.1</v>
       </c>
-      <c r="N61" s="45">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="O61" s="9"/>
+      <c r="N61" s="37">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="O61" s="7"/>
     </row>
     <row r="62" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="11">
-        <f>ROW(B62) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="C62" s="13" t="s">
+      <c r="C62" s="12" t="s">
         <v>17</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>378</v>
+        <v>70</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>189</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="H62" s="9" t="s">
         <v>271</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="J62" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K62" s="7">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L62" s="38" t="s">
+        <v>5</v>
+      </c>
+      <c r="L62" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M62" s="14">
         <v>0.1</v>
       </c>
-      <c r="N62" s="45">
-        <f>M62*K62</f>
-        <v>1</v>
+      <c r="N62" s="37">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="O62" s="9"/>
     </row>
     <row r="63" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B63) - ROW($B$2)</f>
         <v>61</v>
       </c>
-      <c r="C63" s="13" t="s">
+      <c r="C63" s="12" t="s">
         <v>17</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E63" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="F63" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="G63" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="H63" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="H63" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="I63" s="10" t="s">
-        <v>325</v>
-      </c>
-      <c r="J63" s="9">
+      <c r="I63" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="J63" s="7">
         <v>1</v>
       </c>
       <c r="K63" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L63" s="38" t="s">
+      <c r="L63" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M63" s="14">
-        <v>0.1</v>
-      </c>
-      <c r="N63" s="45">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
-      <c r="O63" s="9"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N63" s="37">
+        <f t="shared" si="2"/>
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="O63" s="7"/>
     </row>
     <row r="64" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="11">
-        <f>ROW(B64) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="C64" s="12" t="s">
+      <c r="C64" s="13" t="s">
         <v>17</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="E64" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="F64" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E64" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="F64" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="G64" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="H64" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="I64" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="J64" s="7">
-        <v>6</v>
+      <c r="G64" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="H64" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="I64" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="J64" s="9">
+        <v>1</v>
       </c>
       <c r="K64" s="7">
         <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="L64" s="38" t="s">
+        <v>5</v>
+      </c>
+      <c r="L64" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M64" s="14">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="N64" s="45">
-        <f t="shared" si="2"/>
-        <v>0.44999999999999996</v>
-      </c>
-      <c r="O64" s="7"/>
+        <v>0.1</v>
+      </c>
+      <c r="N64" s="37">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="O64" s="9"/>
     </row>
     <row r="65" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
@@ -4980,43 +5061,43 @@
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="C65" s="13" t="s">
+      <c r="C65" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D65" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E65" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="F65" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="G65" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="H65" s="9" t="s">
+      <c r="D65" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="G65" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="H65" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="I65" s="10" t="s">
-        <v>326</v>
-      </c>
-      <c r="J65" s="9">
+      <c r="I65" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="J65" s="7">
         <v>2</v>
       </c>
       <c r="K65" s="7">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L65" s="38" t="s">
+      <c r="L65" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M65" s="14">
-        <v>1.9E-2</v>
-      </c>
-      <c r="N65" s="45">
-        <f t="shared" si="2"/>
-        <v>0.19</v>
+        <v>0.1</v>
+      </c>
+      <c r="N65" s="37">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="O65" s="9"/>
     </row>
@@ -5026,45 +5107,45 @@
         <f>ROW(B66) - ROW($B$2)</f>
         <v>64</v>
       </c>
-      <c r="C66" s="12" t="s">
+      <c r="C66" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D66" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E66" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="G66" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H66" s="7" t="s">
+      <c r="D66" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="E66" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="G66" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="H66" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="I66" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="J66" s="7">
-        <v>1</v>
+      <c r="I66" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="J66" s="9">
+        <v>2</v>
       </c>
       <c r="K66" s="7">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L66" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="L66" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M66" s="14">
         <v>0.1</v>
       </c>
-      <c r="N66" s="45">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
-      <c r="O66" s="7"/>
+      <c r="N66" s="37">
+        <f>M66*K66</f>
+        <v>1</v>
+      </c>
+      <c r="O66" s="9"/>
     </row>
     <row r="67" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
@@ -5076,22 +5157,22 @@
         <v>17</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>190</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="H67" s="9" t="s">
         <v>271</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="J67" s="9">
         <v>1</v>
@@ -5100,13 +5181,13 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L67" s="38" t="s">
+      <c r="L67" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M67" s="14">
         <v>0.1</v>
       </c>
-      <c r="N67" s="45">
+      <c r="N67" s="37">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
@@ -5115,46 +5196,46 @@
     <row r="68" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
       <c r="B68" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B68) - ROW($B$2)</f>
         <v>66</v>
       </c>
-      <c r="C68" s="13" t="s">
+      <c r="C68" s="12" t="s">
         <v>17</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>379</v>
-      </c>
-      <c r="E68" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="F68" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="G68" s="10" t="s">
-        <v>372</v>
-      </c>
-      <c r="H68" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="H68" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="I68" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="J68" s="9">
-        <v>1</v>
+      <c r="I68" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="J68" s="7">
+        <v>6</v>
       </c>
       <c r="K68" s="7">
-        <f t="shared" ref="K68:K90" si="3">J68*5</f>
-        <v>5</v>
-      </c>
-      <c r="L68" s="38" t="s">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="L68" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M68" s="14">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="N68" s="45">
-        <f t="shared" si="2"/>
-        <v>0.70000000000000007</v>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N68" s="37">
+        <f t="shared" si="2"/>
+        <v>0.44999999999999996</v>
       </c>
       <c r="O68" s="7"/>
     </row>
@@ -5164,45 +5245,45 @@
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
-      <c r="C69" s="12" t="s">
+      <c r="C69" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D69" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="E69" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="F69" s="7" t="s">
+      <c r="D69" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E69" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="F69" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="G69" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="H69" s="7" t="s">
+      <c r="G69" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="H69" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="I69" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="J69" s="7">
-        <v>1</v>
+      <c r="I69" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="J69" s="9">
+        <v>2</v>
       </c>
       <c r="K69" s="7">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="L69" s="38" t="s">
+        <f t="shared" ref="K69:K98" si="5">J69*5</f>
+        <v>10</v>
+      </c>
+      <c r="L69" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M69" s="14">
-        <v>0.1</v>
-      </c>
-      <c r="N69" s="45">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
-      <c r="O69" s="7"/>
+        <v>1.9E-2</v>
+      </c>
+      <c r="N69" s="37">
+        <f t="shared" si="2"/>
+        <v>0.19</v>
+      </c>
+      <c r="O69" s="9"/>
     </row>
     <row r="70" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
@@ -5214,39 +5295,39 @@
         <v>17</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H70" s="7" t="s">
         <v>271</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="J70" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K70" s="7">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="L70" s="38" t="s">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="L70" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M70" s="14">
-        <v>9.4030000000000002E-2</v>
-      </c>
-      <c r="N70" s="45">
-        <f t="shared" si="2"/>
-        <v>0.94030000000000002</v>
+        <v>0.1</v>
+      </c>
+      <c r="N70" s="37">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="O70" s="7"/>
     </row>
@@ -5256,43 +5337,43 @@
         <f t="shared" si="0"/>
         <v>69</v>
       </c>
-      <c r="C71" s="12" t="s">
+      <c r="C71" s="13" t="s">
         <v>17</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>190</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="H71" s="9" t="s">
         <v>271</v>
       </c>
       <c r="I71" s="10" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="J71" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K71" s="7">
-        <f t="shared" si="3"/>
-        <v>20</v>
-      </c>
-      <c r="L71" s="38" t="s">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="L71" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M71" s="14">
-        <v>1.9E-2</v>
-      </c>
-      <c r="N71" s="45">
-        <f t="shared" ref="N71:N90" si="4">M71*K71</f>
-        <v>0.38</v>
+        <v>0.1</v>
+      </c>
+      <c r="N71" s="37">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="O71" s="9"/>
     </row>
@@ -5302,552 +5383,552 @@
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="C72" s="12" t="s">
+      <c r="C72" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D72" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="E72" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="F72" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="G72" s="8" t="s">
-        <v>363</v>
-      </c>
-      <c r="H72" s="7" t="s">
+      <c r="D72" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="E72" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="F72" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="G72" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="H72" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="I72" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="J72" s="7">
-        <v>2</v>
+      <c r="I72" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="J72" s="9">
+        <v>1</v>
       </c>
       <c r="K72" s="7">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="L72" s="38" t="s">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="L72" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M72" s="14">
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="N72" s="45">
-        <f t="shared" si="4"/>
-        <v>0.10999999999999999</v>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="N72" s="37">
+        <f t="shared" si="2"/>
+        <v>0.70000000000000007</v>
       </c>
       <c r="O72" s="7"/>
     </row>
     <row r="73" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="11">
-        <f>ROW(B73) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>71</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D73" s="15" t="s">
-        <v>381</v>
-      </c>
-      <c r="E73" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="F73" s="15" t="s">
-        <v>341</v>
-      </c>
-      <c r="G73" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="H73" s="15" t="s">
-        <v>336</v>
-      </c>
-      <c r="I73" s="16" t="s">
-        <v>336</v>
-      </c>
-      <c r="J73" s="15">
+        <v>17</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="F73" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="H73" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="I73" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="J73" s="7">
         <v>1</v>
       </c>
       <c r="K73" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="L73" s="39" t="s">
-        <v>336</v>
-      </c>
-      <c r="M73" s="17" t="s">
-        <v>336</v>
-      </c>
-      <c r="N73" s="46" t="s">
-        <v>336</v>
-      </c>
-      <c r="O73" s="15" t="s">
-        <v>347</v>
-      </c>
+      <c r="L73" s="30" t="s">
+        <v>337</v>
+      </c>
+      <c r="M73" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="N73" s="37">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="O73" s="7"/>
     </row>
     <row r="74" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B74) - ROW($B$2)</f>
         <v>72</v>
       </c>
-      <c r="C74" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D74" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="E74" s="9" t="s">
-        <v>153</v>
+      <c r="C74" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E74" s="7" t="s">
+        <v>149</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="G74" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="H74" s="9" t="s">
-        <v>287</v>
+        <v>192</v>
+      </c>
+      <c r="G74" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="H74" s="7" t="s">
+        <v>271</v>
       </c>
       <c r="I74" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="J74" s="9">
+        <v>329</v>
+      </c>
+      <c r="J74" s="7">
         <v>2</v>
       </c>
       <c r="K74" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="L74" s="38" t="s">
+      <c r="L74" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M74" s="14">
-        <v>0.98299999999999998</v>
-      </c>
-      <c r="N74" s="45">
-        <f t="shared" si="4"/>
-        <v>9.83</v>
-      </c>
-      <c r="O74" s="9"/>
+        <v>9.4030000000000002E-2</v>
+      </c>
+      <c r="N74" s="37">
+        <f t="shared" si="2"/>
+        <v>0.94030000000000002</v>
+      </c>
+      <c r="O74" s="7"/>
     </row>
     <row r="75" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="11">
-        <f>ROW(B75) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>73</v>
       </c>
       <c r="C75" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E75" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="G75" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="H75" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="I75" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="J75" s="9">
+        <v>4</v>
+      </c>
+      <c r="K75" s="7">
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
-      <c r="D75" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="E75" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="F75" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="G75" s="8">
-        <v>760390015</v>
-      </c>
-      <c r="H75" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="I75" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="J75" s="7">
-        <v>1</v>
-      </c>
-      <c r="K75" s="7">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="L75" s="38" t="s">
+      <c r="L75" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M75" s="14">
-        <v>1.9</v>
-      </c>
-      <c r="N75" s="45">
-        <f t="shared" si="4"/>
-        <v>9.5</v>
-      </c>
-      <c r="O75" s="7"/>
-    </row>
-    <row r="76" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1.9E-2</v>
+      </c>
+      <c r="N75" s="37">
+        <f t="shared" ref="N75:N98" si="6">M75*K75</f>
+        <v>0.38</v>
+      </c>
+      <c r="O75" s="9"/>
+    </row>
+    <row r="76" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="11">
         <f t="shared" si="0"/>
         <v>74</v>
       </c>
-      <c r="C76" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D76" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E76" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="F76" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="G76" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="H76" s="9" t="s">
-        <v>289</v>
+      <c r="C76" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="E76" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="G76" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="H76" s="7" t="s">
+        <v>271</v>
       </c>
       <c r="I76" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="J76" s="9">
-        <v>1</v>
+        <v>368</v>
+      </c>
+      <c r="J76" s="7">
+        <v>2</v>
       </c>
       <c r="K76" s="7">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="L76" s="38" t="s">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="L76" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M76" s="14">
-        <v>6.11</v>
-      </c>
-      <c r="N76" s="45">
-        <f t="shared" si="4"/>
-        <v>30.55</v>
-      </c>
-      <c r="O76" s="9"/>
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="N76" s="37">
+        <f t="shared" si="6"/>
+        <v>0.10999999999999999</v>
+      </c>
+      <c r="O76" s="7"/>
     </row>
     <row r="77" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="11">
-        <f>ROW(B77) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>75</v>
       </c>
-      <c r="C77" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D77" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E77" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="F77" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="G77" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="H77" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="I77" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="J77" s="7">
-        <v>1</v>
+      <c r="C77" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="E77" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="G77" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="H77" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="I77" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="J77" s="9">
+        <v>4</v>
       </c>
       <c r="K77" s="7">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="L77" s="38" t="s">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L77" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M77" s="14">
-        <v>2.41</v>
-      </c>
-      <c r="N77" s="45">
-        <f t="shared" si="4"/>
-        <v>12.05</v>
+        <v>0.16</v>
+      </c>
+      <c r="N77" s="37">
+        <f t="shared" si="6"/>
+        <v>3.2</v>
       </c>
       <c r="O77" s="7"/>
     </row>
     <row r="78" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B78) - ROW($B$2)</f>
         <v>76</v>
       </c>
-      <c r="C78" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D78" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="E78" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="F78" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="G78" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="H78" s="9" t="s">
-        <v>285</v>
+      <c r="C78" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="G78" s="8" t="s">
+        <v>400</v>
+      </c>
+      <c r="H78" s="7" t="s">
+        <v>271</v>
       </c>
       <c r="I78" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="J78" s="9">
-        <v>1</v>
+        <v>418</v>
+      </c>
+      <c r="J78" s="7">
+        <v>8</v>
       </c>
       <c r="K78" s="7">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="L78" s="38" t="s">
+        <f t="shared" si="5"/>
+        <v>40</v>
+      </c>
+      <c r="L78" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M78" s="14">
-        <v>1.43</v>
-      </c>
-      <c r="N78" s="45">
-        <f t="shared" si="4"/>
-        <v>7.1499999999999995</v>
-      </c>
-      <c r="O78" s="9"/>
+        <v>0.16</v>
+      </c>
+      <c r="N78" s="37">
+        <f t="shared" si="6"/>
+        <v>6.4</v>
+      </c>
+      <c r="O78" s="7"/>
     </row>
     <row r="79" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="11">
-        <f>ROW(B79) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>77</v>
       </c>
-      <c r="C79" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E79" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="F79" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="G79" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="H79" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="I79" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="J79" s="7">
-        <v>1</v>
+      <c r="C79" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="E79" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="G79" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="I79" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="J79" s="9">
+        <v>8</v>
       </c>
       <c r="K79" s="7">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="L79" s="38" t="s">
+        <f t="shared" si="5"/>
+        <v>40</v>
+      </c>
+      <c r="L79" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M79" s="14">
-        <v>2.27</v>
-      </c>
-      <c r="N79" s="45">
-        <f t="shared" si="4"/>
-        <v>11.35</v>
+        <v>0.16</v>
+      </c>
+      <c r="N79" s="37">
+        <f t="shared" si="6"/>
+        <v>6.4</v>
       </c>
       <c r="O79" s="7"/>
     </row>
     <row r="80" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B80) - ROW($B$2)</f>
         <v>78</v>
       </c>
-      <c r="C80" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E80" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="F80" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="G80" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="H80" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="I80" s="8" t="s">
+      <c r="C80" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D80" s="15" t="s">
+        <v>381</v>
+      </c>
+      <c r="E80" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="F80" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="G80" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="H80" s="15" t="s">
         <v>336</v>
       </c>
-      <c r="J80" s="9">
+      <c r="I80" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="J80" s="15">
         <v>1</v>
       </c>
       <c r="K80" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="L80" s="38" t="s">
-        <v>337</v>
-      </c>
-      <c r="M80" s="14">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="N80" s="45">
-        <f t="shared" si="4"/>
-        <v>5.8</v>
-      </c>
-      <c r="O80" s="9"/>
-    </row>
-    <row r="81" spans="1:22" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L80" s="31" t="s">
+        <v>336</v>
+      </c>
+      <c r="M80" s="17" t="s">
+        <v>336</v>
+      </c>
+      <c r="N80" s="38" t="s">
+        <v>336</v>
+      </c>
+      <c r="O80" s="15" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="81" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="11">
-        <f>ROW(B81) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>79</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D81" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="E81" s="7" t="s">
-        <v>160</v>
+        <v>19</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E81" s="9" t="s">
+        <v>153</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="G81" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="H81" s="7" t="s">
-        <v>290</v>
+        <v>341</v>
+      </c>
+      <c r="G81" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="H81" s="9" t="s">
+        <v>287</v>
       </c>
       <c r="I81" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="J81" s="7">
-        <v>1</v>
+      <c r="J81" s="9">
+        <v>2</v>
       </c>
       <c r="K81" s="7">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="L81" s="38" t="s">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="L81" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M81" s="14">
-        <v>4.66</v>
-      </c>
-      <c r="N81" s="45">
-        <f t="shared" si="4"/>
-        <v>23.3</v>
-      </c>
-      <c r="O81" s="7"/>
-    </row>
-    <row r="82" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.98299999999999998</v>
+      </c>
+      <c r="N81" s="37">
+        <f t="shared" si="6"/>
+        <v>9.83</v>
+      </c>
+      <c r="O81" s="9"/>
+    </row>
+    <row r="82" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B82) - ROW($B$2)</f>
         <v>80</v>
       </c>
-      <c r="C82" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E82" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="F82" s="9" t="s">
+      <c r="C82" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E82" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="F82" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="G82" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="H82" s="9" t="s">
-        <v>291</v>
+      <c r="G82" s="8">
+        <v>760390015</v>
+      </c>
+      <c r="H82" s="7" t="s">
+        <v>288</v>
       </c>
       <c r="I82" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="J82" s="9">
+      <c r="J82" s="7">
         <v>1</v>
       </c>
       <c r="K82" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="L82" s="38" t="s">
+      <c r="L82" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M82" s="14">
-        <v>3</v>
-      </c>
-      <c r="N82" s="45">
-        <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="O82" s="9"/>
-    </row>
-    <row r="83" spans="1:22" s="19" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1.9</v>
+      </c>
+      <c r="N82" s="37">
+        <f t="shared" si="6"/>
+        <v>9.5</v>
+      </c>
+      <c r="O82" s="7"/>
+    </row>
+    <row r="83" spans="1:23" s="19" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="18"/>
       <c r="B83" s="11">
-        <f>ROW(B83) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>81</v>
       </c>
       <c r="C83" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D83" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="E83" s="7" t="s">
-        <v>162</v>
+      <c r="D83" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E83" s="9" t="s">
+        <v>155</v>
       </c>
       <c r="F83" s="9" t="s">
-        <v>341</v>
-      </c>
-      <c r="G83" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="H83" s="7" t="s">
-        <v>292</v>
+        <v>195</v>
+      </c>
+      <c r="G83" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="H83" s="9" t="s">
+        <v>289</v>
       </c>
       <c r="I83" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="J83" s="7">
+      <c r="J83" s="9">
         <v>1</v>
       </c>
       <c r="K83" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="L83" s="38" t="s">
-        <v>349</v>
+      <c r="L83" s="30" t="s">
+        <v>337</v>
       </c>
       <c r="M83" s="14">
-        <v>2.6663999999999999</v>
-      </c>
-      <c r="N83" s="45">
-        <f t="shared" si="4"/>
-        <v>13.331999999999999</v>
-      </c>
-      <c r="O83" s="7"/>
+        <v>6.11</v>
+      </c>
+      <c r="N83" s="37">
+        <f t="shared" si="6"/>
+        <v>30.55</v>
+      </c>
+      <c r="O83" s="9"/>
       <c r="P83"/>
       <c r="Q83"/>
       <c r="R83"/>
@@ -5855,384 +5936,739 @@
       <c r="T83"/>
       <c r="U83"/>
       <c r="V83"/>
-    </row>
-    <row r="84" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="W83"/>
+    </row>
+    <row r="84" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B84) - ROW($B$2)</f>
         <v>82</v>
       </c>
-      <c r="C84" s="13" t="s">
+      <c r="C84" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D84" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="E84" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="F84" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="G84" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="H84" s="9" t="s">
+      <c r="D84" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="G84" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="H84" s="7" t="s">
         <v>285</v>
       </c>
       <c r="I84" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="J84" s="9">
+      <c r="J84" s="7">
         <v>1</v>
       </c>
       <c r="K84" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="L84" s="38" t="s">
+      <c r="L84" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M84" s="14">
-        <v>4.51</v>
-      </c>
-      <c r="N84" s="45">
-        <f t="shared" si="4"/>
-        <v>22.549999999999997</v>
-      </c>
-      <c r="O84" s="9"/>
-    </row>
-    <row r="85" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2.41</v>
+      </c>
+      <c r="N84" s="37">
+        <f t="shared" si="6"/>
+        <v>12.05</v>
+      </c>
+      <c r="O84" s="7"/>
+    </row>
+    <row r="85" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="11">
-        <f>ROW(B85) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>83</v>
       </c>
-      <c r="C85" s="12" t="s">
+      <c r="C85" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D85" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="E85" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="F85" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="G85" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="H85" s="7" t="s">
+      <c r="D85" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E85" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="F85" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="G85" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="H85" s="9" t="s">
         <v>285</v>
       </c>
       <c r="I85" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="J85" s="7">
-        <v>4</v>
+      <c r="J85" s="9">
+        <v>1</v>
       </c>
       <c r="K85" s="7">
-        <f t="shared" si="3"/>
-        <v>20</v>
-      </c>
-      <c r="L85" s="38" t="s">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="L85" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M85" s="14">
-        <v>0.68</v>
-      </c>
-      <c r="N85" s="45">
-        <f t="shared" si="4"/>
-        <v>13.600000000000001</v>
-      </c>
-      <c r="O85" s="7"/>
-    </row>
-    <row r="86" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1.43</v>
+      </c>
+      <c r="N85" s="37">
+        <f t="shared" si="6"/>
+        <v>7.1499999999999995</v>
+      </c>
+      <c r="O85" s="9"/>
+    </row>
+    <row r="86" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B86) - ROW($B$2)</f>
         <v>84</v>
       </c>
-      <c r="C86" s="13" t="s">
+      <c r="C86" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D86" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E86" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="F86" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="G86" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="H86" s="9" t="s">
+      <c r="D86" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E86" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="G86" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="H86" s="7" t="s">
         <v>285</v>
       </c>
       <c r="I86" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="J86" s="9">
-        <v>2</v>
+      <c r="J86" s="7">
+        <v>1</v>
       </c>
       <c r="K86" s="7">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="L86" s="38" t="s">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="L86" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M86" s="14">
-        <v>5.2880000000000003</v>
-      </c>
-      <c r="N86" s="45">
-        <f t="shared" si="4"/>
-        <v>52.88</v>
-      </c>
-      <c r="O86" s="9"/>
-    </row>
-    <row r="87" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2.27</v>
+      </c>
+      <c r="N86" s="37">
+        <f t="shared" si="6"/>
+        <v>11.35</v>
+      </c>
+      <c r="O86" s="7"/>
+    </row>
+    <row r="87" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="11">
-        <f>ROW(B87) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>85</v>
       </c>
-      <c r="C87" s="12" t="s">
+      <c r="C87" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D87" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E87" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="F87" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="G87" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="H87" s="7" t="s">
+      <c r="D87" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E87" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="G87" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="H87" s="9" t="s">
         <v>285</v>
       </c>
       <c r="I87" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="J87" s="7">
+      <c r="J87" s="9">
         <v>1</v>
       </c>
       <c r="K87" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="L87" s="38" t="s">
+      <c r="L87" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M87" s="14">
-        <v>0.95</v>
-      </c>
-      <c r="N87" s="45">
-        <f t="shared" si="4"/>
-        <v>4.75</v>
-      </c>
-      <c r="O87" s="7"/>
-    </row>
-    <row r="88" spans="1:22" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="N87" s="37">
+        <f t="shared" si="6"/>
+        <v>5.8</v>
+      </c>
+      <c r="O87" s="9"/>
+    </row>
+    <row r="88" spans="1:23" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="11">
         <f>ROW(B88) - ROW($B$2)</f>
         <v>86</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>354</v>
-      </c>
-      <c r="D88" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="G88" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="H88" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="I88" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="E88" s="23" t="s">
-        <v>355</v>
-      </c>
-      <c r="F88" s="23" t="s">
-        <v>336</v>
-      </c>
-      <c r="G88" s="22" t="s">
-        <v>356</v>
-      </c>
-      <c r="H88" s="23" t="s">
-        <v>357</v>
-      </c>
-      <c r="I88" s="22" t="s">
-        <v>336</v>
-      </c>
-      <c r="J88" s="23">
-        <v>2</v>
+      <c r="J88" s="7">
+        <v>1</v>
       </c>
       <c r="K88" s="7">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="L88" s="40" t="s">
-        <v>337</v>
-      </c>
-      <c r="M88" s="24">
-        <v>0.35</v>
-      </c>
-      <c r="N88" s="47">
-        <f t="shared" si="4"/>
-        <v>3.5</v>
-      </c>
-      <c r="O88" s="23"/>
-    </row>
-    <row r="89" spans="1:22" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="L88" s="30" t="s">
+        <v>337</v>
+      </c>
+      <c r="M88" s="14">
+        <v>4.66</v>
+      </c>
+      <c r="N88" s="37">
+        <f t="shared" si="6"/>
+        <v>23.3</v>
+      </c>
+      <c r="O88" s="7"/>
+    </row>
+    <row r="89" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="11">
-        <f t="shared" ref="B89:B90" si="5">ROW(B89) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>87</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>354</v>
+        <v>21</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>336</v>
+        <v>86</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>398</v>
+        <v>161</v>
       </c>
       <c r="F89" s="9" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>399</v>
+        <v>200</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>400</v>
-      </c>
-      <c r="I89" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="I89" s="8" t="s">
         <v>336</v>
       </c>
       <c r="J89" s="9">
         <v>1</v>
       </c>
       <c r="K89" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="L89" s="41" t="s">
-        <v>349</v>
-      </c>
-      <c r="M89" s="43">
-        <v>1.5257000000000001</v>
-      </c>
-      <c r="N89" s="48">
-        <f t="shared" si="4"/>
-        <v>7.6285000000000007</v>
+      <c r="L89" s="30" t="s">
+        <v>337</v>
+      </c>
+      <c r="M89" s="14">
+        <v>3</v>
+      </c>
+      <c r="N89" s="37">
+        <f t="shared" si="6"/>
+        <v>15</v>
       </c>
       <c r="O89" s="9"/>
     </row>
-    <row r="90" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:23" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="11">
+        <f>ROW(B90) - ROW($B$2)</f>
+        <v>88</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E90" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="F90" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="G90" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="H90" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="I90" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="J90" s="7">
+        <v>1</v>
+      </c>
+      <c r="K90" s="7">
         <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="L90" s="30" t="s">
+        <v>349</v>
+      </c>
+      <c r="M90" s="14">
+        <v>2.6663999999999999</v>
+      </c>
+      <c r="N90" s="37">
+        <f t="shared" si="6"/>
+        <v>13.331999999999999</v>
+      </c>
+      <c r="O90" s="7"/>
+    </row>
+    <row r="91" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="1"/>
+      <c r="B91" s="11">
+        <f t="shared" si="0"/>
+        <v>89</v>
+      </c>
+      <c r="C91" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D91" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="C90" s="32" t="s">
+      <c r="E91" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="F91" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="G91" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="H91" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="I91" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="J91" s="9">
+        <v>1</v>
+      </c>
+      <c r="K91" s="7">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="L91" s="30" t="s">
+        <v>337</v>
+      </c>
+      <c r="M91" s="14">
+        <v>4.51</v>
+      </c>
+      <c r="N91" s="37">
+        <f t="shared" si="6"/>
+        <v>22.549999999999997</v>
+      </c>
+      <c r="O91" s="9"/>
+    </row>
+    <row r="92" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="1"/>
+      <c r="B92" s="11">
+        <f>ROW(B92) - ROW($B$2)</f>
+        <v>90</v>
+      </c>
+      <c r="C92" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="G92" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="H92" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="I92" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="J92" s="7">
+        <v>4</v>
+      </c>
+      <c r="K92" s="7">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L92" s="30" t="s">
+        <v>337</v>
+      </c>
+      <c r="M92" s="14">
+        <v>0.68</v>
+      </c>
+      <c r="N92" s="37">
+        <f t="shared" si="6"/>
+        <v>13.600000000000001</v>
+      </c>
+      <c r="O92" s="7"/>
+    </row>
+    <row r="93" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="1"/>
+      <c r="B93" s="11">
+        <f t="shared" si="0"/>
+        <v>91</v>
+      </c>
+      <c r="C93" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D93" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E93" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="F93" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="G93" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="H93" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="I93" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="J93" s="9">
+        <v>2</v>
+      </c>
+      <c r="K93" s="7">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="L93" s="30" t="s">
+        <v>337</v>
+      </c>
+      <c r="M93" s="14">
+        <v>5.2880000000000003</v>
+      </c>
+      <c r="N93" s="37">
+        <f t="shared" si="6"/>
+        <v>52.88</v>
+      </c>
+      <c r="O93" s="9"/>
+    </row>
+    <row r="94" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="1"/>
+      <c r="B94" s="11">
+        <f>ROW(B94) - ROW($B$2)</f>
+        <v>92</v>
+      </c>
+      <c r="C94" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="G94" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="H94" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="I94" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="J94" s="7">
+        <v>1</v>
+      </c>
+      <c r="K94" s="7">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="L94" s="30" t="s">
+        <v>337</v>
+      </c>
+      <c r="M94" s="14">
+        <v>0.95</v>
+      </c>
+      <c r="N94" s="37">
+        <f t="shared" si="6"/>
+        <v>4.75</v>
+      </c>
+      <c r="O94" s="7"/>
+    </row>
+    <row r="95" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B95" s="11">
+        <f t="shared" ref="B95" si="7">ROW(B95) - ROW($B$2)</f>
+        <v>93</v>
+      </c>
+      <c r="C95" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D95" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="E95" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="F95" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="G95" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="H95" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="I95" s="10"/>
+      <c r="J95" s="9">
+        <v>8</v>
+      </c>
+      <c r="K95" s="7">
+        <f t="shared" si="5"/>
+        <v>40</v>
+      </c>
+      <c r="L95" s="32" t="s">
+        <v>337</v>
+      </c>
+      <c r="M95" s="14">
+        <v>2.98</v>
+      </c>
+      <c r="N95" s="37">
+        <f t="shared" si="6"/>
+        <v>119.2</v>
+      </c>
+      <c r="O95" s="23"/>
+    </row>
+    <row r="96" spans="1:23" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B96" s="11">
+        <f>ROW(B96) - ROW($B$2)</f>
+        <v>94</v>
+      </c>
+      <c r="C96" s="13" t="s">
         <v>354</v>
       </c>
-      <c r="D90" s="34" t="s">
+      <c r="D96" s="23" t="s">
         <v>336</v>
       </c>
-      <c r="E90" s="34" t="s">
-        <v>401</v>
-      </c>
-      <c r="F90" s="34" t="s">
+      <c r="E96" s="23" t="s">
+        <v>355</v>
+      </c>
+      <c r="F96" s="23" t="s">
         <v>336</v>
       </c>
-      <c r="G90" s="35" t="s">
-        <v>402</v>
-      </c>
-      <c r="H90" s="34" t="s">
-        <v>403</v>
-      </c>
-      <c r="I90" s="35" t="s">
+      <c r="G96" s="22" t="s">
+        <v>356</v>
+      </c>
+      <c r="H96" s="23" t="s">
+        <v>357</v>
+      </c>
+      <c r="I96" s="22" t="s">
         <v>336</v>
       </c>
-      <c r="J90" s="34">
+      <c r="J96" s="23">
+        <v>2</v>
+      </c>
+      <c r="K96" s="7">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="L96" s="32" t="s">
+        <v>337</v>
+      </c>
+      <c r="M96" s="24">
+        <v>0.35</v>
+      </c>
+      <c r="N96" s="39">
+        <f t="shared" si="6"/>
+        <v>3.5</v>
+      </c>
+      <c r="O96" s="23"/>
+    </row>
+    <row r="97" spans="2:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B97" s="11">
+        <f t="shared" ref="B97:B98" si="8">ROW(B97) - ROW($B$2)</f>
+        <v>95</v>
+      </c>
+      <c r="C97" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="D97" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="E97" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="F97" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="G97" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="H97" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="I97" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="J97" s="9">
         <v>1</v>
       </c>
-      <c r="K90" s="33">
-        <f t="shared" si="3"/>
+      <c r="K97" s="7">
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="L90" s="42" t="s">
+      <c r="L97" s="33" t="s">
         <v>349</v>
       </c>
-      <c r="M90" s="44">
+      <c r="M97" s="35">
+        <v>0.73499999999999999</v>
+      </c>
+      <c r="N97" s="40">
+        <f t="shared" si="6"/>
+        <v>3.6749999999999998</v>
+      </c>
+      <c r="O97" s="9"/>
+    </row>
+    <row r="98" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B98" s="11">
+        <f t="shared" si="8"/>
+        <v>96</v>
+      </c>
+      <c r="C98" s="25" t="s">
+        <v>354</v>
+      </c>
+      <c r="D98" s="26" t="s">
+        <v>336</v>
+      </c>
+      <c r="E98" s="26" t="s">
+        <v>427</v>
+      </c>
+      <c r="F98" s="26" t="s">
+        <v>336</v>
+      </c>
+      <c r="G98" s="27" t="s">
+        <v>426</v>
+      </c>
+      <c r="H98" s="26" t="s">
+        <v>394</v>
+      </c>
+      <c r="I98" s="27" t="s">
+        <v>336</v>
+      </c>
+      <c r="J98" s="26">
+        <v>1</v>
+      </c>
+      <c r="K98" s="7">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="L98" s="34" t="s">
+        <v>349</v>
+      </c>
+      <c r="M98" s="36">
         <v>1.2457</v>
       </c>
-      <c r="N90" s="49">
-        <f t="shared" si="4"/>
+      <c r="N98" s="41">
+        <f t="shared" si="6"/>
         <v>6.2285000000000004</v>
       </c>
-      <c r="O90" s="34"/>
-    </row>
-    <row r="91" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="1"/>
-      <c r="B91" s="1"/>
-      <c r="C91" s="1"/>
-      <c r="D91" s="1"/>
-      <c r="E91" s="1"/>
-      <c r="F91" s="1"/>
-      <c r="G91" s="1"/>
-      <c r="H91" s="1"/>
-      <c r="I91" s="1"/>
-      <c r="J91" s="1"/>
-      <c r="K91" s="26" t="s">
+      <c r="O98" s="26"/>
+    </row>
+    <row r="99" spans="2:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B99" s="1"/>
+      <c r="C99" s="1"/>
+      <c r="D99" s="1"/>
+      <c r="E99" s="1"/>
+      <c r="F99" s="1"/>
+      <c r="G99" s="1"/>
+      <c r="H99" s="1"/>
+      <c r="I99" s="1"/>
+      <c r="J99" s="1"/>
+      <c r="K99" s="43" t="s">
         <v>350</v>
       </c>
-      <c r="L91" s="27"/>
-      <c r="M91" s="28"/>
-      <c r="N91" s="21">
-        <f>SUM(N10:N90)</f>
-        <v>536.35930000000008</v>
-      </c>
-      <c r="O91" s="1"/>
-    </row>
-    <row r="92" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="1"/>
-      <c r="B92" s="1"/>
-      <c r="C92" s="1"/>
-      <c r="D92" s="1"/>
-      <c r="E92" s="1"/>
-      <c r="F92" s="1"/>
-      <c r="G92" s="1"/>
-      <c r="H92" s="1"/>
-      <c r="I92" s="1"/>
-      <c r="J92" s="1"/>
-      <c r="K92" s="29" t="s">
+      <c r="L99" s="44"/>
+      <c r="M99" s="45"/>
+      <c r="N99" s="21">
+        <f>SUM(N10:N98)</f>
+        <v>679.78879999999992</v>
+      </c>
+      <c r="O99" s="1"/>
+    </row>
+    <row r="100" spans="2:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B100" s="1"/>
+      <c r="C100" s="1"/>
+      <c r="D100" s="1"/>
+      <c r="E100" s="1"/>
+      <c r="F100" s="1"/>
+      <c r="G100" s="1"/>
+      <c r="H100" s="1"/>
+      <c r="I100" s="1"/>
+      <c r="J100" s="1"/>
+      <c r="K100" s="46" t="s">
         <v>348</v>
       </c>
-      <c r="L92" s="30"/>
-      <c r="M92" s="31"/>
-      <c r="N92" s="20">
-        <f>N91/5</f>
-        <v>107.27186000000002</v>
-      </c>
-      <c r="O92" s="1"/>
-    </row>
-    <row r="93" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A93" s="1"/>
-    </row>
-    <row r="94" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A94" s="1"/>
+      <c r="L100" s="47"/>
+      <c r="M100" s="48"/>
+      <c r="N100" s="20">
+        <f>N99/5</f>
+        <v>135.95775999999998</v>
+      </c>
+      <c r="O100" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="I1:O1"/>
-    <mergeCell ref="K91:M91"/>
-    <mergeCell ref="K92:M92"/>
+    <mergeCell ref="K99:M99"/>
+    <mergeCell ref="K100:M100"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="L3" r:id="rId1"/>
@@ -6251,79 +6687,87 @@
     <hyperlink ref="L16" r:id="rId14"/>
     <hyperlink ref="L17" r:id="rId15"/>
     <hyperlink ref="L18" r:id="rId16"/>
-    <hyperlink ref="L19" r:id="rId17"/>
-    <hyperlink ref="L20" r:id="rId18"/>
-    <hyperlink ref="L21" r:id="rId19"/>
-    <hyperlink ref="L22" r:id="rId20"/>
-    <hyperlink ref="L23" r:id="rId21"/>
-    <hyperlink ref="L24" r:id="rId22"/>
-    <hyperlink ref="L26" r:id="rId23"/>
-    <hyperlink ref="L27" r:id="rId24"/>
-    <hyperlink ref="L29" r:id="rId25"/>
-    <hyperlink ref="L36" r:id="rId26"/>
-    <hyperlink ref="L37" r:id="rId27"/>
-    <hyperlink ref="L38" r:id="rId28"/>
-    <hyperlink ref="L43" r:id="rId29"/>
-    <hyperlink ref="L44" r:id="rId30"/>
-    <hyperlink ref="L45" r:id="rId31"/>
-    <hyperlink ref="L46" r:id="rId32"/>
-    <hyperlink ref="L47" r:id="rId33"/>
-    <hyperlink ref="L48" r:id="rId34"/>
-    <hyperlink ref="L49" r:id="rId35"/>
-    <hyperlink ref="L50" r:id="rId36"/>
-    <hyperlink ref="L51" r:id="rId37"/>
-    <hyperlink ref="L52" r:id="rId38"/>
-    <hyperlink ref="L53" r:id="rId39"/>
-    <hyperlink ref="L54" r:id="rId40"/>
-    <hyperlink ref="L55" r:id="rId41"/>
-    <hyperlink ref="L56" r:id="rId42"/>
-    <hyperlink ref="L57" r:id="rId43"/>
-    <hyperlink ref="L58" r:id="rId44"/>
-    <hyperlink ref="L59" r:id="rId45"/>
-    <hyperlink ref="L60" r:id="rId46"/>
-    <hyperlink ref="L63" r:id="rId47"/>
-    <hyperlink ref="L64" r:id="rId48"/>
-    <hyperlink ref="L65" r:id="rId49"/>
-    <hyperlink ref="L66" r:id="rId50"/>
-    <hyperlink ref="L67" r:id="rId51"/>
-    <hyperlink ref="L70" r:id="rId52"/>
-    <hyperlink ref="L62" r:id="rId53"/>
-    <hyperlink ref="L71" r:id="rId54"/>
-    <hyperlink ref="L74" r:id="rId55"/>
-    <hyperlink ref="L75" r:id="rId56"/>
-    <hyperlink ref="L76" r:id="rId57"/>
-    <hyperlink ref="L77" r:id="rId58"/>
-    <hyperlink ref="L78" r:id="rId59"/>
-    <hyperlink ref="L79" r:id="rId60"/>
-    <hyperlink ref="L80" r:id="rId61"/>
-    <hyperlink ref="L81" r:id="rId62"/>
-    <hyperlink ref="L82" r:id="rId63"/>
-    <hyperlink ref="L84" r:id="rId64"/>
-    <hyperlink ref="L85" r:id="rId65"/>
-    <hyperlink ref="L86" r:id="rId66"/>
-    <hyperlink ref="L87" r:id="rId67"/>
-    <hyperlink ref="L25" r:id="rId68"/>
-    <hyperlink ref="L32" r:id="rId69"/>
-    <hyperlink ref="L39" r:id="rId70"/>
-    <hyperlink ref="L40" r:id="rId71"/>
-    <hyperlink ref="L41" r:id="rId72"/>
-    <hyperlink ref="L42" r:id="rId73"/>
-    <hyperlink ref="L83" r:id="rId74"/>
-    <hyperlink ref="L33" r:id="rId75"/>
-    <hyperlink ref="L88" r:id="rId76"/>
-    <hyperlink ref="L28" r:id="rId77"/>
-    <hyperlink ref="L72" r:id="rId78"/>
-    <hyperlink ref="L34" r:id="rId79"/>
-    <hyperlink ref="L35" r:id="rId80"/>
-    <hyperlink ref="L68" r:id="rId81"/>
-    <hyperlink ref="L69" r:id="rId82"/>
-    <hyperlink ref="L30" r:id="rId83"/>
-    <hyperlink ref="L31" r:id="rId84"/>
-    <hyperlink ref="L61" r:id="rId85"/>
-    <hyperlink ref="L89" r:id="rId86"/>
-    <hyperlink ref="L90" r:id="rId87"/>
+    <hyperlink ref="L23" r:id="rId17"/>
+    <hyperlink ref="L24" r:id="rId18"/>
+    <hyperlink ref="L25" r:id="rId19"/>
+    <hyperlink ref="L26" r:id="rId20"/>
+    <hyperlink ref="L27" r:id="rId21"/>
+    <hyperlink ref="L28" r:id="rId22"/>
+    <hyperlink ref="L30" r:id="rId23"/>
+    <hyperlink ref="L31" r:id="rId24"/>
+    <hyperlink ref="L33" r:id="rId25"/>
+    <hyperlink ref="L40" r:id="rId26"/>
+    <hyperlink ref="L41" r:id="rId27"/>
+    <hyperlink ref="L42" r:id="rId28"/>
+    <hyperlink ref="L47" r:id="rId29"/>
+    <hyperlink ref="L48" r:id="rId30"/>
+    <hyperlink ref="L49" r:id="rId31"/>
+    <hyperlink ref="L50" r:id="rId32"/>
+    <hyperlink ref="L51" r:id="rId33"/>
+    <hyperlink ref="L52" r:id="rId34"/>
+    <hyperlink ref="L53" r:id="rId35"/>
+    <hyperlink ref="L54" r:id="rId36"/>
+    <hyperlink ref="L55" r:id="rId37"/>
+    <hyperlink ref="L56" r:id="rId38"/>
+    <hyperlink ref="L57" r:id="rId39"/>
+    <hyperlink ref="L58" r:id="rId40"/>
+    <hyperlink ref="L59" r:id="rId41"/>
+    <hyperlink ref="L60" r:id="rId42"/>
+    <hyperlink ref="L61" r:id="rId43"/>
+    <hyperlink ref="L62" r:id="rId44"/>
+    <hyperlink ref="L63" r:id="rId45"/>
+    <hyperlink ref="L64" r:id="rId46"/>
+    <hyperlink ref="L67" r:id="rId47"/>
+    <hyperlink ref="L68" r:id="rId48"/>
+    <hyperlink ref="L69" r:id="rId49"/>
+    <hyperlink ref="L70" r:id="rId50"/>
+    <hyperlink ref="L71" r:id="rId51"/>
+    <hyperlink ref="L74" r:id="rId52"/>
+    <hyperlink ref="L66" r:id="rId53"/>
+    <hyperlink ref="L75" r:id="rId54"/>
+    <hyperlink ref="L81" r:id="rId55"/>
+    <hyperlink ref="L82" r:id="rId56"/>
+    <hyperlink ref="L83" r:id="rId57"/>
+    <hyperlink ref="L84" r:id="rId58"/>
+    <hyperlink ref="L85" r:id="rId59"/>
+    <hyperlink ref="L86" r:id="rId60"/>
+    <hyperlink ref="L87" r:id="rId61"/>
+    <hyperlink ref="L88" r:id="rId62"/>
+    <hyperlink ref="L89" r:id="rId63"/>
+    <hyperlink ref="L91" r:id="rId64"/>
+    <hyperlink ref="L92" r:id="rId65"/>
+    <hyperlink ref="L93" r:id="rId66"/>
+    <hyperlink ref="L94" r:id="rId67"/>
+    <hyperlink ref="L29" r:id="rId68"/>
+    <hyperlink ref="L36" r:id="rId69"/>
+    <hyperlink ref="L43" r:id="rId70"/>
+    <hyperlink ref="L44" r:id="rId71"/>
+    <hyperlink ref="L45" r:id="rId72"/>
+    <hyperlink ref="L46" r:id="rId73"/>
+    <hyperlink ref="L90" r:id="rId74"/>
+    <hyperlink ref="L37" r:id="rId75"/>
+    <hyperlink ref="L96" r:id="rId76"/>
+    <hyperlink ref="L32" r:id="rId77"/>
+    <hyperlink ref="L76" r:id="rId78"/>
+    <hyperlink ref="L38" r:id="rId79"/>
+    <hyperlink ref="L39" r:id="rId80"/>
+    <hyperlink ref="L72" r:id="rId81"/>
+    <hyperlink ref="L73" r:id="rId82"/>
+    <hyperlink ref="L34" r:id="rId83"/>
+    <hyperlink ref="L65" r:id="rId84"/>
+    <hyperlink ref="L98" r:id="rId85"/>
+    <hyperlink ref="L19" r:id="rId86"/>
+    <hyperlink ref="L20" r:id="rId87"/>
+    <hyperlink ref="L21" r:id="rId88"/>
+    <hyperlink ref="L77" r:id="rId89"/>
+    <hyperlink ref="L78" r:id="rId90"/>
+    <hyperlink ref="L79" r:id="rId91"/>
+    <hyperlink ref="L95" r:id="rId92"/>
+    <hyperlink ref="L97" r:id="rId93"/>
+    <hyperlink ref="L22" r:id="rId94"/>
+    <hyperlink ref="L35" r:id="rId95"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId88"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId96"/>
 </worksheet>
 </file>
--- a/Design-Files/FMM-v1.0/BOM/Client-BOM-FMM-v1.0.xlsx
+++ b/Design-Files/FMM-v1.0/BOM/Client-BOM-FMM-v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="432">
   <si>
     <t>#</t>
   </si>
@@ -1324,7 +1324,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1395,6 +1395,21 @@
       <b/>
       <sz val="14"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1684,7 +1699,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1831,6 +1846,21 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3362,42 +3392,43 @@
       <c r="C28" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="E28" s="50" t="s">
         <v>113</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="F28" s="50" t="s">
         <v>178</v>
       </c>
-      <c r="G28" s="10" t="s">
+      <c r="G28" s="51" t="s">
         <v>225</v>
       </c>
-      <c r="H28" s="9" t="s">
+      <c r="H28" s="50" t="s">
         <v>277</v>
       </c>
-      <c r="I28" s="8" t="s">
+      <c r="I28" s="52" t="s">
         <v>336</v>
       </c>
-      <c r="J28" s="9">
+      <c r="J28" s="50">
         <v>1</v>
       </c>
-      <c r="K28" s="7">
+      <c r="K28" s="53">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="L28" s="30" t="s">
         <v>337</v>
       </c>
-      <c r="M28" s="14">
-        <v>0.41</v>
-      </c>
-      <c r="N28" s="37">
-        <f t="shared" si="2"/>
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="O28" s="9"/>
+      <c r="M28" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="N28" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="O28" s="49" t="s">
+        <v>347</v>
+      </c>
     </row>
     <row r="29" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
@@ -6639,7 +6670,7 @@
       <c r="M99" s="45"/>
       <c r="N99" s="21">
         <f>SUM(N10:N98)</f>
-        <v>679.78879999999992</v>
+        <v>677.73879999999997</v>
       </c>
       <c r="O99" s="1"/>
     </row>
@@ -6660,7 +6691,7 @@
       <c r="M100" s="48"/>
       <c r="N100" s="20">
         <f>N99/5</f>
-        <v>135.95775999999998</v>
+        <v>135.54775999999998</v>
       </c>
       <c r="O100" s="1"/>
     </row>

--- a/Design-Files/FMM-v1.0/BOM/Client-BOM-FMM-v1.0.xlsx
+++ b/Design-Files/FMM-v1.0/BOM/Client-BOM-FMM-v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="435">
   <si>
     <t>#</t>
   </si>
@@ -1315,6 +1315,15 @@
   </si>
   <si>
     <t>R2, R69</t>
+  </si>
+  <si>
+    <t>Voltlink</t>
+  </si>
+  <si>
+    <t>Tinde</t>
+  </si>
+  <si>
+    <t>VoltLink CP2102N USB Serial Adapter &amp; Programmer</t>
   </si>
 </sst>
 </file>
@@ -1699,7 +1708,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1760,13 +1769,7 @@
     <xf numFmtId="164" fontId="8" fillId="3" borderId="13" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1811,13 +1814,25 @@
     <xf numFmtId="164" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1846,21 +1861,6 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2150,7 +2150,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:W100"/>
+  <dimension ref="A1:Z101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="4" customWidth="1"/>
@@ -2168,10 +2168,13 @@
     <col min="14" max="14" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="29.42578125" customWidth="1"/>
     <col min="16" max="16" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="36" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="25.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -2180,15 +2183,17 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-    </row>
-    <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+    </row>
+    <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="5" t="s">
         <v>0</v>
@@ -2220,7 +2225,7 @@
       <c r="K2" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="L2" s="28" t="s">
+      <c r="L2" s="26" t="s">
         <v>335</v>
       </c>
       <c r="M2" s="5" t="s">
@@ -2233,7 +2238,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="11">
         <f>ROW(B3) - ROW($B$2)</f>
@@ -2267,19 +2272,31 @@
         <f>J3*5</f>
         <v>45</v>
       </c>
-      <c r="L3" s="29" t="s">
+      <c r="L3" s="27" t="s">
         <v>337</v>
       </c>
       <c r="M3" s="14">
         <v>0.124</v>
       </c>
-      <c r="N3" s="37">
+      <c r="N3" s="35">
         <f>M3*K3</f>
         <v>5.58</v>
       </c>
       <c r="O3" s="7"/>
-    </row>
-    <row r="4" spans="1:15" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T3" t="b">
+        <f>IF(Q3=D3,TRUE,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <f>IF(R3=G3,TRUE,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="V3" t="b">
+        <f>IF(S3=J3,TRUE,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="11">
         <f t="shared" ref="B4:B93" si="0">ROW(B4) - ROW($B$2)</f>
@@ -2313,19 +2330,31 @@
         <f t="shared" ref="K4:K68" si="1">J4*5</f>
         <v>155</v>
       </c>
-      <c r="L4" s="30" t="s">
+      <c r="L4" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M4" s="14">
         <v>1.9400000000000001E-2</v>
       </c>
-      <c r="N4" s="37">
+      <c r="N4" s="35">
         <f t="shared" ref="N4:N74" si="2">M4*K4</f>
         <v>3.0070000000000001</v>
       </c>
       <c r="O4" s="9"/>
-    </row>
-    <row r="5" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T4" t="b">
+        <f t="shared" ref="T4:T67" si="3">IF(Q4=D4,TRUE,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <f t="shared" ref="U4:U67" si="4">IF(R4=G4,TRUE,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="V4" t="b">
+        <f t="shared" ref="V4:V67" si="5">IF(S4=J4,TRUE,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="11">
         <f>ROW(B5) - ROW($B$2)</f>
@@ -2359,19 +2388,31 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L5" s="30" t="s">
+      <c r="L5" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M5" s="14">
         <v>0.92100000000000004</v>
       </c>
-      <c r="N5" s="37">
+      <c r="N5" s="35">
         <f t="shared" si="2"/>
         <v>9.2100000000000009</v>
       </c>
       <c r="O5" s="7"/>
-    </row>
-    <row r="6" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T5" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V5" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="11">
         <f t="shared" si="0"/>
@@ -2405,19 +2446,31 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L6" s="30" t="s">
+      <c r="L6" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M6" s="14">
         <v>1.0389999999999999</v>
       </c>
-      <c r="N6" s="37">
+      <c r="N6" s="35">
         <f t="shared" si="2"/>
         <v>10.389999999999999</v>
       </c>
       <c r="O6" s="9"/>
-    </row>
-    <row r="7" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T6" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V6" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="11">
         <f>ROW(B7) - ROW($B$2)</f>
@@ -2451,19 +2504,31 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L7" s="30" t="s">
+      <c r="L7" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M7" s="14">
         <v>0.22</v>
       </c>
-      <c r="N7" s="37">
+      <c r="N7" s="35">
         <f t="shared" si="2"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="O7" s="7"/>
-    </row>
-    <row r="8" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T7" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V7" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="11">
         <f t="shared" si="0"/>
@@ -2497,19 +2562,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L8" s="30" t="s">
+      <c r="L8" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M8" s="14">
         <v>0.1</v>
       </c>
-      <c r="N8" s="37">
+      <c r="N8" s="35">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="O8" s="9"/>
-    </row>
-    <row r="9" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T8" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V8" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="11">
         <f>ROW(B9) - ROW($B$2)</f>
@@ -2543,19 +2620,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L9" s="30" t="s">
+      <c r="L9" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M9" s="14">
         <v>0.1</v>
       </c>
-      <c r="N9" s="37">
+      <c r="N9" s="35">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="O9" s="7"/>
-    </row>
-    <row r="10" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T9" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V9" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="11">
         <f t="shared" si="0"/>
@@ -2589,19 +2678,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L10" s="30" t="s">
+      <c r="L10" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M10" s="14">
         <v>0.1</v>
       </c>
-      <c r="N10" s="37">
+      <c r="N10" s="35">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="O10" s="9"/>
-    </row>
-    <row r="11" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T10" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V10" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="11">
         <f>ROW(B11) - ROW($B$2)</f>
@@ -2635,19 +2736,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L11" s="30" t="s">
+      <c r="L11" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M11" s="14">
         <v>0.1</v>
       </c>
-      <c r="N11" s="37">
+      <c r="N11" s="35">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="O11" s="7"/>
-    </row>
-    <row r="12" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T11" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U11" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V11" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="11">
         <f t="shared" si="0"/>
@@ -2681,19 +2794,31 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="L12" s="30" t="s">
+      <c r="L12" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M12" s="14">
         <v>0.22600000000000001</v>
       </c>
-      <c r="N12" s="37">
+      <c r="N12" s="35">
         <f t="shared" si="2"/>
         <v>3.39</v>
       </c>
       <c r="O12" s="9"/>
-    </row>
-    <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T12" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U12" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V12" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="11">
         <f>ROW(B13) - ROW($B$2)</f>
@@ -2727,19 +2852,31 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L13" s="30" t="s">
+      <c r="L13" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M13" s="14">
         <v>0.73699999999999999</v>
       </c>
-      <c r="N13" s="37">
+      <c r="N13" s="35">
         <f t="shared" si="2"/>
         <v>7.37</v>
       </c>
       <c r="O13" s="7"/>
-    </row>
-    <row r="14" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T13" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U13" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V13" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="11">
         <f t="shared" si="0"/>
@@ -2773,19 +2910,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L14" s="30" t="s">
+      <c r="L14" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M14" s="14">
         <v>0.22</v>
       </c>
-      <c r="N14" s="37">
+      <c r="N14" s="35">
         <f t="shared" si="2"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="O14" s="9"/>
-    </row>
-    <row r="15" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T14" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U14" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V14" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="11">
         <f>ROW(B15) - ROW($B$2)</f>
@@ -2819,19 +2968,31 @@
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="L15" s="30" t="s">
+      <c r="L15" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M15" s="14">
         <v>0.26</v>
       </c>
-      <c r="N15" s="37">
+      <c r="N15" s="35">
         <f t="shared" si="2"/>
         <v>9.1</v>
       </c>
       <c r="O15" s="7"/>
-    </row>
-    <row r="16" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T15" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U15" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="11">
         <f t="shared" si="0"/>
@@ -2865,19 +3026,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L16" s="30" t="s">
+      <c r="L16" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M16" s="14">
         <v>0.45</v>
       </c>
-      <c r="N16" s="37">
+      <c r="N16" s="35">
         <f t="shared" si="2"/>
         <v>2.25</v>
       </c>
       <c r="O16" s="9"/>
-    </row>
-    <row r="17" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T16" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U16" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="11">
         <f>ROW(B17) - ROW($B$2)</f>
@@ -2911,19 +3084,31 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L17" s="30" t="s">
+      <c r="L17" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M17" s="14">
         <v>0.11899999999999999</v>
       </c>
-      <c r="N17" s="37">
+      <c r="N17" s="35">
         <f t="shared" si="2"/>
         <v>1.19</v>
       </c>
       <c r="O17" s="7"/>
-    </row>
-    <row r="18" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T17" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U17" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V17" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="11">
         <f t="shared" si="0"/>
@@ -2957,19 +3142,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L18" s="30" t="s">
+      <c r="L18" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M18" s="14">
         <v>0.48</v>
       </c>
-      <c r="N18" s="37">
+      <c r="N18" s="35">
         <f t="shared" si="2"/>
         <v>2.4</v>
       </c>
       <c r="O18" s="9"/>
-    </row>
-    <row r="19" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T18" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U18" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="11">
         <f>ROW(B19) - ROW($B$2)</f>
@@ -3003,22 +3200,34 @@
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="L19" s="30" t="s">
+      <c r="L19" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M19" s="14">
         <v>0.1</v>
       </c>
-      <c r="N19" s="37">
+      <c r="N19" s="35">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="O19" s="7"/>
-    </row>
-    <row r="20" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T19" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U19" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V19" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="11">
-        <f t="shared" ref="B20" si="3">ROW(B20) - ROW($B$2)</f>
+        <f t="shared" ref="B20" si="6">ROW(B20) - ROW($B$2)</f>
         <v>18</v>
       </c>
       <c r="C20" s="13" t="s">
@@ -3049,19 +3258,31 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L20" s="30" t="s">
+      <c r="L20" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M20" s="14">
         <v>0.1</v>
       </c>
-      <c r="N20" s="37">
+      <c r="N20" s="35">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="O20" s="7"/>
-    </row>
-    <row r="21" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T20" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U20" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V20" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="11">
         <f>ROW(B21) - ROW($B$2)</f>
@@ -3095,22 +3316,34 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L21" s="30" t="s">
+      <c r="L21" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M21" s="14">
         <v>0.1</v>
       </c>
-      <c r="N21" s="37">
+      <c r="N21" s="35">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="O21" s="7"/>
-    </row>
-    <row r="22" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T21" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U21" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V21" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="11">
-        <f t="shared" ref="B22" si="4">ROW(B22) - ROW($B$2)</f>
+        <f t="shared" ref="B22" si="7">ROW(B22) - ROW($B$2)</f>
         <v>20</v>
       </c>
       <c r="C22" s="13" t="s">
@@ -3141,19 +3374,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L22" s="30" t="s">
+      <c r="L22" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M22" s="14">
         <v>0.37</v>
       </c>
-      <c r="N22" s="37">
+      <c r="N22" s="35">
         <f t="shared" si="2"/>
         <v>1.85</v>
       </c>
       <c r="O22" s="7"/>
-    </row>
-    <row r="23" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T22" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U22" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V22" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="11">
         <f>ROW(B23) - ROW($B$2)</f>
@@ -3187,19 +3432,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L23" s="30" t="s">
+      <c r="L23" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M23" s="14">
         <v>2.96</v>
       </c>
-      <c r="N23" s="37">
+      <c r="N23" s="35">
         <f t="shared" si="2"/>
         <v>14.8</v>
       </c>
       <c r="O23" s="7"/>
-    </row>
-    <row r="24" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T23" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U23" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V23" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="11">
         <f t="shared" si="0"/>
@@ -3233,19 +3490,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L24" s="30" t="s">
+      <c r="L24" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M24" s="14">
         <v>0.91</v>
       </c>
-      <c r="N24" s="37">
+      <c r="N24" s="35">
         <f t="shared" si="2"/>
         <v>4.55</v>
       </c>
       <c r="O24" s="9"/>
-    </row>
-    <row r="25" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T24" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U24" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V24" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="11">
         <f>ROW(B25) - ROW($B$2)</f>
@@ -3279,19 +3548,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L25" s="30" t="s">
+      <c r="L25" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M25" s="14">
         <v>0.21</v>
       </c>
-      <c r="N25" s="37">
+      <c r="N25" s="35">
         <f t="shared" si="2"/>
         <v>1.05</v>
       </c>
       <c r="O25" s="7"/>
-    </row>
-    <row r="26" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T25" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U25" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V25" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="11">
         <f t="shared" si="0"/>
@@ -3325,19 +3606,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L26" s="30" t="s">
+      <c r="L26" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M26" s="14">
         <v>0.38</v>
       </c>
-      <c r="N26" s="37">
+      <c r="N26" s="35">
         <f t="shared" si="2"/>
         <v>1.9</v>
       </c>
       <c r="O26" s="9"/>
-    </row>
-    <row r="27" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T26" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U26" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="11">
         <f>ROW(B27) - ROW($B$2)</f>
@@ -3371,19 +3664,31 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L27" s="30" t="s">
+      <c r="L27" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M27" s="14">
         <v>0.255</v>
       </c>
-      <c r="N27" s="37">
+      <c r="N27" s="35">
         <f t="shared" si="2"/>
         <v>2.5499999999999998</v>
       </c>
       <c r="O27" s="7"/>
-    </row>
-    <row r="28" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T27" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U27" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V27" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="11">
         <f t="shared" si="0"/>
@@ -3392,45 +3697,57 @@
       <c r="C28" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D28" s="50" t="s">
+      <c r="D28" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="E28" s="50" t="s">
+      <c r="E28" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="F28" s="50" t="s">
+      <c r="F28" s="40" t="s">
         <v>178</v>
       </c>
-      <c r="G28" s="51" t="s">
+      <c r="G28" s="41" t="s">
         <v>225</v>
       </c>
-      <c r="H28" s="50" t="s">
+      <c r="H28" s="40" t="s">
         <v>277</v>
       </c>
-      <c r="I28" s="52" t="s">
+      <c r="I28" s="42" t="s">
         <v>336</v>
       </c>
-      <c r="J28" s="50">
+      <c r="J28" s="40">
         <v>1</v>
       </c>
-      <c r="K28" s="53">
+      <c r="K28" s="43">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L28" s="30" t="s">
+      <c r="L28" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M28" s="14" t="s">
         <v>336</v>
       </c>
-      <c r="N28" s="37" t="s">
+      <c r="N28" s="35" t="s">
         <v>336</v>
       </c>
-      <c r="O28" s="49" t="s">
+      <c r="O28" s="39" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T28" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U28" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V28" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="11">
         <f>ROW(B29) - ROW($B$2)</f>
@@ -3464,19 +3781,31 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="L29" s="30" t="s">
+      <c r="L29" s="28" t="s">
         <v>349</v>
       </c>
       <c r="M29" s="14">
         <v>1.54E-2</v>
       </c>
-      <c r="N29" s="37">
+      <c r="N29" s="35">
         <f t="shared" si="2"/>
         <v>0.23100000000000001</v>
       </c>
       <c r="O29" s="7"/>
-    </row>
-    <row r="30" spans="1:15" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T29" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U29" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V29" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="11">
         <f t="shared" si="0"/>
@@ -3510,19 +3839,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L30" s="30" t="s">
+      <c r="L30" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M30" s="14">
         <v>1.5</v>
       </c>
-      <c r="N30" s="37">
+      <c r="N30" s="35">
         <f t="shared" si="2"/>
         <v>7.5</v>
       </c>
       <c r="O30" s="9"/>
-    </row>
-    <row r="31" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T30" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U30" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V30" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="11">
         <f>ROW(B31) - ROW($B$2)</f>
@@ -3556,19 +3897,31 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L31" s="30" t="s">
+      <c r="L31" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M31" s="14">
         <v>0.26900000000000002</v>
       </c>
-      <c r="N31" s="37">
+      <c r="N31" s="35">
         <f t="shared" si="2"/>
         <v>5.3800000000000008</v>
       </c>
       <c r="O31" s="7"/>
-    </row>
-    <row r="32" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T31" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U31" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="11">
         <f>ROW(B32) - ROW($B$2)</f>
@@ -3602,19 +3955,31 @@
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="L32" s="30" t="s">
+      <c r="L32" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M32" s="14">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="N32" s="37">
+      <c r="N32" s="35">
         <f t="shared" si="2"/>
         <v>2.3250000000000002</v>
       </c>
       <c r="O32" s="7"/>
-    </row>
-    <row r="33" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T32" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U32" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="11">
         <f t="shared" si="0"/>
@@ -3648,19 +4013,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L33" s="30" t="s">
+      <c r="L33" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M33" s="14">
         <v>4.3280000000000003</v>
       </c>
-      <c r="N33" s="37">
+      <c r="N33" s="35">
         <f t="shared" si="2"/>
         <v>21.64</v>
       </c>
       <c r="O33" s="9"/>
-    </row>
-    <row r="34" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T33" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U33" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="11">
         <f>ROW(B34) - ROW($B$2)</f>
@@ -3694,19 +4071,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L34" s="30" t="s">
+      <c r="L34" s="28" t="s">
         <v>349</v>
       </c>
       <c r="M34" s="14">
         <v>0.3725</v>
       </c>
-      <c r="N34" s="37">
+      <c r="N34" s="35">
         <f t="shared" si="2"/>
         <v>1.8625</v>
       </c>
       <c r="O34" s="7"/>
-    </row>
-    <row r="35" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T34" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U34" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V34" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="11">
         <f t="shared" si="0"/>
@@ -3740,19 +4129,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L35" s="30" t="s">
+      <c r="L35" s="28" t="s">
         <v>349</v>
       </c>
       <c r="M35" s="14">
         <v>0.57599999999999996</v>
       </c>
-      <c r="N35" s="37">
+      <c r="N35" s="35">
         <f t="shared" si="2"/>
         <v>2.88</v>
       </c>
       <c r="O35" s="9"/>
-    </row>
-    <row r="36" spans="1:15" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T35" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U35" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="11">
         <f>ROW(B36) - ROW($B$2)</f>
@@ -3786,19 +4187,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L36" s="30" t="s">
+      <c r="L36" s="28" t="s">
         <v>349</v>
       </c>
       <c r="M36" s="14">
         <v>6.8000000000000005E-2</v>
       </c>
-      <c r="N36" s="37">
+      <c r="N36" s="35">
         <f t="shared" si="2"/>
         <v>0.34</v>
       </c>
       <c r="O36" s="7"/>
-    </row>
-    <row r="37" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T36" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U36" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="11">
         <f t="shared" si="0"/>
@@ -3832,19 +4245,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L37" s="30" t="s">
+      <c r="L37" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M37" s="14">
         <v>25.25</v>
       </c>
-      <c r="N37" s="37">
+      <c r="N37" s="35">
         <f t="shared" si="2"/>
         <v>126.25</v>
       </c>
       <c r="O37" s="9"/>
-    </row>
-    <row r="38" spans="1:15" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T37" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U37" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V37" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="11">
         <f>ROW(B38) - ROW($B$2)</f>
@@ -3878,19 +4303,31 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L38" s="30" t="s">
+      <c r="L38" s="28" t="s">
         <v>349</v>
       </c>
       <c r="M38" s="14">
         <v>0.30809999999999998</v>
       </c>
-      <c r="N38" s="37">
+      <c r="N38" s="35">
         <f t="shared" si="2"/>
         <v>3.081</v>
       </c>
       <c r="O38" s="7"/>
-    </row>
-    <row r="39" spans="1:15" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T38" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U38" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V38" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="11">
         <f t="shared" si="0"/>
@@ -3924,19 +4361,31 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L39" s="30" t="s">
+      <c r="L39" s="28" t="s">
         <v>349</v>
       </c>
       <c r="M39" s="14">
         <v>0.30669999999999997</v>
       </c>
-      <c r="N39" s="37">
+      <c r="N39" s="35">
         <f t="shared" si="2"/>
         <v>6.1339999999999995</v>
       </c>
       <c r="O39" s="9"/>
-    </row>
-    <row r="40" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T39" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U39" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V39" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="11">
         <f>ROW(B40) - ROW($B$2)</f>
@@ -3970,19 +4419,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L40" s="30" t="s">
+      <c r="L40" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M40" s="14">
         <v>1.56</v>
       </c>
-      <c r="N40" s="37">
+      <c r="N40" s="35">
         <f t="shared" si="2"/>
         <v>7.8000000000000007</v>
       </c>
       <c r="O40" s="7"/>
-    </row>
-    <row r="41" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T40" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U40" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V40" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="11">
         <f t="shared" si="0"/>
@@ -4016,19 +4477,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L41" s="30" t="s">
+      <c r="L41" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M41" s="14">
         <v>1.19</v>
       </c>
-      <c r="N41" s="37">
+      <c r="N41" s="35">
         <f t="shared" si="2"/>
         <v>5.9499999999999993</v>
       </c>
       <c r="O41" s="9"/>
-    </row>
-    <row r="42" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T41" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U41" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V41" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="11">
         <f>ROW(B42) - ROW($B$2)</f>
@@ -4062,19 +4535,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L42" s="30" t="s">
+      <c r="L42" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M42" s="14">
         <v>1.85</v>
       </c>
-      <c r="N42" s="37">
+      <c r="N42" s="35">
         <f t="shared" si="2"/>
         <v>9.25</v>
       </c>
       <c r="O42" s="7"/>
-    </row>
-    <row r="43" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T42" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U42" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V42" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="11">
         <f t="shared" si="0"/>
@@ -4108,19 +4593,31 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L43" s="30" t="s">
+      <c r="L43" s="28" t="s">
         <v>349</v>
       </c>
       <c r="M43" s="14">
         <v>2.0799999999999999E-2</v>
       </c>
-      <c r="N43" s="37">
+      <c r="N43" s="35">
         <f t="shared" si="2"/>
         <v>0.41599999999999998</v>
       </c>
       <c r="O43" s="9"/>
-    </row>
-    <row r="44" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T43" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U43" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V43" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="11">
         <f>ROW(B44) - ROW($B$2)</f>
@@ -4154,19 +4651,31 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L44" s="30" t="s">
+      <c r="L44" s="28" t="s">
         <v>349</v>
       </c>
       <c r="M44" s="14">
         <v>2.1700000000000001E-2</v>
       </c>
-      <c r="N44" s="37">
+      <c r="N44" s="35">
         <f t="shared" si="2"/>
         <v>0.217</v>
       </c>
       <c r="O44" s="7"/>
-    </row>
-    <row r="45" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T44" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U44" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V44" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="11">
         <f t="shared" si="0"/>
@@ -4200,19 +4709,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L45" s="30" t="s">
+      <c r="L45" s="28" t="s">
         <v>349</v>
       </c>
       <c r="M45" s="14">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="N45" s="37">
+      <c r="N45" s="35">
         <f t="shared" si="2"/>
         <v>0.10999999999999999</v>
       </c>
       <c r="O45" s="9"/>
-    </row>
-    <row r="46" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T45" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U45" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V45" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="11">
         <f>ROW(B46) - ROW($B$2)</f>
@@ -4246,19 +4767,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L46" s="30" t="s">
+      <c r="L46" s="28" t="s">
         <v>349</v>
       </c>
       <c r="M46" s="14">
         <v>3.1300000000000001E-2</v>
       </c>
-      <c r="N46" s="37">
+      <c r="N46" s="35">
         <f t="shared" si="2"/>
         <v>0.1565</v>
       </c>
       <c r="O46" s="7"/>
-    </row>
-    <row r="47" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T46" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U46" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V46" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="11">
         <f t="shared" si="0"/>
@@ -4292,19 +4825,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L47" s="30" t="s">
+      <c r="L47" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M47" s="14">
         <v>1.0900000000000001</v>
       </c>
-      <c r="N47" s="37">
+      <c r="N47" s="35">
         <f t="shared" si="2"/>
         <v>5.45</v>
       </c>
       <c r="O47" s="9"/>
-    </row>
-    <row r="48" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T47" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U47" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V47" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="11">
         <f>ROW(B48) - ROW($B$2)</f>
@@ -4338,19 +4883,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L48" s="30" t="s">
+      <c r="L48" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M48" s="14">
         <v>1.0900000000000001</v>
       </c>
-      <c r="N48" s="37">
+      <c r="N48" s="35">
         <f t="shared" si="2"/>
         <v>5.45</v>
       </c>
       <c r="O48" s="7"/>
-    </row>
-    <row r="49" spans="1:15" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T48" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U48" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V48" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="11">
         <f t="shared" si="0"/>
@@ -4384,19 +4941,31 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L49" s="30" t="s">
+      <c r="L49" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M49" s="14">
         <v>0.2</v>
       </c>
-      <c r="N49" s="37">
+      <c r="N49" s="35">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="O49" s="9"/>
-    </row>
-    <row r="50" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T49" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U49" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V49" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="11">
         <f t="shared" si="0"/>
@@ -4430,19 +4999,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L50" s="30" t="s">
+      <c r="L50" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M50" s="14">
         <v>0.15</v>
       </c>
-      <c r="N50" s="37">
+      <c r="N50" s="35">
         <f t="shared" si="2"/>
         <v>0.75</v>
       </c>
       <c r="O50" s="9"/>
-    </row>
-    <row r="51" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T50" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U50" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V50" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="11">
         <f>ROW(B51) - ROW($B$2)</f>
@@ -4476,19 +5057,31 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L51" s="30" t="s">
+      <c r="L51" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M51" s="14">
         <v>0.1</v>
       </c>
-      <c r="N51" s="37">
+      <c r="N51" s="35">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O51" s="7"/>
-    </row>
-    <row r="52" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T51" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U51" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V51" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="11">
         <f t="shared" si="0"/>
@@ -4522,19 +5115,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L52" s="30" t="s">
+      <c r="L52" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M52" s="14">
         <v>0.15</v>
       </c>
-      <c r="N52" s="37">
+      <c r="N52" s="35">
         <f t="shared" si="2"/>
         <v>0.75</v>
       </c>
       <c r="O52" s="9"/>
-    </row>
-    <row r="53" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T52" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U52" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V52" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="11">
         <f>ROW(B53) - ROW($B$2)</f>
@@ -4568,19 +5173,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L53" s="30" t="s">
+      <c r="L53" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M53" s="14">
         <v>0.13</v>
       </c>
-      <c r="N53" s="37">
+      <c r="N53" s="35">
         <f t="shared" si="2"/>
         <v>0.65</v>
       </c>
       <c r="O53" s="7"/>
-    </row>
-    <row r="54" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T53" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U53" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V53" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="11">
         <f t="shared" si="0"/>
@@ -4614,19 +5231,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L54" s="30" t="s">
+      <c r="L54" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M54" s="14">
         <v>0.64</v>
       </c>
-      <c r="N54" s="37">
+      <c r="N54" s="35">
         <f t="shared" si="2"/>
         <v>3.2</v>
       </c>
       <c r="O54" s="9"/>
-    </row>
-    <row r="55" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T54" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U54" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V54" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="11">
         <f>ROW(B55) - ROW($B$2)</f>
@@ -4660,19 +5289,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L55" s="30" t="s">
+      <c r="L55" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M55" s="14">
         <v>0.15</v>
       </c>
-      <c r="N55" s="37">
+      <c r="N55" s="35">
         <f t="shared" si="2"/>
         <v>0.75</v>
       </c>
       <c r="O55" s="7"/>
-    </row>
-    <row r="56" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T55" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U55" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V55" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="11">
         <f t="shared" si="0"/>
@@ -4706,19 +5347,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L56" s="30" t="s">
+      <c r="L56" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M56" s="14">
         <v>0.15</v>
       </c>
-      <c r="N56" s="37">
+      <c r="N56" s="35">
         <f t="shared" si="2"/>
         <v>0.75</v>
       </c>
       <c r="O56" s="9"/>
-    </row>
-    <row r="57" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T56" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U56" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V56" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="11">
         <f>ROW(B57) - ROW($B$2)</f>
@@ -4752,19 +5405,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L57" s="30" t="s">
+      <c r="L57" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M57" s="14">
         <v>0.15</v>
       </c>
-      <c r="N57" s="37">
+      <c r="N57" s="35">
         <f t="shared" si="2"/>
         <v>0.75</v>
       </c>
       <c r="O57" s="7"/>
-    </row>
-    <row r="58" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T57" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U57" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V57" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="11">
         <f t="shared" si="0"/>
@@ -4798,19 +5463,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L58" s="30" t="s">
+      <c r="L58" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M58" s="14">
         <v>0.15</v>
       </c>
-      <c r="N58" s="37">
+      <c r="N58" s="35">
         <f t="shared" si="2"/>
         <v>0.75</v>
       </c>
       <c r="O58" s="9"/>
-    </row>
-    <row r="59" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T58" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U58" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V58" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="11">
         <f>ROW(B59) - ROW($B$2)</f>
@@ -4844,19 +5521,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L59" s="30" t="s">
+      <c r="L59" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M59" s="14">
         <v>0.1</v>
       </c>
-      <c r="N59" s="37">
+      <c r="N59" s="35">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="O59" s="7"/>
-    </row>
-    <row r="60" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T59" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U59" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V59" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="11">
         <f t="shared" si="0"/>
@@ -4890,19 +5579,31 @@
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="L60" s="30" t="s">
+      <c r="L60" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M60" s="14">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="N60" s="37">
+      <c r="N60" s="35">
         <f t="shared" si="2"/>
         <v>0.375</v>
       </c>
       <c r="O60" s="9"/>
-    </row>
-    <row r="61" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T60" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U60" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V60" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="11">
         <f>ROW(B61) - ROW($B$2)</f>
@@ -4936,19 +5637,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L61" s="30" t="s">
+      <c r="L61" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M61" s="14">
         <v>0.1</v>
       </c>
-      <c r="N61" s="37">
+      <c r="N61" s="35">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="O61" s="7"/>
-    </row>
-    <row r="62" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T61" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U61" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V61" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="11">
         <f t="shared" si="0"/>
@@ -4982,19 +5695,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L62" s="30" t="s">
+      <c r="L62" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M62" s="14">
         <v>0.1</v>
       </c>
-      <c r="N62" s="37">
+      <c r="N62" s="35">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="O62" s="9"/>
-    </row>
-    <row r="63" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T62" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U62" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V62" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="11">
         <f>ROW(B63) - ROW($B$2)</f>
@@ -5028,19 +5753,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L63" s="30" t="s">
+      <c r="L63" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M63" s="14">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="N63" s="37">
+      <c r="N63" s="35">
         <f t="shared" si="2"/>
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="O63" s="7"/>
-    </row>
-    <row r="64" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T63" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U63" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V63" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="11">
         <f t="shared" si="0"/>
@@ -5074,19 +5811,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L64" s="30" t="s">
+      <c r="L64" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M64" s="14">
         <v>0.1</v>
       </c>
-      <c r="N64" s="37">
+      <c r="N64" s="35">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="O64" s="9"/>
-    </row>
-    <row r="65" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T64" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U64" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V64" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="11">
         <f t="shared" si="0"/>
@@ -5120,19 +5869,31 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L65" s="30" t="s">
+      <c r="L65" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M65" s="14">
         <v>0.1</v>
       </c>
-      <c r="N65" s="37">
+      <c r="N65" s="35">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O65" s="9"/>
-    </row>
-    <row r="66" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T65" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U65" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V65" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="11">
         <f>ROW(B66) - ROW($B$2)</f>
@@ -5166,19 +5927,31 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L66" s="30" t="s">
+      <c r="L66" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M66" s="14">
         <v>0.1</v>
       </c>
-      <c r="N66" s="37">
+      <c r="N66" s="35">
         <f>M66*K66</f>
         <v>1</v>
       </c>
       <c r="O66" s="9"/>
-    </row>
-    <row r="67" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T66" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U66" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V66" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="11">
         <f t="shared" si="0"/>
@@ -5212,19 +5985,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L67" s="30" t="s">
+      <c r="L67" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M67" s="14">
         <v>0.1</v>
       </c>
-      <c r="N67" s="37">
+      <c r="N67" s="35">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="O67" s="9"/>
-    </row>
-    <row r="68" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T67" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U67" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V67" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
       <c r="B68" s="11">
         <f>ROW(B68) - ROW($B$2)</f>
@@ -5258,19 +6043,31 @@
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="L68" s="30" t="s">
+      <c r="L68" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M68" s="14">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="N68" s="37">
+      <c r="N68" s="35">
         <f t="shared" si="2"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="O68" s="7"/>
-    </row>
-    <row r="69" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T68" t="b">
+        <f t="shared" ref="T68:T95" si="8">IF(Q68=D68,TRUE,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="U68" t="b">
+        <f t="shared" ref="U68:U95" si="9">IF(R68=G68,TRUE,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="V68" t="b">
+        <f t="shared" ref="V68:V95" si="10">IF(S68=J68,TRUE,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="11">
         <f t="shared" si="0"/>
@@ -5301,22 +6098,34 @@
         <v>2</v>
       </c>
       <c r="K69" s="7">
-        <f t="shared" ref="K69:K98" si="5">J69*5</f>
+        <f t="shared" ref="K69:K99" si="11">J69*5</f>
         <v>10</v>
       </c>
-      <c r="L69" s="30" t="s">
+      <c r="L69" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M69" s="14">
         <v>1.9E-2</v>
       </c>
-      <c r="N69" s="37">
+      <c r="N69" s="35">
         <f t="shared" si="2"/>
         <v>0.19</v>
       </c>
       <c r="O69" s="9"/>
-    </row>
-    <row r="70" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T69" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U69" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V69" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
       <c r="B70" s="11">
         <f>ROW(B70) - ROW($B$2)</f>
@@ -5347,22 +6156,34 @@
         <v>1</v>
       </c>
       <c r="K70" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="L70" s="30" t="s">
+      <c r="L70" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M70" s="14">
         <v>0.1</v>
       </c>
-      <c r="N70" s="37">
+      <c r="N70" s="35">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="O70" s="7"/>
-    </row>
-    <row r="71" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T70" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U70" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V70" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
       <c r="B71" s="11">
         <f t="shared" si="0"/>
@@ -5393,22 +6214,34 @@
         <v>1</v>
       </c>
       <c r="K71" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="L71" s="30" t="s">
+      <c r="L71" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M71" s="14">
         <v>0.1</v>
       </c>
-      <c r="N71" s="37">
+      <c r="N71" s="35">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="O71" s="9"/>
-    </row>
-    <row r="72" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T71" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U71" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V71" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="11">
         <f t="shared" si="0"/>
@@ -5439,22 +6272,34 @@
         <v>1</v>
       </c>
       <c r="K72" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="L72" s="30" t="s">
+      <c r="L72" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M72" s="14">
         <v>0.14000000000000001</v>
       </c>
-      <c r="N72" s="37">
+      <c r="N72" s="35">
         <f t="shared" si="2"/>
         <v>0.70000000000000007</v>
       </c>
       <c r="O72" s="7"/>
-    </row>
-    <row r="73" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T72" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U72" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V72" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="11">
         <f t="shared" si="0"/>
@@ -5485,22 +6330,34 @@
         <v>1</v>
       </c>
       <c r="K73" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="L73" s="30" t="s">
+      <c r="L73" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M73" s="14">
         <v>0.1</v>
       </c>
-      <c r="N73" s="37">
+      <c r="N73" s="35">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="O73" s="7"/>
-    </row>
-    <row r="74" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T73" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U73" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V73" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="11">
         <f>ROW(B74) - ROW($B$2)</f>
@@ -5531,22 +6388,34 @@
         <v>2</v>
       </c>
       <c r="K74" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
-      <c r="L74" s="30" t="s">
+      <c r="L74" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M74" s="14">
         <v>9.4030000000000002E-2</v>
       </c>
-      <c r="N74" s="37">
+      <c r="N74" s="35">
         <f t="shared" si="2"/>
         <v>0.94030000000000002</v>
       </c>
       <c r="O74" s="7"/>
-    </row>
-    <row r="75" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T74" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U74" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V74" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="11">
         <f t="shared" si="0"/>
@@ -5577,22 +6446,34 @@
         <v>4</v>
       </c>
       <c r="K75" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
-      <c r="L75" s="30" t="s">
+      <c r="L75" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M75" s="14">
         <v>1.9E-2</v>
       </c>
-      <c r="N75" s="37">
-        <f t="shared" ref="N75:N98" si="6">M75*K75</f>
+      <c r="N75" s="35">
+        <f t="shared" ref="N75:N99" si="12">M75*K75</f>
         <v>0.38</v>
       </c>
       <c r="O75" s="9"/>
-    </row>
-    <row r="76" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T75" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U75" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V75" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="11">
         <f t="shared" si="0"/>
@@ -5623,22 +6504,34 @@
         <v>2</v>
       </c>
       <c r="K76" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
-      <c r="L76" s="30" t="s">
+      <c r="L76" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M76" s="14">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="N76" s="37">
-        <f t="shared" si="6"/>
+      <c r="N76" s="35">
+        <f t="shared" si="12"/>
         <v>0.10999999999999999</v>
       </c>
       <c r="O76" s="7"/>
-    </row>
-    <row r="77" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T76" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U76" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V76" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="11">
         <f t="shared" si="0"/>
@@ -5669,22 +6562,34 @@
         <v>4</v>
       </c>
       <c r="K77" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
-      <c r="L77" s="30" t="s">
+      <c r="L77" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M77" s="14">
         <v>0.16</v>
       </c>
-      <c r="N77" s="37">
-        <f t="shared" si="6"/>
+      <c r="N77" s="35">
+        <f t="shared" si="12"/>
         <v>3.2</v>
       </c>
       <c r="O77" s="7"/>
-    </row>
-    <row r="78" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T77" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U77" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V77" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="11">
         <f>ROW(B78) - ROW($B$2)</f>
@@ -5715,22 +6620,34 @@
         <v>8</v>
       </c>
       <c r="K78" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>40</v>
       </c>
-      <c r="L78" s="30" t="s">
+      <c r="L78" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M78" s="14">
         <v>0.16</v>
       </c>
-      <c r="N78" s="37">
-        <f t="shared" si="6"/>
+      <c r="N78" s="35">
+        <f t="shared" si="12"/>
         <v>6.4</v>
       </c>
       <c r="O78" s="7"/>
-    </row>
-    <row r="79" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T78" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U78" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V78" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="11">
         <f t="shared" si="0"/>
@@ -5761,22 +6678,34 @@
         <v>8</v>
       </c>
       <c r="K79" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>40</v>
       </c>
-      <c r="L79" s="30" t="s">
+      <c r="L79" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M79" s="14">
         <v>0.16</v>
       </c>
-      <c r="N79" s="37">
-        <f t="shared" si="6"/>
+      <c r="N79" s="35">
+        <f t="shared" si="12"/>
         <v>6.4</v>
       </c>
       <c r="O79" s="7"/>
-    </row>
-    <row r="80" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T79" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U79" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V79" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="11">
         <f>ROW(B80) - ROW($B$2)</f>
@@ -5807,23 +6736,35 @@
         <v>1</v>
       </c>
       <c r="K80" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="L80" s="31" t="s">
+      <c r="L80" s="29" t="s">
         <v>336</v>
       </c>
       <c r="M80" s="17" t="s">
         <v>336</v>
       </c>
-      <c r="N80" s="38" t="s">
+      <c r="N80" s="36" t="s">
         <v>336</v>
       </c>
       <c r="O80" s="15" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="81" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T80" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U80" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V80" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="11">
         <f t="shared" si="0"/>
@@ -5854,22 +6795,34 @@
         <v>2</v>
       </c>
       <c r="K81" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
-      <c r="L81" s="30" t="s">
+      <c r="L81" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M81" s="14">
         <v>0.98299999999999998</v>
       </c>
-      <c r="N81" s="37">
-        <f t="shared" si="6"/>
+      <c r="N81" s="35">
+        <f t="shared" si="12"/>
         <v>9.83</v>
       </c>
       <c r="O81" s="9"/>
-    </row>
-    <row r="82" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T81" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U81" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V81" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="11">
         <f>ROW(B82) - ROW($B$2)</f>
@@ -5900,22 +6853,34 @@
         <v>1</v>
       </c>
       <c r="K82" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="L82" s="30" t="s">
+      <c r="L82" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M82" s="14">
         <v>1.9</v>
       </c>
-      <c r="N82" s="37">
-        <f t="shared" si="6"/>
+      <c r="N82" s="35">
+        <f t="shared" si="12"/>
         <v>9.5</v>
       </c>
       <c r="O82" s="7"/>
-    </row>
-    <row r="83" spans="1:23" s="19" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T82" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U82" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V82" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:26" s="19" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="18"/>
       <c r="B83" s="11">
         <f t="shared" si="0"/>
@@ -5946,17 +6911,17 @@
         <v>1</v>
       </c>
       <c r="K83" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="L83" s="30" t="s">
+      <c r="L83" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M83" s="14">
         <v>6.11</v>
       </c>
-      <c r="N83" s="37">
-        <f t="shared" si="6"/>
+      <c r="N83" s="35">
+        <f t="shared" si="12"/>
         <v>30.55</v>
       </c>
       <c r="O83" s="9"/>
@@ -5964,12 +6929,24 @@
       <c r="Q83"/>
       <c r="R83"/>
       <c r="S83"/>
-      <c r="T83"/>
-      <c r="U83"/>
-      <c r="V83"/>
+      <c r="T83" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U83" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V83" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="W83"/>
-    </row>
-    <row r="84" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="X83"/>
+      <c r="Y83"/>
+      <c r="Z83"/>
+    </row>
+    <row r="84" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="11">
         <f>ROW(B84) - ROW($B$2)</f>
@@ -6000,22 +6977,34 @@
         <v>1</v>
       </c>
       <c r="K84" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="L84" s="30" t="s">
+      <c r="L84" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M84" s="14">
         <v>2.41</v>
       </c>
-      <c r="N84" s="37">
-        <f t="shared" si="6"/>
+      <c r="N84" s="35">
+        <f t="shared" si="12"/>
         <v>12.05</v>
       </c>
       <c r="O84" s="7"/>
-    </row>
-    <row r="85" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T84" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U84" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V84" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="11">
         <f t="shared" si="0"/>
@@ -6046,22 +7035,34 @@
         <v>1</v>
       </c>
       <c r="K85" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="L85" s="30" t="s">
+      <c r="L85" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M85" s="14">
         <v>1.43</v>
       </c>
-      <c r="N85" s="37">
-        <f t="shared" si="6"/>
+      <c r="N85" s="35">
+        <f t="shared" si="12"/>
         <v>7.1499999999999995</v>
       </c>
       <c r="O85" s="9"/>
-    </row>
-    <row r="86" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T85" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U85" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V85" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="11">
         <f>ROW(B86) - ROW($B$2)</f>
@@ -6092,22 +7093,34 @@
         <v>1</v>
       </c>
       <c r="K86" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="L86" s="30" t="s">
+      <c r="L86" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M86" s="14">
         <v>2.27</v>
       </c>
-      <c r="N86" s="37">
-        <f t="shared" si="6"/>
+      <c r="N86" s="35">
+        <f t="shared" si="12"/>
         <v>11.35</v>
       </c>
       <c r="O86" s="7"/>
-    </row>
-    <row r="87" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T86" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U86" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V86" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="11">
         <f t="shared" si="0"/>
@@ -6138,22 +7151,34 @@
         <v>1</v>
       </c>
       <c r="K87" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="L87" s="30" t="s">
+      <c r="L87" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M87" s="14">
         <v>1.1599999999999999</v>
       </c>
-      <c r="N87" s="37">
-        <f t="shared" si="6"/>
+      <c r="N87" s="35">
+        <f t="shared" si="12"/>
         <v>5.8</v>
       </c>
       <c r="O87" s="9"/>
-    </row>
-    <row r="88" spans="1:23" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T87" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U87" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V87" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:26" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="11">
         <f>ROW(B88) - ROW($B$2)</f>
@@ -6184,22 +7209,34 @@
         <v>1</v>
       </c>
       <c r="K88" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="L88" s="30" t="s">
+      <c r="L88" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M88" s="14">
         <v>4.66</v>
       </c>
-      <c r="N88" s="37">
-        <f t="shared" si="6"/>
+      <c r="N88" s="35">
+        <f t="shared" si="12"/>
         <v>23.3</v>
       </c>
       <c r="O88" s="7"/>
-    </row>
-    <row r="89" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T88" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U88" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V88" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="11">
         <f t="shared" si="0"/>
@@ -6230,22 +7267,34 @@
         <v>1</v>
       </c>
       <c r="K89" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="L89" s="30" t="s">
+      <c r="L89" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M89" s="14">
         <v>3</v>
       </c>
-      <c r="N89" s="37">
-        <f t="shared" si="6"/>
+      <c r="N89" s="35">
+        <f t="shared" si="12"/>
         <v>15</v>
       </c>
       <c r="O89" s="9"/>
-    </row>
-    <row r="90" spans="1:23" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T89" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U89" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V89" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:26" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="11">
         <f>ROW(B90) - ROW($B$2)</f>
@@ -6276,22 +7325,34 @@
         <v>1</v>
       </c>
       <c r="K90" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="L90" s="30" t="s">
+      <c r="L90" s="28" t="s">
         <v>349</v>
       </c>
       <c r="M90" s="14">
         <v>2.6663999999999999</v>
       </c>
-      <c r="N90" s="37">
-        <f t="shared" si="6"/>
+      <c r="N90" s="35">
+        <f t="shared" si="12"/>
         <v>13.331999999999999</v>
       </c>
       <c r="O90" s="7"/>
-    </row>
-    <row r="91" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T90" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U90" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V90" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="11">
         <f t="shared" si="0"/>
@@ -6322,22 +7383,34 @@
         <v>1</v>
       </c>
       <c r="K91" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="L91" s="30" t="s">
+      <c r="L91" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M91" s="14">
         <v>4.51</v>
       </c>
-      <c r="N91" s="37">
-        <f t="shared" si="6"/>
+      <c r="N91" s="35">
+        <f t="shared" si="12"/>
         <v>22.549999999999997</v>
       </c>
       <c r="O91" s="9"/>
-    </row>
-    <row r="92" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T91" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U91" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V91" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
       <c r="B92" s="11">
         <f>ROW(B92) - ROW($B$2)</f>
@@ -6368,22 +7441,34 @@
         <v>4</v>
       </c>
       <c r="K92" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
-      <c r="L92" s="30" t="s">
+      <c r="L92" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M92" s="14">
         <v>0.68</v>
       </c>
-      <c r="N92" s="37">
-        <f t="shared" si="6"/>
+      <c r="N92" s="35">
+        <f t="shared" si="12"/>
         <v>13.600000000000001</v>
       </c>
       <c r="O92" s="7"/>
-    </row>
-    <row r="93" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T92" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U92" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V92" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
       <c r="B93" s="11">
         <f t="shared" si="0"/>
@@ -6414,22 +7499,34 @@
         <v>2</v>
       </c>
       <c r="K93" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
-      <c r="L93" s="30" t="s">
+      <c r="L93" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M93" s="14">
         <v>5.2880000000000003</v>
       </c>
-      <c r="N93" s="37">
-        <f t="shared" si="6"/>
+      <c r="N93" s="35">
+        <f t="shared" si="12"/>
         <v>52.88</v>
       </c>
       <c r="O93" s="9"/>
-    </row>
-    <row r="94" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T93" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U93" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V93" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
       <c r="B94" s="11">
         <f>ROW(B94) - ROW($B$2)</f>
@@ -6460,24 +7557,36 @@
         <v>1</v>
       </c>
       <c r="K94" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="L94" s="30" t="s">
+      <c r="L94" s="28" t="s">
         <v>337</v>
       </c>
       <c r="M94" s="14">
         <v>0.95</v>
       </c>
-      <c r="N94" s="37">
-        <f t="shared" si="6"/>
+      <c r="N94" s="35">
+        <f t="shared" si="12"/>
         <v>4.75</v>
       </c>
       <c r="O94" s="7"/>
-    </row>
-    <row r="95" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T94" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U94" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V94" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B95" s="11">
-        <f t="shared" ref="B95" si="7">ROW(B95) - ROW($B$2)</f>
+        <f t="shared" ref="B95" si="13">ROW(B95) - ROW($B$2)</f>
         <v>93</v>
       </c>
       <c r="C95" s="13" t="s">
@@ -6503,176 +7612,209 @@
         <v>8</v>
       </c>
       <c r="K95" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>40</v>
       </c>
-      <c r="L95" s="32" t="s">
+      <c r="L95" s="30" t="s">
         <v>337</v>
       </c>
       <c r="M95" s="14">
         <v>2.98</v>
       </c>
-      <c r="N95" s="37">
-        <f t="shared" si="6"/>
+      <c r="N95" s="35">
+        <f t="shared" si="12"/>
         <v>119.2</v>
       </c>
-      <c r="O95" s="23"/>
-    </row>
-    <row r="96" spans="1:23" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O95" s="22"/>
+      <c r="T95" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U95" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V95" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:26" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B96" s="11">
         <f>ROW(B96) - ROW($B$2)</f>
         <v>94</v>
       </c>
-      <c r="C96" s="13" t="s">
+      <c r="C96" s="12" t="s">
         <v>354</v>
       </c>
-      <c r="D96" s="23" t="s">
+      <c r="D96" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="E96" s="23" t="s">
+      <c r="E96" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="F96" s="23" t="s">
+      <c r="F96" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="G96" s="22" t="s">
+      <c r="G96" s="8" t="s">
         <v>356</v>
       </c>
-      <c r="H96" s="23" t="s">
+      <c r="H96" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="I96" s="22" t="s">
+      <c r="I96" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="J96" s="23">
+      <c r="J96" s="7">
         <v>2</v>
       </c>
       <c r="K96" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
-      <c r="L96" s="32" t="s">
-        <v>337</v>
-      </c>
-      <c r="M96" s="24">
-        <v>0.35</v>
-      </c>
-      <c r="N96" s="39">
-        <f t="shared" si="6"/>
-        <v>3.5</v>
-      </c>
-      <c r="O96" s="23"/>
+      <c r="L96" s="28" t="s">
+        <v>349</v>
+      </c>
+      <c r="M96" s="14">
+        <v>8.3099999999999993E-2</v>
+      </c>
+      <c r="N96" s="35">
+        <f t="shared" si="12"/>
+        <v>0.83099999999999996</v>
+      </c>
+      <c r="O96" s="7"/>
     </row>
     <row r="97" spans="2:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B97" s="11">
-        <f t="shared" ref="B97:B98" si="8">ROW(B97) - ROW($B$2)</f>
+        <f t="shared" ref="B97" si="14">ROW(B97) - ROW($B$2)</f>
         <v>95</v>
       </c>
-      <c r="C97" s="13" t="s">
+      <c r="C97" s="12" t="s">
         <v>354</v>
       </c>
-      <c r="D97" s="9" t="s">
+      <c r="D97" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="E97" s="9" t="s">
+      <c r="E97" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="F97" s="7"/>
+      <c r="G97" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="H97" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="I97" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="J97" s="7">
+        <v>1</v>
+      </c>
+      <c r="K97" s="7">
+        <v>2</v>
+      </c>
+      <c r="L97" s="28" t="s">
+        <v>433</v>
+      </c>
+      <c r="M97" s="14">
+        <v>16.989999999999998</v>
+      </c>
+      <c r="N97" s="35">
+        <f t="shared" si="12"/>
+        <v>33.979999999999997</v>
+      </c>
+      <c r="O97" s="7"/>
+    </row>
+    <row r="98" spans="2:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B98" s="11">
+        <f t="shared" ref="B98:B99" si="15">ROW(B98) - ROW($B$2)</f>
+        <v>96</v>
+      </c>
+      <c r="C98" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="D98" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="E98" s="9" t="s">
         <v>425</v>
       </c>
-      <c r="F97" s="9" t="s">
+      <c r="F98" s="9" t="s">
         <v>336</v>
       </c>
-      <c r="G97" s="10" t="s">
+      <c r="G98" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="H97" s="9" t="s">
+      <c r="H98" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="I97" s="10" t="s">
+      <c r="I98" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="J97" s="9">
+      <c r="J98" s="9">
         <v>1</v>
       </c>
-      <c r="K97" s="7">
-        <f t="shared" si="5"/>
+      <c r="K98" s="7">
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="L97" s="33" t="s">
+      <c r="L98" s="31" t="s">
         <v>349</v>
       </c>
-      <c r="M97" s="35">
+      <c r="M98" s="33">
         <v>0.73499999999999999</v>
       </c>
-      <c r="N97" s="40">
-        <f t="shared" si="6"/>
+      <c r="N98" s="37">
+        <f t="shared" si="12"/>
         <v>3.6749999999999998</v>
       </c>
-      <c r="O97" s="9"/>
-    </row>
-    <row r="98" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B98" s="11">
-        <f t="shared" si="8"/>
-        <v>96</v>
-      </c>
-      <c r="C98" s="25" t="s">
+      <c r="O98" s="9"/>
+    </row>
+    <row r="99" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B99" s="11">
+        <f t="shared" si="15"/>
+        <v>97</v>
+      </c>
+      <c r="C99" s="23" t="s">
         <v>354</v>
       </c>
-      <c r="D98" s="26" t="s">
+      <c r="D99" s="24" t="s">
         <v>336</v>
       </c>
-      <c r="E98" s="26" t="s">
+      <c r="E99" s="24" t="s">
         <v>427</v>
       </c>
-      <c r="F98" s="26" t="s">
+      <c r="F99" s="24" t="s">
         <v>336</v>
       </c>
-      <c r="G98" s="27" t="s">
+      <c r="G99" s="25" t="s">
         <v>426</v>
       </c>
-      <c r="H98" s="26" t="s">
+      <c r="H99" s="24" t="s">
         <v>394</v>
       </c>
-      <c r="I98" s="27" t="s">
+      <c r="I99" s="25" t="s">
         <v>336</v>
       </c>
-      <c r="J98" s="26">
+      <c r="J99" s="24">
         <v>1</v>
       </c>
-      <c r="K98" s="7">
-        <f t="shared" si="5"/>
+      <c r="K99" s="7">
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="L98" s="34" t="s">
+      <c r="L99" s="32" t="s">
         <v>349</v>
       </c>
-      <c r="M98" s="36">
+      <c r="M99" s="34">
         <v>1.2457</v>
       </c>
-      <c r="N98" s="41">
-        <f t="shared" si="6"/>
+      <c r="N99" s="38">
+        <f t="shared" si="12"/>
         <v>6.2285000000000004</v>
       </c>
-      <c r="O98" s="26"/>
-    </row>
-    <row r="99" spans="2:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B99" s="1"/>
-      <c r="C99" s="1"/>
-      <c r="D99" s="1"/>
-      <c r="E99" s="1"/>
-      <c r="F99" s="1"/>
-      <c r="G99" s="1"/>
-      <c r="H99" s="1"/>
-      <c r="I99" s="1"/>
-      <c r="J99" s="1"/>
-      <c r="K99" s="43" t="s">
-        <v>350</v>
-      </c>
-      <c r="L99" s="44"/>
-      <c r="M99" s="45"/>
-      <c r="N99" s="21">
-        <f>SUM(N10:N98)</f>
-        <v>677.73879999999997</v>
-      </c>
-      <c r="O99" s="1"/>
+      <c r="O99" s="24"/>
     </row>
     <row r="100" spans="2:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B100" s="1"/>
@@ -6684,22 +7826,43 @@
       <c r="H100" s="1"/>
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
-      <c r="K100" s="46" t="s">
+      <c r="K100" s="45" t="s">
+        <v>350</v>
+      </c>
+      <c r="L100" s="46"/>
+      <c r="M100" s="47"/>
+      <c r="N100" s="21">
+        <f>SUM(N10:N99)</f>
+        <v>709.0498</v>
+      </c>
+      <c r="O100" s="1"/>
+    </row>
+    <row r="101" spans="2:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B101" s="1"/>
+      <c r="C101" s="1"/>
+      <c r="D101" s="1"/>
+      <c r="E101" s="1"/>
+      <c r="F101" s="1"/>
+      <c r="G101" s="1"/>
+      <c r="H101" s="1"/>
+      <c r="I101" s="1"/>
+      <c r="J101" s="1"/>
+      <c r="K101" s="48" t="s">
         <v>348</v>
       </c>
-      <c r="L100" s="47"/>
-      <c r="M100" s="48"/>
-      <c r="N100" s="20">
-        <f>N99/5</f>
-        <v>135.54775999999998</v>
-      </c>
-      <c r="O100" s="1"/>
+      <c r="L101" s="49"/>
+      <c r="M101" s="50"/>
+      <c r="N101" s="20">
+        <f>N100/5</f>
+        <v>141.80995999999999</v>
+      </c>
+      <c r="O101" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="I1:O1"/>
-    <mergeCell ref="K99:M99"/>
     <mergeCell ref="K100:M100"/>
+    <mergeCell ref="K101:M101"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="L3" r:id="rId1"/>
@@ -6777,28 +7940,29 @@
     <hyperlink ref="L46" r:id="rId73"/>
     <hyperlink ref="L90" r:id="rId74"/>
     <hyperlink ref="L37" r:id="rId75"/>
-    <hyperlink ref="L96" r:id="rId76"/>
-    <hyperlink ref="L32" r:id="rId77"/>
-    <hyperlink ref="L76" r:id="rId78"/>
-    <hyperlink ref="L38" r:id="rId79"/>
-    <hyperlink ref="L39" r:id="rId80"/>
-    <hyperlink ref="L72" r:id="rId81"/>
-    <hyperlink ref="L73" r:id="rId82"/>
-    <hyperlink ref="L34" r:id="rId83"/>
-    <hyperlink ref="L65" r:id="rId84"/>
-    <hyperlink ref="L98" r:id="rId85"/>
-    <hyperlink ref="L19" r:id="rId86"/>
-    <hyperlink ref="L20" r:id="rId87"/>
-    <hyperlink ref="L21" r:id="rId88"/>
-    <hyperlink ref="L77" r:id="rId89"/>
-    <hyperlink ref="L78" r:id="rId90"/>
-    <hyperlink ref="L79" r:id="rId91"/>
-    <hyperlink ref="L95" r:id="rId92"/>
-    <hyperlink ref="L97" r:id="rId93"/>
-    <hyperlink ref="L22" r:id="rId94"/>
-    <hyperlink ref="L35" r:id="rId95"/>
+    <hyperlink ref="L32" r:id="rId76"/>
+    <hyperlink ref="L76" r:id="rId77"/>
+    <hyperlink ref="L38" r:id="rId78"/>
+    <hyperlink ref="L39" r:id="rId79"/>
+    <hyperlink ref="L72" r:id="rId80"/>
+    <hyperlink ref="L73" r:id="rId81"/>
+    <hyperlink ref="L34" r:id="rId82"/>
+    <hyperlink ref="L65" r:id="rId83"/>
+    <hyperlink ref="L99" r:id="rId84"/>
+    <hyperlink ref="L19" r:id="rId85"/>
+    <hyperlink ref="L20" r:id="rId86"/>
+    <hyperlink ref="L21" r:id="rId87"/>
+    <hyperlink ref="L77" r:id="rId88"/>
+    <hyperlink ref="L78" r:id="rId89"/>
+    <hyperlink ref="L79" r:id="rId90"/>
+    <hyperlink ref="L95" r:id="rId91"/>
+    <hyperlink ref="L98" r:id="rId92"/>
+    <hyperlink ref="L22" r:id="rId93"/>
+    <hyperlink ref="L35" r:id="rId94"/>
+    <hyperlink ref="L96" r:id="rId95"/>
+    <hyperlink ref="L97" r:id="rId96"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId96"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId97"/>
 </worksheet>
 </file>